--- a/data/xlsx/vat.xlsx
+++ b/data/xlsx/vat.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>yCnzny</t>
+          <t>yCnzn</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>235597361</t>
+          <t>335597361</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2235676551</t>
+          <t>1235676551</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0000001560</t>
+          <t>000000156</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1237418735</t>
+          <t>2237418735</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>338052254</t>
+          <t>238052254</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>000000456</t>
+          <t>0000004567</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>72021472604</t>
+          <t>62021472604</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>239556867</t>
+          <t>339556867</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2239556861</t>
+          <t>1239556861</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0000006410</t>
+          <t>000000641</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1241219858</t>
+          <t>2241219858</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>342090949</t>
+          <t>242090949</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>75032139753</t>
+          <t>65032139753</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>000000941</t>
+          <t>0000009417</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>243516362</t>
+          <t>343516362</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2243516365</t>
+          <t>1243516365</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>0000011260</t>
+          <t>000001126</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>95090780855</t>
+          <t>05090780855</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1245100166</t>
+          <t>2245100166</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>345971254</t>
+          <t>245971254</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>78042806868</t>
+          <t>68042806868</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>000001426</t>
+          <t>0000014267</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2247396679</t>
+          <t>1247396679</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>247475861</t>
+          <t>347475861</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10412,7 +10412,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>0000016110</t>
+          <t>000001611</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>1248980475</t>
+          <t>2248980475</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11828,7 +11828,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>350009941</t>
+          <t>250009941</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>81050774016</t>
+          <t>71050774016</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>000001911</t>
+          <t>0000019117</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">

--- a/data/xlsx/vat.xlsx
+++ b/data/xlsx/vat.xlsx
@@ -105,7 +105,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -145,7 +145,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2018/06/03</t>
+          <t>2015/19/07</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -157,7 +157,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp z oo</t>
+          <t>Polskie Przetwory sp z oo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -167,7 +167,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -207,7 +207,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>03-03-2023</t>
+          <t>26-08-2016</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -219,7 +219,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o. o.</t>
+          <t>Hurtownia Nabiału Mleczko sp. z o. o.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -229,7 +229,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -269,7 +269,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2024-29-12</t>
+          <t>2017-05-09</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -281,7 +281,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lumen Advisory Sp. z o.o.</t>
+          <t>Agencja Reklamowa Kreatywni Sp. z o.o.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -291,7 +291,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -331,7 +331,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20151104</t>
+          <t>20181012</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -343,7 +343,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nova Data SP Z O O</t>
+          <t>Kancelaria Prawna Sankcja SP Z O O</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -353,7 +353,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -393,7 +393,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>19/11/2019</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -405,7 +405,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Optima Trade spółka z ograniczoną odpowiedzialnością</t>
+          <t>Śląskie Zakłady Mechaniczne spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -415,7 +415,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -455,7 +455,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2024/26/02</t>
+          <t>2020/26/12</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -467,7 +467,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Fabryka Okien i Drzwi Profil Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -477,7 +477,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>30-11-2019</t>
+          <t>05-01-2021</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -529,7 +529,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Quantum Services S.A.</t>
+          <t>Przedsiębiorstwo Robót rDogowych S.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>yCnzn</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -579,19 +579,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2016-17-06</t>
+          <t>2022-12-02</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2021-11-08</t>
+          <t>2021-08-11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Silesia Invest SA</t>
+          <t>Krakowskie Biuro Nieruchomości SA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>335597361</t>
+          <t>235597361</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>20220921</t>
+          <t>20230319</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vistula Fintech S. A.</t>
+          <t>Salon Samochodowy Auto-Hit S. A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>13/05/2021</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Astra Finance Spółka Akcyjna</t>
+          <t>Klinika Stomatologiczna Dent-Med Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2018/28/12</t>
+          <t>2025/05/05</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -777,7 +777,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o.o.</t>
+          <t>Polski Tytoń sp. z o.o.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>10-02-2018</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Helios Markets sp z oo</t>
+          <t>Gdańska Stocznia Jachtowa sp z oo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2018-16-10</t>
+          <t>2015-19-07</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o. o.</t>
+          <t>Wytwórnia Makaronu Jajecznego sp. z o. o.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wykreslony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>20210324</t>
+          <t>20160826</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nova Data Sp. z o.o.</t>
+          <t>Zakłady Mięsne Tradycja Sp. z o.o.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>02/08/2015</t>
+          <t>05/09/2017</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Optima Trade SP Z O O</t>
+          <t>Spółdzielnia Mleczarska Radomsko SP Z O O</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2023/03/01</t>
+          <t>2018/12/10</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1087,7 +1087,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Polaris Capital spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kancelaria Finansowo-Księgowa Bilans spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>000000156</t>
+          <t>0000001560</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>03-08-2015</t>
+          <t>19-11-2019</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1149,7 +1149,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zarząd Nieruchomości Komercyjnych Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Silesia Invest S.A.</t>
+          <t>Polskie Linie Oceaniczne S.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>20160313</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1273,7 +1273,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Vistula Fintech SA</t>
+          <t>Hurtownia Materiałów Budowlanych Cegiełka SA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Piłsudskiego 84, Rzeszów</t>
+          <t>Rynek 84, Opole</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Piłsudskiego 84, Rzeszów</t>
+          <t>Rynek 84, Opole</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19/07/2020</t>
+          <t>12/02/2022</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PPHU Astra Finance</t>
+          <t>PPHU Studio Projektowe Architektura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2015/13/08</t>
+          <t>2023/19/03</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1397,7 +1397,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka Akcyjna</t>
+          <t>Centrum Medycyny Pracy Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>10-11-2019</t>
+          <t>26-04-2024</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1459,7 +1459,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o.o.</t>
+          <t>Przedsiębiorstwo Energetyki Cieplnej sp. z o.o.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>236785219</t>
+          <t>246706057</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2015-22-04</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp z oo</t>
+          <t>Gospodarstwo Rolno-Ogrodnicze sp z oo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>20180517</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1583,7 +1583,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o. o.</t>
+          <t>Drukarnia Wielkoformatowa Impress sp. z o. o.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>21/03/2025</t>
+          <t>19/07/2015</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1645,7 +1645,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Optima Trade Sp. z o.o.</t>
+          <t>Klub Fitness Sylwetka Sp. z o.o.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2017/01/12</t>
+          <t>2016/26/08</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Polaris Capital SP Z O O</t>
+          <t>Polska Grupa Energetyczna SP Z O O</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>26-12-2019</t>
+          <t>05-09-2017</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -1769,7 +1769,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Quantum Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Mazowieckie Zakłady Drobiarskie spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1819,19 +1819,19 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2022-25-03</t>
+          <t>2018-12-10</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2018-05-03</t>
+          <t>2018-03-05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Hurtownia Farmaceutyczna Aptekarz Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>20150114</t>
+          <t>20191119</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -1893,7 +1893,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Kancelaria Notarialna Lex S.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>17/04/2021</t>
+          <t>26/12/2020</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -1955,7 +1955,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Astra Finance SA</t>
+          <t>Biuro Podróży Wojażer SA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2022/21/09</t>
+          <t>2021/05/01</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2017,7 +2017,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S. A.</t>
+          <t>Szkoła Języków Obcych Lingua S. A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>20-02-2024</t>
+          <t>12-02-2022</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2079,22 +2079,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka Akcyjna</t>
+          <t>Centrum Logistyczne Podlasie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2237418735</t>
+          <t>1247339575</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>237577115</t>
+          <t>247497957</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2129,19 +2129,19 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2022-19-05</t>
+          <t>2023-19-03</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2023-08-12</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o.o.</t>
+          <t>Fabryka Mebli Drewnianych Dąb sp. z o.o.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>20181213</t>
+          <t>20240426</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2203,7 +2203,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nova Data sp z oo</t>
+          <t>Polskie Sady sp z oo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>04/12/2017</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2265,17 +2265,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o. o.</t>
+          <t>Wielkopolska Hurtownia Stali sp. z o. o.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1237656305</t>
+          <t>1247577145</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2020/08/11</t>
+          <t>2026/12/06</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2327,7 +2327,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Polaris Capital Sp. z o.o.</t>
+          <t>Zakład Oczyszczania Miasta Sp. z o.o.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>237893879</t>
+          <t>247814719</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>13-01-2022</t>
+          <t>19-07-2015</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2389,7 +2389,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Quantum Services SP Z O O</t>
+          <t>Przedsiębiorstwo Wodociągów i Kanalizacji SP Z O O</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>57-300 Kłodzko</t>
+          <t>70-435 Szczecin</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>57-300 Kłodzko</t>
+          <t>70-435 Szczecin</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2021-16-09</t>
+          <t>2016-26-08</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Silesia Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Instytut Badań Rynkowych spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>20161117</t>
+          <t>20170905</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Vistula Fintech Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Agencja Ochrony Solidna Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>21/01/2018</t>
+          <t>12/10/2018</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>238210635</t>
+          <t>348131477</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2023/06/02</t>
+          <t>2019/19/11</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2637,7 +2637,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SA</t>
+          <t>Krajowa Izba Gospodarcza SA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>04-09-2019</t>
+          <t>26-12-2020</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2699,7 +2699,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Helios Markets S. A.</t>
+          <t>Polskie Zakłady Lotnicze S. A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2025-14-10</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2761,17 +2761,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka Akcyjna</t>
+          <t>Hurtownia Elektryczna Wat Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1238289820</t>
+          <t>1248210665</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>20250827</t>
+          <t>20220212</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2823,7 +2823,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o.o.</t>
+          <t>Centrum Ogrodnicze Zielona Oaza sp. z o.o.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>26/10/2022</t>
+          <t>19/03/2023</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -2885,7 +2885,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Optima Trade sp z oo</t>
+          <t>Piekarnia i Cukiernia Chrupiący Rogalik sp z oo</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2016/21/06</t>
+          <t>2024/26/04</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -2947,7 +2947,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o. o.</t>
+          <t>Zakład Usług Komunalnych sp. z o. o.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>04-06-2023</t>
+          <t>05-05-2025</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3009,7 +3009,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Quantum Services Sp. z o.o.</t>
+          <t>Polski Komfort Sp. z o.o.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3059,19 +3059,19 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2020-18-06</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Silesia Invest SP Z O O</t>
+          <t>Kancelaria Radców Prawnych Partnerzy SP Z O O</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>20200616</t>
+          <t>20150719</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3133,17 +3133,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Vistula Fintech spółka z ograniczoną odpowiedzialnością</t>
+          <t>Centrum Dystrybucji Alkoholi spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1238764965</t>
+          <t>1248685807</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>28/06/2024</t>
+          <t>26/08/2016</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3195,7 +3195,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Astra Finance Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Przedsiębiorstwo Spedycyjne Ładunek Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2018/29/08</t>
+          <t>2017/05/09</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3257,7 +3257,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Fabryka Tekstyliów Splot S.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>22-02-2019</t>
+          <t>12-10-2018</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3319,7 +3319,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Helios Markets SA</t>
+          <t>Górnośląskie Towarzystwo Finansowe SA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3369,19 +3369,19 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2023-21-03</t>
+          <t>2019-19-11</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2019-12-04</t>
+          <t>2019-04-12</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Lumen Advisory S. A.</t>
+          <t>Krajowa Agencja Informacyjna S. A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>20181119</t>
+          <t>20201226</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3443,7 +3443,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>Polskie Jagody Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>28/05/2017</t>
+          <t>05/01/2021</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3505,7 +3505,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o.o.</t>
+          <t>Zielony Amber sp. z o.o.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2025/22/06</t>
+          <t>2022/12/02</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3567,7 +3567,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Polaris Capital sp z oo</t>
+          <t>Zielony Bizon sp z oo</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>30-01-2025</t>
+          <t>19-03-2023</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Quantmu Services sp. z o. o.</t>
+          <t>Zielony Canyon sp. z o. .</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wkyrśe</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2023-15-03</t>
+          <t>2024-26-04</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3691,7 +3691,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Silesia Invest Sp. z o.o.</t>
+          <t>Zielony Delfin Sp. z o.o.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>339556867</t>
+          <t>239556867</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2024-29-03 07:07</t>
+          <t>2025-05-05 07:07</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -3753,7 +3753,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Vistula Fintech SP Z O O</t>
+          <t>Zielony Echo SP Z O O</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>22/06/2022</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -3815,7 +3815,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>P.P.H.U. Astra Finance</t>
+          <t>P.P.H.U. Zielony Falcon</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2024/24/12</t>
+          <t>2015/19/07</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -3877,7 +3877,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Gryf Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>11-12-2022</t>
+          <t>26-08-2016</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -3939,7 +3939,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Helios Markets S.A.</t>
+          <t>Zielony Horyzont S.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2016-28-11</t>
+          <t>2017-05-09</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4001,7 +4001,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lumen Advisory SA</t>
+          <t>Zielony Ikar SA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>20220604</t>
+          <t>20181012</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4063,7 +4063,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Nova Data S. A.</t>
+          <t>Zielony Jantar S. A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>20/02/2019</t>
+          <t>19/11/2019</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4125,7 +4125,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka Akcyjna</t>
+          <t>Zielony Koral Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2022/22/08</t>
+          <t>2020/26/12</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4187,7 +4187,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o.o.</t>
+          <t>Zielony Lotos sp. z o.o.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4212,17 +4212,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>000000641</t>
+          <t>0000006410</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 43, 00-590 Warszawa</t>
+          <t>ulica Chmielna 43, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 43, 00-590 Warszawa</t>
+          <t>ulica Chmielna 43, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>10-08-2023</t>
+          <t>05-01-2021</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Quantum Services sp z oo</t>
+          <t>Zielony Magnolia sp z oo</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 60, 00-071 Warszawa</t>
+          <t>Nowy Świat 60, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 60, 00-071 Warszawa</t>
+          <t>Nowy Świat 60, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4299,19 +4299,19 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2023-25-08</t>
+          <t>2022-12-02</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
+          <t>2022-07-05</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o. o.</t>
+          <t>Zielony Neon sp. z o. o.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ul. Floriańska 77/75, 31-019 Kraków</t>
+          <t>ul. os. Przyjaźń 77/75, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>ul. Floriańska 77/75, 31-019 Kraków</t>
+          <t>ul. os. Przyjaźń 77/75, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>20201010</t>
+          <t>20230319</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4373,7 +4373,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Vistula Fintech Sp. z o.o.</t>
+          <t>Zielony Oaza Sp. z o.o.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ul Długa 94, 31-147 Kraków</t>
+          <t>ul Jagiellońska 94, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ul Długa 94, 31-147 Kraków</t>
+          <t>ul Jagiellońska 94, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>23/02/2021</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4435,7 +4435,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Astra Finance SP Z O O</t>
+          <t>Zielony Pegaz SP Z O O</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ulica Piotrkowska 111, 90-102 Łódź</t>
+          <t>ulica Piłsudskiego 111, 05-270 Marki</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ulica Piotrkowska 111, 90-102 Łódź</t>
+          <t>ulica Piłsudskiego 111, 05-270 Marki</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2021/22/01</t>
+          <t>2025/05/05</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Baltic Med Supply spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Rubin spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Zachodnia 128, 90-402 Łódź</t>
+          <t>Andriollego 128, 05-400 Otwock</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Zachodnia 128, 90-402 Łódź</t>
+          <t>Andriollego 128, 05-400 Otwock</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>23-09-2022</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4559,7 +4559,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Szafir Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4589,12 +4589,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ul. Świdnicka 145/37, 50-066 Wrocław</t>
+          <t>ul. Żeromskiego 145/37, 26-600 Radom</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>ul. Świdnicka 145/37, 50-066 Wrocław</t>
+          <t>ul. Żeromskiego 145/37, 26-600 Radom</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2016-26-04</t>
+          <t>2015-19-07</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4621,7 +4621,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Lumen Advisory S.A.</t>
+          <t>Zielony Tytan S.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ul Legnicka 162, 54-203 Wrocław</t>
+          <t>ul Tumska 162, 09-402 Płock</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>ul Legnicka 162, 54-203 Wrocław</t>
+          <t>ul Tumska 162, 09-402 Płock</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>20250114</t>
+          <t>20160826</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4683,7 +4683,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Nova Data SA</t>
+          <t>Zielony Uran SA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4693,12 +4693,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>240903093</t>
+          <t>250823937</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ulica Święty Marcin 179, 61-806 Poznań</t>
+          <t>ulica Karmelicka 179, 31-128 Kraków</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>ulica Święty Marcin 179, 61-806 Poznań</t>
+          <t>ulica Karmelicka 179, 31-128 Kraków</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>05/09/2017</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -4745,7 +4745,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Optima Trade S. A.</t>
+          <t>Zielony Wektor S. A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Głogowska 16, 60-734 Poznań</t>
+          <t>os. Na Stoku 16, 31-704 Kraków</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Głogowska 16, 60-734 Poznań</t>
+          <t>os. Na Stoku 16, 31-704 Kraków</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2025/30/04</t>
+          <t>2018/12/10</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -4807,7 +4807,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka Akcyjna</t>
+          <t>Zielony Zefir Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ul. Długa 33/89, 80-831 Gdańsk</t>
+          <t>ul. Krupówki 33/89, 34-500 Zakopane</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ul. Długa 33/89, 80-831 Gdańsk</t>
+          <t>ul. Krupówki 33/89, 34-500 Zakopane</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>28-10-2019</t>
+          <t>19-11-2019</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -4869,7 +4869,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o.o.</t>
+          <t>Zielony Żubr sp. z o.o.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>ul Grunwaldzka 50, 80-236 Gdańsk</t>
+          <t>50, 34-600 Mordarka</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ul Grunwaldzka 50, 80-236 Gdańsk</t>
+          <t>50, 34-600 Mordarka</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2023-28-11</t>
+          <t>2020-26-12</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -4931,7 +4931,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Silesia Invest sp z oo</t>
+          <t>Zielony Sokół sp z oo</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>ulica Jagiellońska 67, 70-435 Szczecin</t>
+          <t>ulica Galicyjska 67, 32-087 Zielonki</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>ulica Jagiellońska 67, 70-435 Szczecin</t>
+          <t>ulica Galicyjska 67, 32-087 Zielonki</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>20240118</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -4993,7 +4993,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o. o.</t>
+          <t>Zielony Orzeł sp. z o. o.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Wyszyńskiego 84, 70-200 Szczecin</t>
+          <t>84, 32-003 Podłęże</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Wyszyńskiego 84, 70-200 Szczecin</t>
+          <t>84, 32-003 Podłęże</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>21/06/2018</t>
+          <t>12/02/2022</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ul. Mariacka 101/51, 40-014 Katowice</t>
+          <t>ul. Wałowa 101/51, 33-100 Tarnów</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>ul. Mariacka 101/51, 40-014 Katowice</t>
+          <t>ul. Wałowa 101/51, 33-100 Tarnów</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2022/03/09</t>
+          <t>2023/19/03</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5117,22 +5117,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SP Z O O</t>
+          <t>Zielony Barycz SP Z O O</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2241219858</t>
+          <t>1241219858</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>241457425</t>
+          <t>251378267</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5147,12 +5147,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ul Warszawska 118, 40-009 Katowice</t>
+          <t>ul Narutowicza 118, 90-135 Łódź</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>ul Warszawska 118, 40-009 Katowice</t>
+          <t>ul Narutowicza 118, 90-135 Łódź</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>25-06-2025</t>
+          <t>26-04-2024</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5179,7 +5179,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Helios Markets spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Noteć spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5209,39 +5209,39 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
+          <t>ulica os. Retkinia 135, 94-004 Łódź</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ulica os. Retkinia 135, 94-004 Łódź</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>26 2399 6551 2838 7620 3194 9893</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
           <t/>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>ulica Krakowskie Przedmieście 135, 20-002 Lublin</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>26 2399 6551 2838 7620 3194 9893</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>2018-19-10</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>2025-26-10</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Pilica Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chełmińska 92, 87-100</t>
+          <t>Piastowska 92, 48-300</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Chełmińska 92, 87-100</t>
+          <t>Piastowska 92, 48-300</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>20151230</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5303,7 +5303,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Nova Data S.A.</t>
+          <t>Zielony Narew S.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ul. Lipowa 169/13, 15-424 Białystok</t>
+          <t>ul. Długa 169/13, 95-100 Zgierz</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>ul. Lipowa 169/13, 15-424 Białystok</t>
+          <t>ul. Długa 169/13, 95-100 Zgierz</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>23/04/2023</t>
+          <t>19/07/2015</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5365,7 +5365,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Optima Trade SA</t>
+          <t>Zielony Jodełka SA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5395,12 +5395,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 6, 15-092 Białystok</t>
+          <t>ul Rynek 6, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 6, 15-092 Białystok</t>
+          <t>ul Rynek 6, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2020/15/04</t>
+          <t>2016/26/08</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5427,7 +5427,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Polaris Capital S. A.</t>
+          <t>Zielony Kaktus S. A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ulica Gdańska 23, 85-005 Bydgoszcz</t>
+          <t>ulica Jedności Narodowej 23, 50-260 Wrocław</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>ulica Gdańska 23, 85-005 Bydgoszcz</t>
+          <t>ulica Jedności Narodowej 23, 50-260 Wrocław</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>10-07-2023</t>
+          <t>05-09-2017</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5489,7 +5489,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka Akcyjna</t>
+          <t>Zielony Szmaragd Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>os. Dworcowa 40, 85-009 Bydgoszcz</t>
+          <t>os. Konstytucji 3 Maja 40, 58-540 Karpacz</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>os. Dworcowa 40, 85-009 Bydgoszcz</t>
+          <t>os. Konstytucji 3 Maja 40, 58-540 Karpacz</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5539,19 +5539,19 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2021-17-05</t>
+          <t>2018-12-10</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2018-05-03</t>
+          <t>2018-03-05</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Zielony Topaz sp. z o.o.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>242090949</t>
+          <t>251932597</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>ul. Szeroka 57/65, 87-100 Toruń</t>
+          <t>ul. Odrodzenia 57/65, 59-300 Lubin</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>ul. Szeroka 57/65, 87-100 Toruń</t>
+          <t>ul. Odrodzenia 57/65, 59-300 Lubin</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>20240628</t>
+          <t>20191119</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5613,7 +5613,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Zielony Granit sp z oo</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>242090949</t>
+          <t>252011787</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ul Chełmińska 74, 87-100 Toruń</t>
+          <t>ul Słowackiego 74, 58-300 Wałbrzych</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>ul Chełmińska 74, 87-100 Toruń</t>
+          <t>ul Słowackiego 74, 58-300 Wałbrzych</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>30/09/2024</t>
+          <t>26/12/2020</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5675,7 +5675,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Astra Finance sp. z o. o.</t>
+          <t>Zielony Marmur sp. z o. o.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 91, 35-030 Rzeszów</t>
+          <t>ulica Półwiejska 91, 61-888 Poznań</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 91, 35-030 Rzeszów</t>
+          <t>ulica Półwiejska 91, 61-888 Poznań</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2019/03/09</t>
+          <t>2021/05/01</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5737,7 +5737,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Sp. z o.o.</t>
+          <t>Zielony Syrena Sp. z o.o.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Piłsudskiego 108, 35-074 Rzeszów</t>
+          <t>os. Bolesława Chrobrego 108, 60-681 Poznań</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Piłsudskiego 108, 35-074 Rzeszów</t>
+          <t>os. Bolesława Chrobrego 108, 60-681 Poznań</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>24-04-2019</t>
+          <t>12-02-2022</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5799,7 +5799,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Helios Markets SP Z O O</t>
+          <t>Zielony Zodiak SP Z O O</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 125/27, 25-007 Kielce</t>
+          <t>ul. Główny Rynek 125/27, 62-800 Kalisz</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 125/27, 25-007 Kielce</t>
+          <t>ul. Główny Rynek 125/27, 62-800 Kalisz</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5849,19 +5849,19 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2018-20-12</t>
+          <t>2023-19-03</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2023-08-12</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Lumen Advisory spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Olimp spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>ul Warszawska 142, 25-512 Kielce</t>
+          <t>ul Kaliska 142, 63-400 Ostrów Wielkopolski</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>ul Warszawska 142, 25-512 Kielce</t>
+          <t>ul Kaliska 142, 63-400 Ostrów Wielkopolski</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>20240211</t>
+          <t>20240426</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -5923,7 +5923,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Nova Data Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Zorza Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 159, 10-504 Olsztyn</t>
+          <t>ulica Ogarna 159, 80-826 Gdańsk</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 159, 10-504 Olsztyn</t>
+          <t>ulica Ogarna 159, 80-826 Gdańsk</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>01/06/2019</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -5985,22 +5985,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Optima Trade S.A.</t>
+          <t>Zielony Krokus S.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1242407705</t>
+          <t>1252328545</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>242566085</t>
+          <t>252486929</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dąbrowszczaków 176, 10-540 Olsztyn</t>
+          <t>os. Jasień 176, 80-180 Gdańsk</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Dąbrowszczaków 176, 10-540 Olsztyn</t>
+          <t>os. Jasień 176, 80-180 Gdańsk</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2015/16/02</t>
+          <t>2026/12/06</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6047,7 +6047,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Polaris Capital SA</t>
+          <t>Zielony Narcyz SA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6077,12 +6077,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>ul. Krakowska 13/79, 45-018 Opole</t>
+          <t>ul. Bohaterów Monte Cassino 13/79, 81-759 Sopot</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>ul. Krakowska 13/79, 45-018 Opole</t>
+          <t>ul. Bohaterów Monte Cassino 13/79, 81-759 Sopot</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>18-10-2019</t>
+          <t>19-07-2015</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6109,7 +6109,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Quantum Services S. A.</t>
+          <t>Zielony Giewont S. A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>ul Ozimska 30, 45-057 Opole</t>
+          <t>30, 80-209 Chwaszczyno</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>ul Ozimska 30, 45-057 Opole</t>
+          <t>30, 80-209 Chwaszczyno</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2016-26-08</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6171,7 +6171,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka Akcyjna</t>
+          <t>Zielony Rysy Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ulica Bohaterów Westerplatte 47, 65-034 Zielona Góra</t>
+          <t>ulica 3 Maja 47, 40-096 Katowice</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>ulica Bohaterów Westerplatte 47, 65-034 Zielona Góra</t>
+          <t>ulica 3 Maja 47, 40-096 Katowice</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>20170404</t>
+          <t>20170905</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6233,7 +6233,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o.o.</t>
+          <t>Zielony Kasprowy sp. z o.o.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Kupiecka 64, 65-058 Zielona Góra</t>
+          <t>os. Paderewskiego 64, 40-282 Katowice</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Kupiecka 64, 65-058 Zielona Góra</t>
+          <t>os. Paderewskiego 64, 40-282 Katowice</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>09/02/2016</t>
+          <t>12/10/2018</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6295,7 +6295,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PPHU Astra Finance</t>
+          <t>PPHU Zielony Beskid</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6325,12 +6325,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>ul. Świętojańska 81/41, 81-372 Gdynia</t>
+          <t>ul. Zwycięstwa 81/41, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>ul. Świętojańska 81/41, 81-372 Gdynia</t>
+          <t>ul. Zwycięstwa 81/41, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2018/01/02</t>
+          <t>2019/19/11</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6357,7 +6357,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o. o.</t>
+          <t>Zielony Bieszczady sp. z o. o.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6387,12 +6387,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 38</t>
+          <t>ul Krupówki 38</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 38</t>
+          <t>ul Krupówki 38</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>22-01-2016</t>
+          <t>26-12-2020</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6419,7 +6419,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Helios Markets Sp. z o.o.</t>
+          <t>Zielony Karpaty Sp. z o.o.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>ulica Bolesława Prusa 115, 05-800 Pruszków</t>
+          <t>ulica Najświętszej Maryi Panny 115, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>ulica Bolesława Prusa 115, 05-800 Pruszków</t>
+          <t>ulica Najświętszej Maryi Panny 115, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6469,19 +6469,19 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2021-24-09</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-05-12</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Lumen Advisory SP Z O O</t>
+          <t>Zielony Bałtyk SP Z O O</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Kościuszki 132, 05-500 Piaseczno</t>
+          <t>11 Listopada 132, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Kościuszki 132, 05-500 Piaseczno</t>
+          <t>11 Listopada 132, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>20170529</t>
+          <t>20220212</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6543,7 +6543,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Nova Data spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Sudety spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6573,12 +6573,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 149/3, 32-020 Wieliczka</t>
+          <t>149/3, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 149/3, 32-020 Wieliczka</t>
+          <t>149/3, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>13/07/2020</t>
+          <t>19/03/2023</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6605,7 +6605,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Amber Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6635,12 +6635,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>ul Dąbrowskiego 166, 32-600 Oświęcim</t>
+          <t>ul Franciszkańska 166, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>ul Dąbrowskiego 166, 32-600 Oświęcim</t>
+          <t>ul Franciszkańska 166, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2024/28/07</t>
+          <t>2024/26/04</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -6667,7 +6667,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Polaris Capital S.A.</t>
+          <t>Niebieski Bizon S.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t/>
+          <t>243357981</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>ulica Rynek 3, 38-400 Krosno</t>
+          <t>ulica Kościuszki 3, 38-500 Sanok</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>ulica Rynek 3, 38-400 Krosno</t>
+          <t>ulica Kościuszki 3, 38-500 Sanok</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>19-04-2015</t>
+          <t>05-05-2025</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -6729,7 +6729,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Quantum Services SA</t>
+          <t>Niebieski Canoyn SA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Cyzn</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Mickiewicza 20, 39-300 Mielec</t>
+          <t>Suraska 20, 15-422 Białystok</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Mickiewicza 20, 39-300 Mielec</t>
+          <t>Suraska 20, 15-422 Białystok</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6779,19 +6779,19 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Silesia Invest S. A.</t>
+          <t>Niebieski Delfin S. A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>343516362</t>
+          <t>243516362</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>ul. Długa 37/55, 58-100 Świdnica</t>
+          <t>37/55, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>ul. Długa 37/55, 58-100 Świdnica</t>
+          <t>37/55, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>20201011</t>
+          <t>20150719</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -6853,17 +6853,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Vistula Fintech Spółka Akcyjna</t>
+          <t>Niebieski Echo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1243516365</t>
+          <t>1253437207</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>ul Wojska Polskiego 54, 57-300 Kłodzko</t>
+          <t>ul 3 Maja 54, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>ul Wojska Polskiego 54, 57-300 Kłodzko</t>
+          <t>ul 3 Maja 54, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>09/04/2018</t>
+          <t>26/08/2016</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -6915,7 +6915,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Astra Finance sp. z o.o.</t>
+          <t>Niebieski Falcon sp. z o.o.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>ulica Chrobrego 71, 62-200 Gniezno</t>
+          <t>ulica os. LSM 71, 20-400 Lublin</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>ulica Chrobrego 71, 62-200 Gniezno</t>
+          <t>ulica os. LSM 71, 20-400 Lublin</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2023/26/11</t>
+          <t>2017/05/09</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -6977,7 +6977,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp z oo</t>
+          <t>Niebieski Gryf sp z oo</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Słowiańska 88, 64-100 Leszno</t>
+          <t>88, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Słowiańska 88, 64-100 Leszno</t>
+          <t>88, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>03-10-2015</t>
+          <t>12-10-2018</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7039,17 +7039,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o. o.</t>
+          <t>Niebieski Horyzont sp. z o. o.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1243753935</t>
+          <t>1253674775</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>105/17, 83-110 Tczew</t>
+          <t>ul. Brzeska 105/17, 21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>105/17, 83-110 Tczew</t>
+          <t>ul. Brzeska 105/17, 21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7089,19 +7089,19 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2017-25-04</t>
+          <t>2019-19-11</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2019-12-04</t>
+          <t>2019-04-12</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Lumen Advisory Sp. z o.o.</t>
+          <t>Niebieski Ikar Sp. z o.o.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7131,12 +7131,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>ul Sobieskiego 122, 84-200 Wejherowo</t>
+          <t>ul Rynek Staromiejski 122, 87-100 Toruń</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>ul Sobieskiego 122, 84-200 Wejherowo</t>
+          <t>ul Rynek Staromiejski 122, 87-100 Toruń</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>20170319</t>
+          <t>20201226</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Nova Data SP Z O O</t>
+          <t>Niebieski Jantar SP Z O O</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>ulica Głęboka 139, 43-400 Cieszyn</t>
+          <t>ulica Mostowa 139, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>ulica Głęboka 139, 43-400 Cieszyn</t>
+          <t>ulica Mostowa 139, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>03/03/2017</t>
+          <t>05/01/2021</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7225,7 +7225,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Optima Trade spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Koral spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7255,12 +7255,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Małachowskiego 156, 42-500 Będzin</t>
+          <t>Stare Miasto 156, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Małachowskiego 156, 42-500 Będzin</t>
+          <t>Stare Miasto 156, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2023/26/05</t>
+          <t>2022/12/02</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7287,7 +7287,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Lotos Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7312,17 +7312,17 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>000001126</t>
+          <t>0000011260</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>os. Królowej Jadwigi 173/69, 88-100 Inowrocław</t>
+          <t>os. Warszawska 173/69, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>os. Królowej Jadwigi 173/69, 88-100 Inowrocław</t>
+          <t>os. Warszawska 173/69, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>17-07-2019</t>
+          <t>19-03-2023</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7349,7 +7349,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Quantum Services S.A.</t>
+          <t>Niebieski Magnolia S.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>ul Wybickiego 10, 86-300 Grudziądz</t>
+          <t>ul Wojska Polskiego 10, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>ul Wybickiego 10, 86-300 Grudziądz</t>
+          <t>ul Wojska Polskiego 10, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2015-14-06</t>
+          <t>2024-26-04</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7411,7 +7411,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Silesia Invest SA</t>
+          <t>Niebieski Neon SA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>20211027</t>
+          <t>20250505</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7473,7 +7473,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Vistula Fintech S. A.</t>
+          <t>Niebieski Oaza S. A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7483,12 +7483,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>244387458</t>
+          <t/>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Długa 164, Brzeg</t>
+          <t>Ogarna 164, Gdańsk</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Długa 164, Brzeg</t>
+          <t>Ogarna 164, Gdańsk</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>21/03/2023</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>ul. Lubelska 61/31, 24-100 Puławy</t>
+          <t>ul. Byczyńska 61/31, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>ul. Lubelska 61/31, 24-100 Puławy</t>
+          <t>ul. Byczyńska 61/31, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2021/06/01</t>
+          <t>2015/19/07</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7597,7 +7597,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o.o.</t>
+          <t>Niebieski Rubin sp. z o.o.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>ul Staszica 78, 22-400 Zamość</t>
+          <t>ul Chrobrego 78, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>ul Staszica 78, 22-400 Zamość</t>
+          <t>ul Chrobrego 78, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>12-07-2021</t>
+          <t>26-08-2016</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -7659,7 +7659,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Helios Markets sp z oo</t>
+          <t>Niebieski Szafir sp z oo</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 95, 16-300 Augustów</t>
+          <t>ulica 30 Stycznia 95, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 95, 16-300 Augustów</t>
+          <t>ulica 30 Stycznia 95, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2018-06-12</t>
+          <t>2017-05-09</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -7721,7 +7721,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o. o.</t>
+          <t>Niebieski Tytan sp. z o. o.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>244783409</t>
+          <t>254704247</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Kościuszki 112, 16-400 Suwałki</t>
+          <t>Paderewskiego 112, 25-004 Kielce</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Kościuszki 112, 16-400 Suwałki</t>
+          <t>Paderewskiego 112, 25-004 Kielce</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>20191009</t>
+          <t>20181012</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -7783,7 +7783,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Nova Data Sp. z o.o.</t>
+          <t>Niebieski Uran Sp. z o.o.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>ul. Piastowska 129/83, 48-300 Nysa</t>
+          <t>ul. 1 Maja 129/83, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>ul. Piastowska 129/83, 48-300 Nysa</t>
+          <t>ul. 1 Maja 129/83, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>28/05/2015</t>
+          <t>19/11/2019</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -7845,7 +7845,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Optima Trade SP Z O O</t>
+          <t>Niebieski Wektor SP Z O O</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -7875,12 +7875,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>ul Długa 146, 49-300 Brzeg</t>
+          <t>ul Marszałkowska 146, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>ul Długa 146, 49-300 Brzeg</t>
+          <t>ul Marszałkowska 146, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2022/21/08</t>
+          <t>2020/26/12</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -7907,7 +7907,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Polaris Capital spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Zefir spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>163, 68-200 Żary</t>
+          <t>ulica Krakowskie Przedmieście 163, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>163, 68-200 Żary</t>
+          <t>ulica Krakowskie Przedmieście 163, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>28-10-2019</t>
+          <t>05-01-2021</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -7969,7 +7969,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Żubr Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>05090780855</t>
+          <t>95090780855</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7999,12 +7999,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sikorskiego 180, 66-200 Świebodzin</t>
+          <t>Floriańska 180, 31-019 Kraków</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Sikorskiego 180, 66-200 Świebodzin</t>
+          <t>Floriańska 180, 31-019 Kraków</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8019,19 +8019,19 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2020-31-05</t>
+          <t>2022-12-02</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
+          <t>2022-07-05</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Silesia Invest S.A.</t>
+          <t>Niebieski Sokół S.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>96101482207</t>
+          <t>06101482207</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>ul. Armii Krajowej 17/45, 78-100 Kołobrzeg</t>
+          <t>ul. Długa 17/45, 31-147 Kraków</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>ul. Armii Krajowej 17/45, 78-100 Kołobrzeg</t>
+          <t>ul. Długa 17/45, 31-147 Kraków</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>20200825</t>
+          <t>20230319</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8093,7 +8093,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Vistula Fintech SA</t>
+          <t>Niebieski Orzeł SA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8123,12 +8123,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 34, 73-110 Stargard</t>
+          <t>ul Piotrkowska 34, 90-102 Łódź</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 34, 73-110 Stargard</t>
+          <t>ul Piotrkowska 34, 90-102 Łódź</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>25/02/2021</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8155,22 +8155,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Astra Finance S. A.</t>
+          <t>Niebieski Kormoran S. A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2245100166</t>
+          <t>1245100166</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>245337735</t>
+          <t>255258577</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8185,12 +8185,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>ulica Mickiewicza 51, 27-600 Sandomierz</t>
+          <t>ulica Zachodnia 51, 90-402 Łódź</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>ulica Mickiewicza 51, 27-600 Sandomierz</t>
+          <t>ulica Zachodnia 51, 90-402 Łódź</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2022/06/03</t>
+          <t>2025/05/05</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8217,7 +8217,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka Akcyjna</t>
+          <t>Niebieski Barycz Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sienkiewicza 68, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>Świdnicka 68, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Sienkiewicza 68, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>Świdnicka 68, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>25-04-2018</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8279,7 +8279,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o.o.</t>
+          <t>Niebieski Noteć sp. z o.o.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>ul. Marszałkowska 85/7, 00-590 Warszawa</t>
+          <t>ul. Legnicka 85/7, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>ul. Marszałkowska 85/7, 00-590 Warszawa</t>
+          <t>ul. Legnicka 85/7, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2021-01-05</t>
+          <t>2015-19-07</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8341,7 +8341,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp z oo</t>
+          <t>Niebieski Pilica sp z oo</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>245575305</t>
+          <t>255496147</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 102, 00-071 Warszawa</t>
+          <t>ul Święty Marcin 102, 61-806 Poznań</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 102, 00-071 Warszawa</t>
+          <t>ul Święty Marcin 102, 61-806 Poznań</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>20201015</t>
+          <t>20160826</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8403,7 +8403,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o. o.</t>
+          <t>Niebieski Narew sp. z o. o.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>ulica Floriańska 119, 31-019 Kraków</t>
+          <t>ulica Głogowska 119, 60-734 Poznań</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>ulica Floriańska 119, 31-019 Kraków</t>
+          <t>ulica Głogowska 119, 60-734 Poznań</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>06/05/2024</t>
+          <t>05/09/2017</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8465,7 +8465,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Optima Trade Sp. z o.o.</t>
+          <t>Niebieski Jodełka Sp. z o.o.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Długa 136, 31-147 Kraków</t>
+          <t>Długa 136, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Długa 136, 31-147 Kraków</t>
+          <t>Długa 136, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2019/16/06</t>
+          <t>2018/12/10</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8527,7 +8527,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Polaris Capital SP Z O O</t>
+          <t>Niebieski Kaktus SP Z O O</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8557,12 +8557,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>ul. Piotrkowska 153/59, 90-102 Łódź</t>
+          <t>ul. Grunwaldzka 153/59, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>ul. Piotrkowska 153/59, 90-102 Łódź</t>
+          <t>ul. Grunwaldzka 153/59, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>16-02-2016</t>
+          <t>19-11-2019</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8589,7 +8589,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Quantum Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Szmaragd spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8599,12 +8599,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>245892069</t>
+          <t>255812909</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8619,12 +8619,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>80-236 Gdańsk</t>
+          <t>21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>80-236 Gdańsk</t>
+          <t>21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2019-04-02</t>
+          <t>2020-26-12</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -8651,7 +8651,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Topaz Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>ulica Świdnicka 7, 50-066 Wrocław</t>
+          <t>ulica Wyszyńskiego 7, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>ulica Świdnicka 7, 50-066 Wrocław</t>
+          <t>ulica Wyszyńskiego 7, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8701,7 +8701,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>20151008</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -8713,17 +8713,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Niebieski Granit S.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1245812872</t>
+          <t>2245812872</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8743,12 +8743,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Legnicka 24, 54-203 Wrocław</t>
+          <t>Mariacka 24, 40-014 Katowice</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Legnicka 24, 54-203 Wrocław</t>
+          <t>Mariacka 24, 40-014 Katowice</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>09/08/2023</t>
+          <t>12/02/2022</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -8775,7 +8775,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>P.P.H.U. Astra Finance</t>
+          <t>P.P.H.U. Niebieski Marmur</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>ul. Święty Marcin 41/21, 61-806 Poznań</t>
+          <t>ul. Warszawska 41/21, 40-009 Katowice</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>ul. Święty Marcin 41/21, 61-806 Poznań</t>
+          <t>ul. Warszawska 41/21, 40-009 Katowice</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2022/12/01</t>
+          <t>2023/19/03</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -8837,7 +8837,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S. A.</t>
+          <t>Niebieski Syrena S. A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -8867,12 +8867,12 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>ul Głogowska 58, 60-734 Poznań</t>
+          <t>ul Krakowskie Przedmieście 58, 20-002 Lublin</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>ul Głogowska 58, 60-734 Poznań</t>
+          <t>ul Krakowskie Przedmieście 58, 20-002 Lublin</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>16-10-2021</t>
+          <t>26-04-2024</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -8899,7 +8899,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka Akcyjna</t>
+          <t>Niebieski Zodiak Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8929,12 +8929,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>ulica Długa 75, 80-831 Gdańsk</t>
+          <t>ulica Narutowicza 75, 20-004 Lublin</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>ulica Długa 75, 80-831 Gdańsk</t>
+          <t>ulica Narutowicza 75, 20-004 Lublin</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2024-27-11</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -8961,7 +8961,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o.o.</t>
+          <t>Niebieski Olimp sp. z o.o.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Grunwaldzka 92, 80-236 Gdańsk</t>
+          <t>Lipowa 92, 15-424 Białystok</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Grunwaldzka 92, 80-236 Gdańsk</t>
+          <t>Lipowa 92, 15-424 Białystok</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>20220625</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9023,17 +9023,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Nova Data sp z oo</t>
+          <t>Niebieski Zorza sp z oo</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1246288019</t>
+          <t>1256208855</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>ul. Jagiellońska 109/73, 70-435 Szczecin</t>
+          <t>ul. Sienkiewicza 109/73, 15-092 Białystok</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>ul. Jagiellońska 109/73, 70-435 Szczecin</t>
+          <t>ul. Sienkiewicza 109/73, 15-092 Białystok</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>19/01/2016</t>
+          <t>19/07/2015</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9085,7 +9085,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o. o.</t>
+          <t>Niebieski Krokus sp. z o. o.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>os. Wyszyńskiego 126, 70-200 Szczecin</t>
+          <t>os. Gdańska 126, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>os. Wyszyńskiego 126, 70-200 Szczecin</t>
+          <t>os. Gdańska 126, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2024/28/01</t>
+          <t>2016/26/08</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9147,7 +9147,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Polaris Capital Sp. z o.o.</t>
+          <t>Niebieski Narcyz Sp. z o.o.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>ulica Mariacka 143, 40-014 Katowice</t>
+          <t>ulica Dworcowa 143, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>ulica Mariacka 143, 40-014 Katowice</t>
+          <t>ulica Dworcowa 143, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>16-09-2021</t>
+          <t>05-09-2017</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9209,7 +9209,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Quantum Services SP Z O O</t>
+          <t>Niebieski Giewont SP Z O O</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Warszawska 160, 40-009 Katowice</t>
+          <t>Szeroka 160, 87-100 Toruń</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Warszawska 160, 40-009 Katowice</t>
+          <t>Szeroka 160, 87-100 Toruń</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9259,19 +9259,19 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2024-23-09</t>
+          <t>2018-12-10</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2018-05-03</t>
+          <t>2018-03-05</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Silesia Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Rysy spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9301,12 +9301,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>ul. Krakowskie Przedmieście 177/35, 20-002 Lublin</t>
+          <t>ul. Chełmińska 177/35, 87-100 Toruń</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>ul. Krakowskie Przedmieście 177/35, 20-002 Lublin</t>
+          <t>ul. Chełmińska 177/35, 87-100 Toruń</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>20231019</t>
+          <t>20191119</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9333,7 +9333,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Vistula Fintech Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Kasprowy Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>ul Narutowicza 14, 20-004 Lublin</t>
+          <t>ul 3 Maja 14, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>ul Narutowicza 14, 20-004 Lublin</t>
+          <t>ul 3 Maja 14, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>07/06/2021</t>
+          <t>26/12/2020</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9395,7 +9395,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Astra Finance S.A.</t>
+          <t>Amber Budownictwo S.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>ulica Lipowa 31, 15-424 Białystok</t>
+          <t>ulica Piłsudskiego 31, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>ulica Lipowa 31, 15-424 Białystok</t>
+          <t>ulica Piłsudskiego 31, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9457,7 +9457,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SA</t>
+          <t>Amber Transport SA</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Sienkiewicza 48, 15-092 Białystok</t>
+          <t>Sienkiewicza 48, 25-007 Kielce</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Sienkiewicza 48, 15-092 Białystok</t>
+          <t>Sienkiewicza 48, 25-007 Kielce</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>25-11-2015</t>
+          <t>12-02-2022</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -9519,7 +9519,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Helios Markets S. A.</t>
+          <t>Amber Spedycja S. A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9549,12 +9549,12 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>ul. Gdańska 65/87, 85-005 Bydgoszcz</t>
+          <t>ul. Warszawska 65/87, 25-512 Kielce</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>ul. Gdańska 65/87, 85-005 Bydgoszcz</t>
+          <t>ul. Warszawska 65/87, 25-512 Kielce</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9569,19 +9569,19 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2022-29-12</t>
+          <t>2023-19-03</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
+          <t>2022-10-04</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka Akcyjna</t>
+          <t>Amber Logistyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>ul Dworcowa 82, 85-009 Bydgoszcz</t>
+          <t>ul Kościuszki 82, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>ul Dworcowa 82, 85-009 Bydgoszcz</t>
+          <t>ul Kościuszki 82, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>20220409</t>
+          <t>20240426</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -9643,7 +9643,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o.o.</t>
+          <t>Amber Handel sp. z o.o.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>ulica Szeroka 99, 87-100 Toruń</t>
+          <t>ulica Dąbrowszczaków 99, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>ulica Szeroka 99, 87-100 Toruń</t>
+          <t>ulica Dąbrowszczaków 99, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>09/01/2017</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -9705,7 +9705,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Optima Trade sp z oo</t>
+          <t>Amber Usługi sp z oo</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Chełmińska 116, 87-100 Toruń</t>
+          <t>Krakowska 116, 45-018 Opole</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Chełmińska 116, 87-100 Toruń</t>
+          <t>Krakowska 116, 45-018 Opole</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>02-08-2017 08:26:46</t>
+          <t>12-06-2026 08:26:46</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -9767,7 +9767,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o. o.</t>
+          <t>Amber Finanse sp. z o. o.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -9797,12 +9797,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 133/49, 35-030 Rzeszów</t>
+          <t>ul. Ozimska 133/49, 45-057 Opole</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 133/49, 35-030 Rzeszów</t>
+          <t>ul. Ozimska 133/49, 45-057 Opole</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>30-01-2025</t>
+          <t>19-07-2015</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -9829,7 +9829,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Quantum Serivces Sp. z o.o.</t>
+          <t>Amber Doradztwo pS. z o.o.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>nzCn</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -9859,12 +9859,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 150, 35-074 Rzeszów</t>
+          <t>ul Bohaterów Westerplatte 150, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 150, 35-074 Rzeszów</t>
+          <t>ul Bohaterów Westerplatte 150, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2018-03-09</t>
+          <t>2016-26-08</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -9891,22 +9891,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Silesia Invest SP Z O O</t>
+          <t>Amber Szkolenia SP Z O O</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1247396679</t>
+          <t>1257317517</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>347475861</t>
+          <t>247475861</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 167, 25-007 Kielce</t>
+          <t>ulica Kupiecka 167, 65-058 Zielona Góra</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 167, 25-007 Kielce</t>
+          <t>ulica Kupiecka 167, 65-058 Zielona Góra</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>20250202</t>
+          <t>20170905</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -9953,7 +9953,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Vistula Fintech spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Media spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -9983,12 +9983,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Warszawska 4, 25-512 Kielce</t>
+          <t>Świętojańska 4, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Warszawska 4, 25-512 Kielce</t>
+          <t>Świętojańska 4, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>09/12/2019</t>
+          <t>12/10/2018</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>ul. Kościuszki 21/11, 10-504 Olsztyn</t>
+          <t>ul. 10 Lutego 21/11, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>ul. Kościuszki 21/11, 10-504 Olsztyn</t>
+          <t>ul. 10 Lutego 21/11, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2024/14/08</t>
+          <t>2019/19/11</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10077,17 +10077,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Amber Marketing S.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>1247634245</t>
+          <t>1257555085</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>ul Dąbrowszczaków 38, 10-540 Olsztyn</t>
+          <t>ul Bolesława Prusa 38, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>ul Dąbrowszczaków 38, 10-540 Olsztyn</t>
+          <t>ul Bolesława Prusa 38, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>10-02-2015</t>
+          <t>26-12-2020</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10139,7 +10139,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Helios Markets SA</t>
+          <t>Amber Druk SA</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10169,12 +10169,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>ulica Krakowska 55, 45-018 Opole</t>
+          <t>ulica Kościuszki 55, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>ulica Krakowska 55, 45-018 Opole</t>
+          <t>ulica Kościuszki 55, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10201,7 +10201,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Lumen Advisory S. A.</t>
+          <t>Amber Informatyka S. A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10231,12 +10231,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Ozimska 72, 45-057 Opole</t>
+          <t>Sienkiewicza 72, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Ozimska 72, 45-057 Opole</t>
+          <t>Sienkiewicza 72, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>20200228</t>
+          <t>20220212</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10263,17 +10263,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>Amber Oprogramowanie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1247871815</t>
+          <t>1257792655</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10293,12 +10293,12 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>ul. Bohaterów Westerplatte 89/63, 65-034 Zielona Góra</t>
+          <t>ul. Dąbrowskiego 89/63, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>ul. Bohaterów Westerplatte 89/63, 65-034 Zielona Góra</t>
+          <t>ul. Dąbrowskiego 89/63, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>19/03/2023</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10325,7 +10325,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o.o.</t>
+          <t>Amber Rolnictwo sp. z o.o.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>ul Kupiecka 106, 65-058 Zielona Góra</t>
+          <t>ul Rynek 106, 38-400 Krosno</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>ul Kupiecka 106, 65-058 Zielona Góra</t>
+          <t>ul Rynek 106, 38-400 Krosno</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2017/23/11</t>
+          <t>2024/26/04</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10387,7 +10387,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Polaris Capital sp z oo</t>
+          <t>Amber Ogrodnictwo sp z oo</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>ulica Świętojańska 123, 81-372 Gdynia</t>
+          <t>ulica Mickiewicza 123, 39-300 Mielec</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>ulica Świętojańska 123, 81-372 Gdynia</t>
+          <t>ulica Mickiewicza 123, 39-300 Mielec</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>22-03-2021</t>
+          <t>05-05-2025</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -10449,7 +10449,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o. o.</t>
+          <t>Amber Produkcja sp. z o. o.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10479,12 +10479,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>10 Lutego 140, 81-364 Gdynia</t>
+          <t>Długa 140, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>10 Lutego 140, 81-364 Gdynia</t>
+          <t>Długa 140, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10499,19 +10499,19 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Silesia Invest Sp. z o.o.</t>
+          <t>Amber Przemysł Sp. z o.o.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10541,12 +10541,12 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>ul. Bolesława Prusa 157/25, 05-800 Pruszków</t>
+          <t>157/25, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>ul. Bolesława Prusa 157/25, 05-800 Pruszków</t>
+          <t>157/25, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>20160709</t>
+          <t>20150719</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -10573,7 +10573,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Vistula Fintech SP Z O O</t>
+          <t>Amber Ekologia SP Z O O</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>ul Kościuszki 174, 05-500 Piaseczno</t>
+          <t>ul Chrobrego 174, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>ul Kościuszki 174, 05-500 Piaseczno</t>
+          <t>ul Chrobrego 174, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>26/11/2023</t>
+          <t>26/08/2016</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -10635,7 +10635,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Astra Finance spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Energetyka spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10665,12 +10665,12 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 11, 32-020 Wieliczka</t>
+          <t>ulica Słowiańska 11, 64-100 Leszno</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 11, 32-020 Wieliczka</t>
+          <t>ulica Słowiańska 11, 64-100 Leszno</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2025/03/06</t>
+          <t>2017/05/09</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -10697,7 +10697,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Instalacje Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10727,12 +10727,12 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Dąbrowskiego 28, 32-600 Oświęcim</t>
+          <t>Gdańska 28, 83-110 Tczew</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Dąbrowskiego 28, 32-600 Oświęcim</t>
+          <t>Gdańska 28, 83-110 Tczew</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>03-06-2023</t>
+          <t>12-10-2018</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -10759,7 +10759,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Helios Markets S.A.</t>
+          <t>Amber Nieruchomości S.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10789,12 +10789,12 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>ul. Rynek 45/77, 38-400 Krosno</t>
+          <t>ul. Sobieskiego 45/77, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>ul. Rynek 45/77, 38-400 Krosno</t>
+          <t>ul. Sobieskiego 45/77, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10809,19 +10809,19 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2020-22-01</t>
+          <t>2019-19-11</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2019-12-04</t>
+          <t>2019-04-12</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Lumen Advisory SA</t>
+          <t>Amber Inwestycje SA</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 62, 39-300 Mielec</t>
+          <t>ul Głęboka 62, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 62, 39-300 Mielec</t>
+          <t>ul Głęboka 62, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>20190529</t>
+          <t>20201226</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -10883,7 +10883,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Nova Data S. A.</t>
+          <t>Amber Medycyna S. A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -10913,12 +10913,12 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>os. Długa 79, 58-100 Świdnica</t>
+          <t>os. Małachowskiego 79, 42-500 Będzin</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>os. Długa 79, 58-100 Świdnica</t>
+          <t>os. Małachowskiego 79, 42-500 Będzin</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>21/09/2016</t>
+          <t>05/01/2021</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -10945,7 +10945,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka Akcyjna</t>
+          <t>Amber Zdrowie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -10975,12 +10975,12 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>96, 57-300 Kłodzko</t>
+          <t>Królowej Jadwigi 96, 88-100 Inowrocław</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>96, 57-300 Kłodzko</t>
+          <t>Królowej Jadwigi 96, 88-100 Inowrocław</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2018/27/11</t>
+          <t>2022/12/02</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -11007,7 +11007,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o.o.</t>
+          <t>Amber Urody sp. z o.o.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>ul. Chrobrego 113/39, 62-200 Gniezno</t>
+          <t>ul. Wybickiego 113/39, 86-300 Grudziądz</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>ul. Chrobrego 113/39, 62-200 Gniezno</t>
+          <t>ul. Wybickiego 113/39, 86-300 Grudziądz</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>26-07-2023</t>
+          <t>19-03-2023</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11069,7 +11069,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Quantum Services sp z oo</t>
+          <t>Amber Turystyka sp z oo</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>ul Słowiańska 130, 64-100 Leszno</t>
+          <t>ul Czarnieckiego 130, 14-100 Ostróda</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>ul Słowiańska 130, 64-100 Leszno</t>
+          <t>ul Czarnieckiego 130, 14-100 Ostróda</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11119,19 +11119,19 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2018-26-10</t>
+          <t>2024-26-04</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2022-10-06</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o. o.</t>
+          <t>Amber Rozrywka sp. z o. o.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11161,12 +11161,12 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>ulica Gdańska 147, 83-110 Tczew</t>
+          <t>ulica Warszawska 147, 11-500 Giżycko</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>ulica Gdańska 147, 83-110 Tczew</t>
+          <t>ulica Warszawska 147, 11-500 Giżycko</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>20201023</t>
+          <t>20250505</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11193,22 +11193,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Vistula Fintech Sp. z o.o.</t>
+          <t>Amber Gastronomia Sp. z o.o.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2248980475</t>
+          <t>1248980475</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>249218045</t>
+          <t>259138887</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11223,12 +11223,12 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Sobieskiego 164, 84-200 Wejherowo</t>
+          <t>Lubelska 164, 24-100 Puławy</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Sobieskiego 164, 84-200 Wejherowo</t>
+          <t>Lubelska 164, 24-100 Puławy</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>25/12/2016</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11255,7 +11255,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PPHU Astra Finance</t>
+          <t>PPHU Amber Moda</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>ul. Głęboka 1/1, 43-400 Cieszyn</t>
+          <t>ul. Staszica 1/1, 22-400 Zamość</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>ul. Głęboka 1/1, 43-400 Cieszyn</t>
+          <t>ul. Staszica 1/1, 22-400 Zamość</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2022/29/07</t>
+          <t>2015/19/07</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11317,7 +11317,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Baltic Med Supply spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Tekstylia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11347,12 +11347,12 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>ul Małachowskiego 18, 42-500 Będzin</t>
+          <t>ul 3 Maja 18, 16-300 Augustów</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>ul Małachowskiego 18, 42-500 Będzin</t>
+          <t>ul 3 Maja 18, 16-300 Augustów</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>08-05-2019</t>
+          <t>26-08-2016</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11379,7 +11379,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Motoryzacja Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11389,12 +11389,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>249455615</t>
+          <t>259376457</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11409,12 +11409,12 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>ulica Królowej Jadwigi 35, 88-100 Inowrocław</t>
+          <t>ulica Kościuszki 35, 16-400 Suwałki</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>ulica Królowej Jadwigi 35, 88-100 Inowrocław</t>
+          <t>ulica Kościuszki 35, 16-400 Suwałki</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2017-29-04</t>
+          <t>2017-05-09</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -11441,7 +11441,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Lumen Advisory S.A.</t>
+          <t>Amber Ubezpieczenia S.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11471,12 +11471,12 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>os. Kościuszki 172, 16-400</t>
+          <t>os. Kupiecka 172, 65-058</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>os. Kościuszki 172, 16-400</t>
+          <t>os. Kupiecka 172, 65-058</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11491,19 +11491,19 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>20161011</t>
+          <t>20181012</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>20180305</t>
+          <t>20180503</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Nova Data SA</t>
+          <t>Amber Spawalnictwo SA</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>ul. Czarnieckiego 69/53, 14-100 Ostróda</t>
+          <t>ul. Długa 69/53, 49-300 Brzeg</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>ul. Czarnieckiego 69/53, 14-100 Ostróda</t>
+          <t>ul. Długa 69/53, 49-300 Brzeg</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>28/08/2025</t>
+          <t>19/11/2019</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -11565,7 +11565,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Optima Trade S. A.</t>
+          <t>Amber Ślusarstwo S. A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>ul Warszawska 86, 11-500 Giżycko</t>
+          <t>ul Rynek 86, 68-200 Żary</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>ul Warszawska 86, 11-500 Giżycko</t>
+          <t>ul Rynek 86, 68-200 Żary</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>2025/12/09</t>
+          <t>2020/26/12</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -11627,7 +11627,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka Akcyjna</t>
+          <t>Amber Krawiectwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11657,12 +11657,12 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>ulica Lubelska 103, 24-100 Puławy</t>
+          <t>ulica Sikorskiego 103, 66-200 Świebodzin</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>ulica Lubelska 103, 24-100 Puławy</t>
+          <t>ulica Sikorskiego 103, 66-200 Świebodzin</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>26-08-2019</t>
+          <t>05-01-2021</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -11689,7 +11689,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o.o.</t>
+          <t>Amber Ochrona sp. z o.o.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Staszica 120, 22-400 Zamość</t>
+          <t>Armii Krajowej 120, 78-100 Kołobrzeg</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Staszica 120, 22-400 Zamość</t>
+          <t>Armii Krajowej 120, 78-100 Kołobrzeg</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -11739,19 +11739,19 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2022-03-08</t>
+          <t>2022-12-02</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
+          <t>2022-07-05</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Silesia Invest sp z oo</t>
+          <t>Amber Catering sp z oo</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 137/15, 16-300 Augustów</t>
+          <t>ul. Piłsudskiego 137/15, 73-110 Stargard</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 137/15, 16-300 Augustów</t>
+          <t>ul. Piłsudskiego 137/15, 73-110 Stargard</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>20170524</t>
+          <t>20230319</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -11813,7 +11813,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o. o.</t>
+          <t>Amber Księgowość sp. z o. o.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>250009941</t>
+          <t>259930787</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11843,12 +11843,12 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>ul Kościuszki 154, 16-400 Suwałki</t>
+          <t>154, 27-600 Sandomierz</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>ul Kościuszki 154, 16-400 Suwałki</t>
+          <t>154, 27-600 Sandomierz</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>02/10/2016</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -11875,7 +11875,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Astra Finance Sp. z o.o.</t>
+          <t>Bizon Budownictwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -11905,12 +11905,12 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>ulica Piastowska 171, 48-300 Nysa</t>
+          <t>ulica Sienkiewicza 171, 27-400 Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>ulica Piastowska 171, 48-300 Nysa</t>
+          <t>ulica Sienkiewicza 171, 27-400 Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2017/08/08</t>
+          <t>2025/05/05</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -11937,7 +11937,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SP Z O O</t>
+          <t>Bizon Transport SP Z O O</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Długa 8, 49-300 Brzeg</t>
+          <t>Chmielna 8, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Długa 8, 49-300 Brzeg</t>
+          <t>Chmielna 8, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>25-02-2017</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -11999,7 +11999,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Helios Markets spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Spedycja spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -12029,12 +12029,12 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>ul. Rynek 25/67, 68-200 Żary</t>
+          <t>ul. Nowy Świat 25/67, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>ul. Rynek 25/67, 68-200 Żary</t>
+          <t>ul. Nowy Świat 25/67, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2020-10-10</t>
+          <t>2015-19-07</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -12061,7 +12061,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Logistyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -12091,12 +12091,12 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>ul Sikorskiego 42, 66-200 Świebodzin</t>
+          <t>ul os. Przyjaźń 42, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>ul Sikorskiego 42, 66-200 Świebodzin</t>
+          <t>ul os. Przyjaźń 42, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>20200318</t>
+          <t>20160826</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -12123,7 +12123,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Nova Data S.A.</t>
+          <t>Bizon Handel S.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -12153,12 +12153,12 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>ulica Armii Krajowej 59, 78-100 Kołobrzeg</t>
+          <t>ulica Jagiellońska 59, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>ulica Armii Krajowej 59, 78-100 Kołobrzeg</t>
+          <t>ulica Jagiellońska 59, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>09/03/2017</t>
+          <t>05/09/2017</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -12185,7 +12185,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Optima Trade SA</t>
+          <t>Bizon Usługi SA</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12215,12 +12215,12 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Piłsudskiego 76, 73-110 Stargard</t>
+          <t>Piłsudskiego 76, 05-270 Marki</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Piłsudskiego 76, 73-110 Stargard</t>
+          <t>Piłsudskiego 76, 05-270 Marki</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2025/17/11</t>
+          <t>2018/12/10</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -12247,7 +12247,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Polaris Capital S. A.</t>
+          <t>Bizon Finanse S. A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>250564275</t>
+          <t>260485119</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>93/29, 27-600 Sandomierz</t>
+          <t>ul. Andriollego 93/29, 05-400 Otwock</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>93/29, 27-600 Sandomierz</t>
+          <t>ul. Andriollego 93/29, 05-400 Otwock</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>30-07-2025</t>
+          <t>19-11-2019</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -12309,7 +12309,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka Akcyjna</t>
+          <t>Bizon Doradztwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 110, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>ul Żeromskiego 110, 26-600 Radom</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 110, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>ul Żeromskiego 110, 26-600 Radom</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2021-20-07</t>
+          <t>2020-26-12</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -12371,7 +12371,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Bizon Szkolenia sp. z o.o.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 127, 00-590 Warszawa</t>
+          <t>ulica Tumska 127, 09-402 Płock</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 127, 00-590 Warszawa</t>
+          <t>ulica Tumska 127, 09-402 Płock</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>20231004</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -12433,7 +12433,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Bizon Media sp z oo</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12443,7 +12443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -12463,12 +12463,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 144, 00-071 Warszawa</t>
+          <t>Karmelicka 144, 31-128 Kraków</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 144, 00-071 Warszawa</t>
+          <t>Karmelicka 144, 31-128 Kraków</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>19/11/2020</t>
+          <t>12/02/2022</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">

--- a/data/xlsx/vat.xlsx
+++ b/data/xlsx/vat.xlsx
@@ -105,7 +105,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -145,7 +145,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2018/06/03</t>
+          <t>2015/19/07</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -157,7 +157,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp z oo</t>
+          <t>Polskie Przetwory sp z oo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -167,7 +167,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -207,7 +207,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>03-03-2023</t>
+          <t>26-08-2016</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -219,7 +219,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o. o.</t>
+          <t>Hurtownia Nabiału Mleczko sp. z o. o.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -229,7 +229,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -269,7 +269,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2024-29-12</t>
+          <t>2017-05-09</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -281,7 +281,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lumen Advisory Sp. z o.o.</t>
+          <t>Agencja Reklamowa Kreatywni Sp. z o.o.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -291,7 +291,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -331,7 +331,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20151104</t>
+          <t>20181012</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -343,7 +343,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nova Data SP Z O O</t>
+          <t>Kancelaria Prawna Sankcja SP Z O O</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -353,7 +353,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -393,7 +393,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>19/11/2019</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -405,7 +405,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Optima Trade spółka z ograniczoną odpowiedzialnością</t>
+          <t>Śląskie Zakłady Mechaniczne spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -415,7 +415,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -455,7 +455,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2024/26/02</t>
+          <t>2020/26/12</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -467,7 +467,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Fabryka Okien i Drzwi Profil Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -477,7 +477,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>30-11-2019</t>
+          <t>05-01-2021</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -529,7 +529,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Quantum Services S.A.</t>
+          <t>Przedsiębiorstwo Robót rDogowych S.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>yCnzny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -579,19 +579,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2016-17-06</t>
+          <t>2022-12-02</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2021-11-08</t>
+          <t>2021-08-11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Silesia Invest SA</t>
+          <t>Krakowskie Biuro Nieruchomości SA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>20220921</t>
+          <t>20230319</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vistula Fintech S. A.</t>
+          <t>Salon Samochodowy Auto-Hit S. A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>13/05/2021</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Astra Finance Spółka Akcyjna</t>
+          <t>Klinika Stomatologiczna Dent-Med Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2018/28/12</t>
+          <t>2025/05/05</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -777,17 +777,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o.o.</t>
+          <t>Polski Tytoń sp. z o.o.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2235676551</t>
+          <t>1235676551</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>10-02-2018</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Helios Markets sp z oo</t>
+          <t>Gdańska Stocznia Jachtowa sp z oo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2018-16-10</t>
+          <t>2015-19-07</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o. o.</t>
+          <t>Wytwórnia Makaronu Jajecznego sp. z o. o.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wykreslony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>20210324</t>
+          <t>20160826</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nova Data Sp. z o.o.</t>
+          <t>Zakłady Mięsne Tradycja Sp. z o.o.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>02/08/2015</t>
+          <t>05/09/2017</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Optima Trade SP Z O O</t>
+          <t>Spółdzielnia Mleczarska Radomsko SP Z O O</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2023/03/01</t>
+          <t>2018/12/10</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1087,7 +1087,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Polaris Capital spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kancelaria Finansowo-Księgowa Bilans spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>03-08-2015</t>
+          <t>19-11-2019</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1149,7 +1149,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zarząd Nieruchomości Komercyjnych Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Silesia Invest S.A.</t>
+          <t>Polskie Linie Oceaniczne S.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>20160313</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1273,7 +1273,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Vistula Fintech SA</t>
+          <t>Hurtownia Materiałów Budowlanych Cegiełka SA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Piłsudskiego 84, Rzeszów</t>
+          <t>Rynek 84, Opole</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Piłsudskiego 84, Rzeszów</t>
+          <t>Rynek 84, Opole</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19/07/2020</t>
+          <t>12/02/2022</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PPHU Astra Finance</t>
+          <t>PPHU Studio Projektowe Architektura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2015/13/08</t>
+          <t>2023/19/03</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1397,7 +1397,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka Akcyjna</t>
+          <t>Centrum Medycyny Pracy Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>10-11-2019</t>
+          <t>26-04-2024</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1459,7 +1459,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o.o.</t>
+          <t>Przedsiębiorstwo Energetyki Cieplnej sp. z o.o.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>236785219</t>
+          <t>246706057</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2015-22-04</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp z oo</t>
+          <t>Gospodarstwo Rolno-Ogrodnicze sp z oo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>20180517</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1583,7 +1583,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o. o.</t>
+          <t>Drukarnia Wielkoformatowa Impress sp. z o. o.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>21/03/2025</t>
+          <t>19/07/2015</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1645,7 +1645,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Optima Trade Sp. z o.o.</t>
+          <t>Klub Fitness Sylwetka Sp. z o.o.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2017/01/12</t>
+          <t>2016/26/08</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Polaris Capital SP Z O O</t>
+          <t>Polska Grupa Energetyczna SP Z O O</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>26-12-2019</t>
+          <t>05-09-2017</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -1769,7 +1769,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Quantum Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Mazowieckie Zakłady Drobiarskie spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1819,19 +1819,19 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2022-25-03</t>
+          <t>2018-12-10</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2018-05-03</t>
+          <t>2018-03-05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Hurtownia Farmaceutyczna Aptekarz Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>20150114</t>
+          <t>20191119</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -1893,7 +1893,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Kancelaria Notarialna Lex S.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>17/04/2021</t>
+          <t>26/12/2020</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -1955,7 +1955,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Astra Finance SA</t>
+          <t>Biuro Podróży Wojażer SA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2022/21/09</t>
+          <t>2021/05/01</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2017,7 +2017,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S. A.</t>
+          <t>Szkoła Języków Obcych Lingua S. A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>20-02-2024</t>
+          <t>12-02-2022</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2079,22 +2079,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka Akcyjna</t>
+          <t>Centrum Logistyczne Podlasie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1237418735</t>
+          <t>1247339575</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>237577115</t>
+          <t>247497957</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2129,19 +2129,19 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2022-19-05</t>
+          <t>2023-19-03</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2023-08-12</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o.o.</t>
+          <t>Fabryka Mebli Drewnianych Dąb sp. z o.o.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>20181213</t>
+          <t>20240426</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2203,7 +2203,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nova Data sp z oo</t>
+          <t>Polskie Sady sp z oo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>04/12/2017</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2265,17 +2265,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o. o.</t>
+          <t>Wielkopolska Hurtownia Stali sp. z o. o.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1237656305</t>
+          <t>1247577145</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2020/08/11</t>
+          <t>2026/12/06</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2327,7 +2327,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Polaris Capital Sp. z o.o.</t>
+          <t>Zakład Oczyszczania Miasta Sp. z o.o.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>237893879</t>
+          <t>247814719</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>13-01-2022</t>
+          <t>19-07-2015</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2389,7 +2389,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Quantum Services SP Z O O</t>
+          <t>Przedsiębiorstwo Wodociągów i Kanalizacji SP Z O O</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>57-300 Kłodzko</t>
+          <t>70-435 Szczecin</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>57-300 Kłodzko</t>
+          <t>70-435 Szczecin</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2021-16-09</t>
+          <t>2016-26-08</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Silesia Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Instytut Badań Rynkowych spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>20161117</t>
+          <t>20170905</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Vistula Fintech Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Agencja Ochrony Solidna Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>338052254</t>
+          <t>238052254</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>21/01/2018</t>
+          <t>12/10/2018</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>238210635</t>
+          <t>348131477</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2023/06/02</t>
+          <t>2019/19/11</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2637,7 +2637,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SA</t>
+          <t>Krajowa Izba Gospodarcza SA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>04-09-2019</t>
+          <t>26-12-2020</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2699,7 +2699,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Helios Markets S. A.</t>
+          <t>Polskie Zakłady Lotnicze S. A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2025-14-10</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2761,17 +2761,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka Akcyjna</t>
+          <t>Hurtownia Elektryczna Wat Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1238289820</t>
+          <t>1248210665</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>20250827</t>
+          <t>20220212</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2823,7 +2823,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o.o.</t>
+          <t>Centrum Ogrodnicze Zielona Oaza sp. z o.o.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>26/10/2022</t>
+          <t>19/03/2023</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -2885,7 +2885,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Optima Trade sp z oo</t>
+          <t>Piekarnia i Cukiernia Chrupiący Rogalik sp z oo</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2016/21/06</t>
+          <t>2024/26/04</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -2947,7 +2947,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o. o.</t>
+          <t>Zakład Usług Komunalnych sp. z o. o.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>04-06-2023</t>
+          <t>05-05-2025</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3009,7 +3009,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Quantum Services Sp. z o.o.</t>
+          <t>Polski Komfort Sp. z o.o.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>000000456</t>
+          <t>0000004567</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3059,19 +3059,19 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2020-18-06</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Silesia Invest SP Z O O</t>
+          <t>Kancelaria Radców Prawnych Partnerzy SP Z O O</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>72021472604</t>
+          <t>62021472604</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>20200616</t>
+          <t>20150719</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3133,17 +3133,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Vistula Fintech spółka z ograniczoną odpowiedzialnością</t>
+          <t>Centrum Dystrybucji Alkoholi spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1238764965</t>
+          <t>1248685807</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>28/06/2024</t>
+          <t>26/08/2016</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3195,7 +3195,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Astra Finance Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Przedsiębiorstwo Spedycyjne Ładunek Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2018/29/08</t>
+          <t>2017/05/09</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3257,7 +3257,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Fabryka Tekstyliów Splot S.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>22-02-2019</t>
+          <t>12-10-2018</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3319,7 +3319,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Helios Markets SA</t>
+          <t>Górnośląskie Towarzystwo Finansowe SA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3369,19 +3369,19 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2023-21-03</t>
+          <t>2019-19-11</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2019-12-04</t>
+          <t>2019-04-12</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Lumen Advisory S. A.</t>
+          <t>Krajowa Agencja Informacyjna S. A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>20181119</t>
+          <t>20201226</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3443,7 +3443,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>Polskie Jagody Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>28/05/2017</t>
+          <t>05/01/2021</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3505,7 +3505,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o.o.</t>
+          <t>Zielony Amber sp. z o.o.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2025/22/06</t>
+          <t>2022/12/02</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3567,7 +3567,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Polaris Capital sp z oo</t>
+          <t>Zielony Bizon sp z oo</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>30-01-2025</t>
+          <t>19-03-2023</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Quantmu Services sp. z o. o.</t>
+          <t>Zielony Canyon sp. z o. .</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wkyrśe</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2023-15-03</t>
+          <t>2024-26-04</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3691,7 +3691,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Silesia Invest Sp. z o.o.</t>
+          <t>Zielony Delfin Sp. z o.o.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2024-29-03 07:07</t>
+          <t>2025-05-05 07:07</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -3753,7 +3753,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Vistula Fintech SP Z O O</t>
+          <t>Zielony Echo SP Z O O</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>22/06/2022</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -3815,17 +3815,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>P.P.H.U. Astra Finance</t>
+          <t>P.P.H.U. Zielony Falcon</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2239556861</t>
+          <t>1239556861</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2024/24/12</t>
+          <t>2015/19/07</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -3877,7 +3877,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Gryf Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>11-12-2022</t>
+          <t>26-08-2016</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -3939,7 +3939,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Helios Markets S.A.</t>
+          <t>Zielony Horyzont S.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2016-28-11</t>
+          <t>2017-05-09</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4001,7 +4001,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lumen Advisory SA</t>
+          <t>Zielony Ikar SA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>20220604</t>
+          <t>20181012</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4063,7 +4063,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Nova Data S. A.</t>
+          <t>Zielony Jantar S. A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>20/02/2019</t>
+          <t>19/11/2019</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4125,7 +4125,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka Akcyjna</t>
+          <t>Zielony Koral Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2022/22/08</t>
+          <t>2020/26/12</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4187,7 +4187,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o.o.</t>
+          <t>Zielony Lotos sp. z o.o.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 43, 00-590 Warszawa</t>
+          <t>ulica Chmielna 43, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 43, 00-590 Warszawa</t>
+          <t>ulica Chmielna 43, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>10-08-2023</t>
+          <t>05-01-2021</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Quantum Services sp z oo</t>
+          <t>Zielony Magnolia sp z oo</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 60, 00-071 Warszawa</t>
+          <t>Nowy Świat 60, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 60, 00-071 Warszawa</t>
+          <t>Nowy Świat 60, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4299,19 +4299,19 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2023-25-08</t>
+          <t>2022-12-02</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
+          <t>2022-07-05</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o. o.</t>
+          <t>Zielony Neon sp. z o. o.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ul. Floriańska 77/75, 31-019 Kraków</t>
+          <t>ul. os. Przyjaźń 77/75, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>ul. Floriańska 77/75, 31-019 Kraków</t>
+          <t>ul. os. Przyjaźń 77/75, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>20201010</t>
+          <t>20230319</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4373,7 +4373,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Vistula Fintech Sp. z o.o.</t>
+          <t>Zielony Oaza Sp. z o.o.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ul Długa 94, 31-147 Kraków</t>
+          <t>ul Jagiellońska 94, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ul Długa 94, 31-147 Kraków</t>
+          <t>ul Jagiellońska 94, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>23/02/2021</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4435,7 +4435,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Astra Finance SP Z O O</t>
+          <t>Zielony Pegaz SP Z O O</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ulica Piotrkowska 111, 90-102 Łódź</t>
+          <t>ulica Piłsudskiego 111, 05-270 Marki</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ulica Piotrkowska 111, 90-102 Łódź</t>
+          <t>ulica Piłsudskiego 111, 05-270 Marki</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2021/22/01</t>
+          <t>2025/05/05</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Baltic Med Supply spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Rubin spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Zachodnia 128, 90-402 Łódź</t>
+          <t>Andriollego 128, 05-400 Otwock</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Zachodnia 128, 90-402 Łódź</t>
+          <t>Andriollego 128, 05-400 Otwock</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>23-09-2022</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4559,7 +4559,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Szafir Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4589,12 +4589,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ul. Świdnicka 145/37, 50-066 Wrocław</t>
+          <t>ul. Żeromskiego 145/37, 26-600 Radom</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>ul. Świdnicka 145/37, 50-066 Wrocław</t>
+          <t>ul. Żeromskiego 145/37, 26-600 Radom</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2016-26-04</t>
+          <t>2015-19-07</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4621,7 +4621,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Lumen Advisory S.A.</t>
+          <t>Zielony Tytan S.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ul Legnicka 162, 54-203 Wrocław</t>
+          <t>ul Tumska 162, 09-402 Płock</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>ul Legnicka 162, 54-203 Wrocław</t>
+          <t>ul Tumska 162, 09-402 Płock</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>20250114</t>
+          <t>20160826</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4683,7 +4683,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Nova Data SA</t>
+          <t>Zielony Uran SA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4693,12 +4693,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>240903093</t>
+          <t>250823937</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ulica Święty Marcin 179, 61-806 Poznań</t>
+          <t>ulica Karmelicka 179, 31-128 Kraków</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>ulica Święty Marcin 179, 61-806 Poznań</t>
+          <t>ulica Karmelicka 179, 31-128 Kraków</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>05/09/2017</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -4745,7 +4745,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Optima Trade S. A.</t>
+          <t>Zielony Wektor S. A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Głogowska 16, 60-734 Poznań</t>
+          <t>os. Na Stoku 16, 31-704 Kraków</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Głogowska 16, 60-734 Poznań</t>
+          <t>os. Na Stoku 16, 31-704 Kraków</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2025/30/04</t>
+          <t>2018/12/10</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -4807,7 +4807,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka Akcyjna</t>
+          <t>Zielony Zefir Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ul. Długa 33/89, 80-831 Gdańsk</t>
+          <t>ul. Krupówki 33/89, 34-500 Zakopane</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ul. Długa 33/89, 80-831 Gdańsk</t>
+          <t>ul. Krupówki 33/89, 34-500 Zakopane</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>28-10-2019</t>
+          <t>19-11-2019</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -4869,7 +4869,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o.o.</t>
+          <t>Zielony Żubr sp. z o.o.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>ul Grunwaldzka 50, 80-236 Gdańsk</t>
+          <t>50, 34-600 Mordarka</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ul Grunwaldzka 50, 80-236 Gdańsk</t>
+          <t>50, 34-600 Mordarka</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2023-28-11</t>
+          <t>2020-26-12</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -4931,7 +4931,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Silesia Invest sp z oo</t>
+          <t>Zielony Sokół sp z oo</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>ulica Jagiellońska 67, 70-435 Szczecin</t>
+          <t>ulica Galicyjska 67, 32-087 Zielonki</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>ulica Jagiellońska 67, 70-435 Szczecin</t>
+          <t>ulica Galicyjska 67, 32-087 Zielonki</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>20240118</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -4993,7 +4993,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o. o.</t>
+          <t>Zielony Orzeł sp. z o. o.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Wyszyńskiego 84, 70-200 Szczecin</t>
+          <t>84, 32-003 Podłęże</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Wyszyńskiego 84, 70-200 Szczecin</t>
+          <t>84, 32-003 Podłęże</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>21/06/2018</t>
+          <t>12/02/2022</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ul. Mariacka 101/51, 40-014 Katowice</t>
+          <t>ul. Wałowa 101/51, 33-100 Tarnów</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>ul. Mariacka 101/51, 40-014 Katowice</t>
+          <t>ul. Wałowa 101/51, 33-100 Tarnów</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2022/03/09</t>
+          <t>2023/19/03</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5117,7 +5117,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SP Z O O</t>
+          <t>Zielony Barycz SP Z O O</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>241457425</t>
+          <t>251378267</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5147,12 +5147,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ul Warszawska 118, 40-009 Katowice</t>
+          <t>ul Narutowicza 118, 90-135 Łódź</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>ul Warszawska 118, 40-009 Katowice</t>
+          <t>ul Narutowicza 118, 90-135 Łódź</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>25-06-2025</t>
+          <t>26-04-2024</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5179,7 +5179,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Helios Markets spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Noteć spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5209,39 +5209,39 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
+          <t>ulica os. Retkinia 135, 94-004 Łódź</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ulica os. Retkinia 135, 94-004 Łódź</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>26 2399 6551 2838 7620 3194 9893</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
           <t/>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>ulica Krakowskie Przedmieście 135, 20-002 Lublin</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>26 2399 6551 2838 7620 3194 9893</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>2018-19-10</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>2025-26-10</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Pilica Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chełmińska 92, 87-100</t>
+          <t>Piastowska 92, 48-300</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Chełmińska 92, 87-100</t>
+          <t>Piastowska 92, 48-300</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>20151230</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5303,7 +5303,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Nova Data S.A.</t>
+          <t>Zielony Narew S.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ul. Lipowa 169/13, 15-424 Białystok</t>
+          <t>ul. Długa 169/13, 95-100 Zgierz</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>ul. Lipowa 169/13, 15-424 Białystok</t>
+          <t>ul. Długa 169/13, 95-100 Zgierz</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>23/04/2023</t>
+          <t>19/07/2015</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5365,7 +5365,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Optima Trade SA</t>
+          <t>Zielony Jodełka SA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5395,12 +5395,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 6, 15-092 Białystok</t>
+          <t>ul Rynek 6, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 6, 15-092 Białystok</t>
+          <t>ul Rynek 6, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2020/15/04</t>
+          <t>2016/26/08</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5427,7 +5427,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Polaris Capital S. A.</t>
+          <t>Zielony Kaktus S. A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ulica Gdańska 23, 85-005 Bydgoszcz</t>
+          <t>ulica Jedności Narodowej 23, 50-260 Wrocław</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>ulica Gdańska 23, 85-005 Bydgoszcz</t>
+          <t>ulica Jedności Narodowej 23, 50-260 Wrocław</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>10-07-2023</t>
+          <t>05-09-2017</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5489,7 +5489,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka Akcyjna</t>
+          <t>Zielony Szmaragd Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>os. Dworcowa 40, 85-009 Bydgoszcz</t>
+          <t>os. Konstytucji 3 Maja 40, 58-540 Karpacz</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>os. Dworcowa 40, 85-009 Bydgoszcz</t>
+          <t>os. Konstytucji 3 Maja 40, 58-540 Karpacz</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5539,19 +5539,19 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2021-17-05</t>
+          <t>2018-12-10</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2018-05-03</t>
+          <t>2018-03-05</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Zielony Topaz sp. z o.o.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>242090949</t>
+          <t>251932597</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>ul. Szeroka 57/65, 87-100 Toruń</t>
+          <t>ul. Odrodzenia 57/65, 59-300 Lubin</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>ul. Szeroka 57/65, 87-100 Toruń</t>
+          <t>ul. Odrodzenia 57/65, 59-300 Lubin</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>20240628</t>
+          <t>20191119</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5613,7 +5613,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Zielony Granit sp z oo</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>342090949</t>
+          <t>252011787</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ul Chełmińska 74, 87-100 Toruń</t>
+          <t>ul Słowackiego 74, 58-300 Wałbrzych</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>ul Chełmińska 74, 87-100 Toruń</t>
+          <t>ul Słowackiego 74, 58-300 Wałbrzych</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>30/09/2024</t>
+          <t>26/12/2020</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5675,7 +5675,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Astra Finance sp. z o. o.</t>
+          <t>Zielony Marmur sp. z o. o.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 91, 35-030 Rzeszów</t>
+          <t>ulica Półwiejska 91, 61-888 Poznań</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 91, 35-030 Rzeszów</t>
+          <t>ulica Półwiejska 91, 61-888 Poznań</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2019/03/09</t>
+          <t>2021/05/01</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5737,7 +5737,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Sp. z o.o.</t>
+          <t>Zielony Syrena Sp. z o.o.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Piłsudskiego 108, 35-074 Rzeszów</t>
+          <t>os. Bolesława Chrobrego 108, 60-681 Poznań</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Piłsudskiego 108, 35-074 Rzeszów</t>
+          <t>os. Bolesława Chrobrego 108, 60-681 Poznań</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>24-04-2019</t>
+          <t>12-02-2022</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5799,7 +5799,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Helios Markets SP Z O O</t>
+          <t>Zielony Zodiak SP Z O O</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 125/27, 25-007 Kielce</t>
+          <t>ul. Główny Rynek 125/27, 62-800 Kalisz</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 125/27, 25-007 Kielce</t>
+          <t>ul. Główny Rynek 125/27, 62-800 Kalisz</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5849,19 +5849,19 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2018-20-12</t>
+          <t>2023-19-03</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2023-08-12</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Lumen Advisory spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Olimp spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>ul Warszawska 142, 25-512 Kielce</t>
+          <t>ul Kaliska 142, 63-400 Ostrów Wielkopolski</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>ul Warszawska 142, 25-512 Kielce</t>
+          <t>ul Kaliska 142, 63-400 Ostrów Wielkopolski</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>20240211</t>
+          <t>20240426</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -5923,7 +5923,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Nova Data Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Zorza Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 159, 10-504 Olsztyn</t>
+          <t>ulica Ogarna 159, 80-826 Gdańsk</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 159, 10-504 Olsztyn</t>
+          <t>ulica Ogarna 159, 80-826 Gdańsk</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>01/06/2019</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -5985,22 +5985,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Optima Trade S.A.</t>
+          <t>Zielony Krokus S.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1242407705</t>
+          <t>1252328545</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>242566085</t>
+          <t>252486929</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dąbrowszczaków 176, 10-540 Olsztyn</t>
+          <t>os. Jasień 176, 80-180 Gdańsk</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Dąbrowszczaków 176, 10-540 Olsztyn</t>
+          <t>os. Jasień 176, 80-180 Gdańsk</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2015/16/02</t>
+          <t>2026/12/06</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6047,7 +6047,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Polaris Capital SA</t>
+          <t>Zielony Narcyz SA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6077,12 +6077,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>ul. Krakowska 13/79, 45-018 Opole</t>
+          <t>ul. Bohaterów Monte Cassino 13/79, 81-759 Sopot</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>ul. Krakowska 13/79, 45-018 Opole</t>
+          <t>ul. Bohaterów Monte Cassino 13/79, 81-759 Sopot</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>18-10-2019</t>
+          <t>19-07-2015</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6109,7 +6109,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Quantum Services S. A.</t>
+          <t>Zielony Giewont S. A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6129,22 +6129,22 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>75032139753</t>
+          <t>65032139753</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>000000941</t>
+          <t>0000009417</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>ul Ozimska 30, 45-057 Opole</t>
+          <t>30, 80-209 Chwaszczyno</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>ul Ozimska 30, 45-057 Opole</t>
+          <t>30, 80-209 Chwaszczyno</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2016-26-08</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6171,7 +6171,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka Akcyjna</t>
+          <t>Zielony Rysy Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ulica Bohaterów Westerplatte 47, 65-034 Zielona Góra</t>
+          <t>ulica 3 Maja 47, 40-096 Katowice</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>ulica Bohaterów Westerplatte 47, 65-034 Zielona Góra</t>
+          <t>ulica 3 Maja 47, 40-096 Katowice</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>20170404</t>
+          <t>20170905</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6233,7 +6233,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o.o.</t>
+          <t>Zielony Kasprowy sp. z o.o.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Kupiecka 64, 65-058 Zielona Góra</t>
+          <t>os. Paderewskiego 64, 40-282 Katowice</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Kupiecka 64, 65-058 Zielona Góra</t>
+          <t>os. Paderewskiego 64, 40-282 Katowice</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>09/02/2016</t>
+          <t>12/10/2018</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6295,7 +6295,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PPHU Astra Finance</t>
+          <t>PPHU Zielony Beskid</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6325,12 +6325,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>ul. Świętojańska 81/41, 81-372 Gdynia</t>
+          <t>ul. Zwycięstwa 81/41, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>ul. Świętojańska 81/41, 81-372 Gdynia</t>
+          <t>ul. Zwycięstwa 81/41, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2018/01/02</t>
+          <t>2019/19/11</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6357,7 +6357,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o. o.</t>
+          <t>Zielony Bieszczady sp. z o. o.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6387,12 +6387,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 38</t>
+          <t>ul Krupówki 38</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 38</t>
+          <t>ul Krupówki 38</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>22-01-2016</t>
+          <t>26-12-2020</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6419,7 +6419,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Helios Markets Sp. z o.o.</t>
+          <t>Zielony Karpaty Sp. z o.o.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>ulica Bolesława Prusa 115, 05-800 Pruszków</t>
+          <t>ulica Najświętszej Maryi Panny 115, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>ulica Bolesława Prusa 115, 05-800 Pruszków</t>
+          <t>ulica Najświętszej Maryi Panny 115, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6469,19 +6469,19 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2021-24-09</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-05-12</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Lumen Advisory SP Z O O</t>
+          <t>Zielony Bałtyk SP Z O O</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Kościuszki 132, 05-500 Piaseczno</t>
+          <t>11 Listopada 132, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Kościuszki 132, 05-500 Piaseczno</t>
+          <t>11 Listopada 132, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>20170529</t>
+          <t>20220212</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6543,7 +6543,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Nova Data spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Sudety spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6573,12 +6573,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 149/3, 32-020 Wieliczka</t>
+          <t>149/3, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 149/3, 32-020 Wieliczka</t>
+          <t>149/3, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>13/07/2020</t>
+          <t>19/03/2023</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6605,7 +6605,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Amber Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6635,12 +6635,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>ul Dąbrowskiego 166, 32-600 Oświęcim</t>
+          <t>ul Franciszkańska 166, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>ul Dąbrowskiego 166, 32-600 Oświęcim</t>
+          <t>ul Franciszkańska 166, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2024/28/07</t>
+          <t>2024/26/04</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -6667,7 +6667,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Polaris Capital S.A.</t>
+          <t>Niebieski Bizon S.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t/>
+          <t>243357981</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>ulica Rynek 3, 38-400 Krosno</t>
+          <t>ulica Kościuszki 3, 38-500 Sanok</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>ulica Rynek 3, 38-400 Krosno</t>
+          <t>ulica Kościuszki 3, 38-500 Sanok</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>19-04-2015</t>
+          <t>05-05-2025</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -6729,7 +6729,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Quantum Services SA</t>
+          <t>Niebieski Canoyn SA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Cyzn</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Mickiewicza 20, 39-300 Mielec</t>
+          <t>Suraska 20, 15-422 Białystok</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Mickiewicza 20, 39-300 Mielec</t>
+          <t>Suraska 20, 15-422 Białystok</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6779,19 +6779,19 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Silesia Invest S. A.</t>
+          <t>Niebieski Delfin S. A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>ul. Długa 37/55, 58-100 Świdnica</t>
+          <t>37/55, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>ul. Długa 37/55, 58-100 Świdnica</t>
+          <t>37/55, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>20201011</t>
+          <t>20150719</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -6853,17 +6853,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Vistula Fintech Spółka Akcyjna</t>
+          <t>Niebieski Echo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2243516365</t>
+          <t>1253437207</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>ul Wojska Polskiego 54, 57-300 Kłodzko</t>
+          <t>ul 3 Maja 54, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>ul Wojska Polskiego 54, 57-300 Kłodzko</t>
+          <t>ul 3 Maja 54, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>09/04/2018</t>
+          <t>26/08/2016</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -6915,7 +6915,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Astra Finance sp. z o.o.</t>
+          <t>Niebieski Falcon sp. z o.o.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>ulica Chrobrego 71, 62-200 Gniezno</t>
+          <t>ulica os. LSM 71, 20-400 Lublin</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>ulica Chrobrego 71, 62-200 Gniezno</t>
+          <t>ulica os. LSM 71, 20-400 Lublin</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2023/26/11</t>
+          <t>2017/05/09</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -6977,7 +6977,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp z oo</t>
+          <t>Niebieski Gryf sp z oo</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Słowiańska 88, 64-100 Leszno</t>
+          <t>88, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Słowiańska 88, 64-100 Leszno</t>
+          <t>88, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>03-10-2015</t>
+          <t>12-10-2018</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7039,17 +7039,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o. o.</t>
+          <t>Niebieski Horyzont sp. z o. o.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1243753935</t>
+          <t>1253674775</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>105/17, 83-110 Tczew</t>
+          <t>ul. Brzeska 105/17, 21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>105/17, 83-110 Tczew</t>
+          <t>ul. Brzeska 105/17, 21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7089,19 +7089,19 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2017-25-04</t>
+          <t>2019-19-11</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2019-12-04</t>
+          <t>2019-04-12</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Lumen Advisory Sp. z o.o.</t>
+          <t>Niebieski Ikar Sp. z o.o.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7131,12 +7131,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>ul Sobieskiego 122, 84-200 Wejherowo</t>
+          <t>ul Rynek Staromiejski 122, 87-100 Toruń</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>ul Sobieskiego 122, 84-200 Wejherowo</t>
+          <t>ul Rynek Staromiejski 122, 87-100 Toruń</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>20170319</t>
+          <t>20201226</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Nova Data SP Z O O</t>
+          <t>Niebieski Jantar SP Z O O</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>ulica Głęboka 139, 43-400 Cieszyn</t>
+          <t>ulica Mostowa 139, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>ulica Głęboka 139, 43-400 Cieszyn</t>
+          <t>ulica Mostowa 139, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>03/03/2017</t>
+          <t>05/01/2021</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7225,7 +7225,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Optima Trade spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Koral spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7255,12 +7255,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Małachowskiego 156, 42-500 Będzin</t>
+          <t>Stare Miasto 156, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Małachowskiego 156, 42-500 Będzin</t>
+          <t>Stare Miasto 156, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2023/26/05</t>
+          <t>2022/12/02</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7287,7 +7287,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Lotos Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7317,12 +7317,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>os. Królowej Jadwigi 173/69, 88-100 Inowrocław</t>
+          <t>os. Warszawska 173/69, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>os. Królowej Jadwigi 173/69, 88-100 Inowrocław</t>
+          <t>os. Warszawska 173/69, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>17-07-2019</t>
+          <t>19-03-2023</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7349,7 +7349,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Quantum Services S.A.</t>
+          <t>Niebieski Magnolia S.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>ul Wybickiego 10, 86-300 Grudziądz</t>
+          <t>ul Wojska Polskiego 10, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>ul Wybickiego 10, 86-300 Grudziądz</t>
+          <t>ul Wojska Polskiego 10, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2015-14-06</t>
+          <t>2024-26-04</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7411,7 +7411,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Silesia Invest SA</t>
+          <t>Niebieski Neon SA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>20211027</t>
+          <t>20250505</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7473,7 +7473,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Vistula Fintech S. A.</t>
+          <t>Niebieski Oaza S. A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7483,12 +7483,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>244387458</t>
+          <t/>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Długa 164, Brzeg</t>
+          <t>Ogarna 164, Gdańsk</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Długa 164, Brzeg</t>
+          <t>Ogarna 164, Gdańsk</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>21/03/2023</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>ul. Lubelska 61/31, 24-100 Puławy</t>
+          <t>ul. Byczyńska 61/31, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>ul. Lubelska 61/31, 24-100 Puławy</t>
+          <t>ul. Byczyńska 61/31, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2021/06/01</t>
+          <t>2015/19/07</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7597,7 +7597,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o.o.</t>
+          <t>Niebieski Rubin sp. z o.o.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>ul Staszica 78, 22-400 Zamość</t>
+          <t>ul Chrobrego 78, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>ul Staszica 78, 22-400 Zamość</t>
+          <t>ul Chrobrego 78, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>12-07-2021</t>
+          <t>26-08-2016</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -7659,7 +7659,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Helios Markets sp z oo</t>
+          <t>Niebieski Szafir sp z oo</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 95, 16-300 Augustów</t>
+          <t>ulica 30 Stycznia 95, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 95, 16-300 Augustów</t>
+          <t>ulica 30 Stycznia 95, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2018-06-12</t>
+          <t>2017-05-09</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -7721,7 +7721,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o. o.</t>
+          <t>Niebieski Tytan sp. z o. o.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>244783409</t>
+          <t>254704247</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Kościuszki 112, 16-400 Suwałki</t>
+          <t>Paderewskiego 112, 25-004 Kielce</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Kościuszki 112, 16-400 Suwałki</t>
+          <t>Paderewskiego 112, 25-004 Kielce</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>20191009</t>
+          <t>20181012</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -7783,7 +7783,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Nova Data Sp. z o.o.</t>
+          <t>Niebieski Uran Sp. z o.o.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>ul. Piastowska 129/83, 48-300 Nysa</t>
+          <t>ul. 1 Maja 129/83, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>ul. Piastowska 129/83, 48-300 Nysa</t>
+          <t>ul. 1 Maja 129/83, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>28/05/2015</t>
+          <t>19/11/2019</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -7845,7 +7845,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Optima Trade SP Z O O</t>
+          <t>Niebieski Wektor SP Z O O</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -7875,12 +7875,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>ul Długa 146, 49-300 Brzeg</t>
+          <t>ul Marszałkowska 146, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>ul Długa 146, 49-300 Brzeg</t>
+          <t>ul Marszałkowska 146, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2022/21/08</t>
+          <t>2020/26/12</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -7907,7 +7907,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Polaris Capital spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Zefir spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>163, 68-200 Żary</t>
+          <t>ulica Krakowskie Przedmieście 163, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>163, 68-200 Żary</t>
+          <t>ulica Krakowskie Przedmieście 163, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>28-10-2019</t>
+          <t>05-01-2021</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -7969,7 +7969,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Żubr Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7999,12 +7999,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sikorskiego 180, 66-200 Świebodzin</t>
+          <t>Floriańska 180, 31-019 Kraków</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Sikorskiego 180, 66-200 Świebodzin</t>
+          <t>Floriańska 180, 31-019 Kraków</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8019,19 +8019,19 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2020-31-05</t>
+          <t>2022-12-02</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
+          <t>2022-07-05</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Silesia Invest S.A.</t>
+          <t>Niebieski Sokół S.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>96101482207</t>
+          <t>06101482207</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>ul. Armii Krajowej 17/45, 78-100 Kołobrzeg</t>
+          <t>ul. Długa 17/45, 31-147 Kraków</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>ul. Armii Krajowej 17/45, 78-100 Kołobrzeg</t>
+          <t>ul. Długa 17/45, 31-147 Kraków</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>20200825</t>
+          <t>20230319</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8093,7 +8093,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Vistula Fintech SA</t>
+          <t>Niebieski Orzeł SA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8123,12 +8123,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 34, 73-110 Stargard</t>
+          <t>ul Piotrkowska 34, 90-102 Łódź</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 34, 73-110 Stargard</t>
+          <t>ul Piotrkowska 34, 90-102 Łódź</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>25/02/2021</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8155,7 +8155,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Astra Finance S. A.</t>
+          <t>Niebieski Kormoran S. A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>245337735</t>
+          <t>255258577</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8185,12 +8185,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>ulica Mickiewicza 51, 27-600 Sandomierz</t>
+          <t>ulica Zachodnia 51, 90-402 Łódź</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>ulica Mickiewicza 51, 27-600 Sandomierz</t>
+          <t>ulica Zachodnia 51, 90-402 Łódź</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2022/06/03</t>
+          <t>2025/05/05</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8217,7 +8217,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka Akcyjna</t>
+          <t>Niebieski Barycz Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sienkiewicza 68, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>Świdnicka 68, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Sienkiewicza 68, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>Świdnicka 68, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>25-04-2018</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8279,7 +8279,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o.o.</t>
+          <t>Niebieski Noteć sp. z o.o.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>ul. Marszałkowska 85/7, 00-590 Warszawa</t>
+          <t>ul. Legnicka 85/7, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>ul. Marszałkowska 85/7, 00-590 Warszawa</t>
+          <t>ul. Legnicka 85/7, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2021-01-05</t>
+          <t>2015-19-07</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8341,7 +8341,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp z oo</t>
+          <t>Niebieski Pilica sp z oo</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>245575305</t>
+          <t>255496147</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 102, 00-071 Warszawa</t>
+          <t>ul Święty Marcin 102, 61-806 Poznań</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 102, 00-071 Warszawa</t>
+          <t>ul Święty Marcin 102, 61-806 Poznań</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>20201015</t>
+          <t>20160826</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8403,7 +8403,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o. o.</t>
+          <t>Niebieski Narew sp. z o. o.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>ulica Floriańska 119, 31-019 Kraków</t>
+          <t>ulica Głogowska 119, 60-734 Poznań</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>ulica Floriańska 119, 31-019 Kraków</t>
+          <t>ulica Głogowska 119, 60-734 Poznań</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>06/05/2024</t>
+          <t>05/09/2017</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8465,7 +8465,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Optima Trade Sp. z o.o.</t>
+          <t>Niebieski Jodełka Sp. z o.o.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Długa 136, 31-147 Kraków</t>
+          <t>Długa 136, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Długa 136, 31-147 Kraków</t>
+          <t>Długa 136, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2019/16/06</t>
+          <t>2018/12/10</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8527,7 +8527,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Polaris Capital SP Z O O</t>
+          <t>Niebieski Kaktus SP Z O O</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8557,12 +8557,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>ul. Piotrkowska 153/59, 90-102 Łódź</t>
+          <t>ul. Grunwaldzka 153/59, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>ul. Piotrkowska 153/59, 90-102 Łódź</t>
+          <t>ul. Grunwaldzka 153/59, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>16-02-2016</t>
+          <t>19-11-2019</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8589,7 +8589,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Quantum Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Szmaragd spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8599,12 +8599,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>245892069</t>
+          <t>255812909</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8619,12 +8619,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>80-236 Gdańsk</t>
+          <t>21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>80-236 Gdańsk</t>
+          <t>21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2019-04-02</t>
+          <t>2020-26-12</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -8651,7 +8651,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Topaz Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>ulica Świdnicka 7, 50-066 Wrocław</t>
+          <t>ulica Wyszyńskiego 7, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>ulica Świdnicka 7, 50-066 Wrocław</t>
+          <t>ulica Wyszyńskiego 7, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8701,7 +8701,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>20151008</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -8713,22 +8713,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Niebieski Granit S.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1245812872</t>
+          <t>2245812872</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>345971254</t>
+          <t>245971254</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8743,12 +8743,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Legnicka 24, 54-203 Wrocław</t>
+          <t>Mariacka 24, 40-014 Katowice</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Legnicka 24, 54-203 Wrocław</t>
+          <t>Mariacka 24, 40-014 Katowice</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>09/08/2023</t>
+          <t>12/02/2022</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -8775,7 +8775,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>P.P.H.U. Astra Finance</t>
+          <t>P.P.H.U. Niebieski Marmur</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>ul. Święty Marcin 41/21, 61-806 Poznań</t>
+          <t>ul. Warszawska 41/21, 40-009 Katowice</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>ul. Święty Marcin 41/21, 61-806 Poznań</t>
+          <t>ul. Warszawska 41/21, 40-009 Katowice</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2022/12/01</t>
+          <t>2023/19/03</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -8837,7 +8837,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S. A.</t>
+          <t>Niebieski Syrena S. A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -8867,12 +8867,12 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>ul Głogowska 58, 60-734 Poznań</t>
+          <t>ul Krakowskie Przedmieście 58, 20-002 Lublin</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>ul Głogowska 58, 60-734 Poznań</t>
+          <t>ul Krakowskie Przedmieście 58, 20-002 Lublin</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>16-10-2021</t>
+          <t>26-04-2024</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -8899,7 +8899,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka Akcyjna</t>
+          <t>Niebieski Zodiak Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8929,12 +8929,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>ulica Długa 75, 80-831 Gdańsk</t>
+          <t>ulica Narutowicza 75, 20-004 Lublin</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>ulica Długa 75, 80-831 Gdańsk</t>
+          <t>ulica Narutowicza 75, 20-004 Lublin</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2024-27-11</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -8961,7 +8961,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp. z o.o.</t>
+          <t>Niebieski Olimp sp. z o.o.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Grunwaldzka 92, 80-236 Gdańsk</t>
+          <t>Lipowa 92, 15-424 Białystok</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Grunwaldzka 92, 80-236 Gdańsk</t>
+          <t>Lipowa 92, 15-424 Białystok</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>20220625</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9023,17 +9023,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Nova Data sp z oo</t>
+          <t>Niebieski Zorza sp z oo</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1246288019</t>
+          <t>1256208855</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>ul. Jagiellońska 109/73, 70-435 Szczecin</t>
+          <t>ul. Sienkiewicza 109/73, 15-092 Białystok</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>ul. Jagiellońska 109/73, 70-435 Szczecin</t>
+          <t>ul. Sienkiewicza 109/73, 15-092 Białystok</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>19/01/2016</t>
+          <t>19/07/2015</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9085,7 +9085,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o. o.</t>
+          <t>Niebieski Krokus sp. z o. o.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>os. Wyszyńskiego 126, 70-200 Szczecin</t>
+          <t>os. Gdańska 126, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>os. Wyszyńskiego 126, 70-200 Szczecin</t>
+          <t>os. Gdańska 126, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2024/28/01</t>
+          <t>2016/26/08</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9147,7 +9147,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Polaris Capital Sp. z o.o.</t>
+          <t>Niebieski Narcyz Sp. z o.o.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>78042806868</t>
+          <t>68042806868</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>ulica Mariacka 143, 40-014 Katowice</t>
+          <t>ulica Dworcowa 143, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>ulica Mariacka 143, 40-014 Katowice</t>
+          <t>ulica Dworcowa 143, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>16-09-2021</t>
+          <t>05-09-2017</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9209,7 +9209,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Quantum Services SP Z O O</t>
+          <t>Niebieski Giewont SP Z O O</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9234,17 +9234,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>000001426</t>
+          <t>0000014267</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Warszawska 160, 40-009 Katowice</t>
+          <t>Szeroka 160, 87-100 Toruń</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Warszawska 160, 40-009 Katowice</t>
+          <t>Szeroka 160, 87-100 Toruń</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9259,19 +9259,19 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2024-23-09</t>
+          <t>2018-12-10</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2018-05-03</t>
+          <t>2018-03-05</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Silesia Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Rysy spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9301,12 +9301,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>ul. Krakowskie Przedmieście 177/35, 20-002 Lublin</t>
+          <t>ul. Chełmińska 177/35, 87-100 Toruń</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>ul. Krakowskie Przedmieście 177/35, 20-002 Lublin</t>
+          <t>ul. Chełmińska 177/35, 87-100 Toruń</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>20231019</t>
+          <t>20191119</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9333,7 +9333,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Vistula Fintech Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Kasprowy Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>ul Narutowicza 14, 20-004 Lublin</t>
+          <t>ul 3 Maja 14, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>ul Narutowicza 14, 20-004 Lublin</t>
+          <t>ul 3 Maja 14, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>07/06/2021</t>
+          <t>26/12/2020</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9395,7 +9395,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Astra Finance S.A.</t>
+          <t>Amber Budownictwo S.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>ulica Lipowa 31, 15-424 Białystok</t>
+          <t>ulica Piłsudskiego 31, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>ulica Lipowa 31, 15-424 Białystok</t>
+          <t>ulica Piłsudskiego 31, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9457,7 +9457,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SA</t>
+          <t>Amber Transport SA</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Sienkiewicza 48, 15-092 Białystok</t>
+          <t>Sienkiewicza 48, 25-007 Kielce</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Sienkiewicza 48, 15-092 Białystok</t>
+          <t>Sienkiewicza 48, 25-007 Kielce</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>25-11-2015</t>
+          <t>12-02-2022</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -9519,7 +9519,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Helios Markets S. A.</t>
+          <t>Amber Spedycja S. A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9549,12 +9549,12 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>ul. Gdańska 65/87, 85-005 Bydgoszcz</t>
+          <t>ul. Warszawska 65/87, 25-512 Kielce</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>ul. Gdańska 65/87, 85-005 Bydgoszcz</t>
+          <t>ul. Warszawska 65/87, 25-512 Kielce</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9569,19 +9569,19 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2022-29-12</t>
+          <t>2023-19-03</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2022-04-10</t>
+          <t>2022-10-04</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka Akcyjna</t>
+          <t>Amber Logistyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>ul Dworcowa 82, 85-009 Bydgoszcz</t>
+          <t>ul Kościuszki 82, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>ul Dworcowa 82, 85-009 Bydgoszcz</t>
+          <t>ul Kościuszki 82, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>20220409</t>
+          <t>20240426</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -9643,7 +9643,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Nova Data sp. z o.o.</t>
+          <t>Amber Handel sp. z o.o.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>ulica Szeroka 99, 87-100 Toruń</t>
+          <t>ulica Dąbrowszczaków 99, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>ulica Szeroka 99, 87-100 Toruń</t>
+          <t>ulica Dąbrowszczaków 99, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>09/01/2017</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -9705,7 +9705,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Optima Trade sp z oo</t>
+          <t>Amber Usługi sp z oo</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Chełmińska 116, 87-100 Toruń</t>
+          <t>Krakowska 116, 45-018 Opole</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Chełmińska 116, 87-100 Toruń</t>
+          <t>Krakowska 116, 45-018 Opole</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>02-08-2017 08:26:46</t>
+          <t>12-06-2026 08:26:46</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -9767,7 +9767,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o. o.</t>
+          <t>Amber Finanse sp. z o. o.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -9797,12 +9797,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 133/49, 35-030 Rzeszów</t>
+          <t>ul. Ozimska 133/49, 45-057 Opole</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 133/49, 35-030 Rzeszów</t>
+          <t>ul. Ozimska 133/49, 45-057 Opole</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>30-01-2025</t>
+          <t>19-07-2015</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -9829,7 +9829,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Quantum Serivces Sp. z o.o.</t>
+          <t>Amber Doradztwo pS. z o.o.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>nzCn</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -9859,12 +9859,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 150, 35-074 Rzeszów</t>
+          <t>ul Bohaterów Westerplatte 150, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 150, 35-074 Rzeszów</t>
+          <t>ul Bohaterów Westerplatte 150, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2018-03-09</t>
+          <t>2016-26-08</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -9891,17 +9891,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Silesia Invest SP Z O O</t>
+          <t>Amber Szkolenia SP Z O O</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2247396679</t>
+          <t>1257317517</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 167, 25-007 Kielce</t>
+          <t>ulica Kupiecka 167, 65-058 Zielona Góra</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 167, 25-007 Kielce</t>
+          <t>ulica Kupiecka 167, 65-058 Zielona Góra</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>20250202</t>
+          <t>20170905</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -9953,7 +9953,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Vistula Fintech spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Media spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -9983,12 +9983,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Warszawska 4, 25-512 Kielce</t>
+          <t>Świętojańska 4, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Warszawska 4, 25-512 Kielce</t>
+          <t>Świętojańska 4, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>09/12/2019</t>
+          <t>12/10/2018</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>ul. Kościuszki 21/11, 10-504 Olsztyn</t>
+          <t>ul. 10 Lutego 21/11, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>ul. Kościuszki 21/11, 10-504 Olsztyn</t>
+          <t>ul. 10 Lutego 21/11, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2024/14/08</t>
+          <t>2019/19/11</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10077,17 +10077,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Amber Marketing S.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>1247634245</t>
+          <t>1257555085</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>ul Dąbrowszczaków 38, 10-540 Olsztyn</t>
+          <t>ul Bolesława Prusa 38, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>ul Dąbrowszczaków 38, 10-540 Olsztyn</t>
+          <t>ul Bolesława Prusa 38, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>10-02-2015</t>
+          <t>26-12-2020</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10139,7 +10139,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Helios Markets SA</t>
+          <t>Amber Druk SA</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10169,12 +10169,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>ulica Krakowska 55, 45-018 Opole</t>
+          <t>ulica Kościuszki 55, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>ulica Krakowska 55, 45-018 Opole</t>
+          <t>ulica Kościuszki 55, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10201,7 +10201,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Lumen Advisory S. A.</t>
+          <t>Amber Informatyka S. A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10231,12 +10231,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Ozimska 72, 45-057 Opole</t>
+          <t>Sienkiewicza 72, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Ozimska 72, 45-057 Opole</t>
+          <t>Sienkiewicza 72, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>20200228</t>
+          <t>20220212</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10263,17 +10263,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>Amber Oprogramowanie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1247871815</t>
+          <t>1257792655</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10293,12 +10293,12 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>ul. Bohaterów Westerplatte 89/63, 65-034 Zielona Góra</t>
+          <t>ul. Dąbrowskiego 89/63, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>ul. Bohaterów Westerplatte 89/63, 65-034 Zielona Góra</t>
+          <t>ul. Dąbrowskiego 89/63, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>19/03/2023</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10325,7 +10325,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o.o.</t>
+          <t>Amber Rolnictwo sp. z o.o.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>ul Kupiecka 106, 65-058 Zielona Góra</t>
+          <t>ul Rynek 106, 38-400 Krosno</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>ul Kupiecka 106, 65-058 Zielona Góra</t>
+          <t>ul Rynek 106, 38-400 Krosno</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2017/23/11</t>
+          <t>2024/26/04</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10387,7 +10387,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Polaris Capital sp z oo</t>
+          <t>Amber Ogrodnictwo sp z oo</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10412,17 +10412,17 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>0000016110</t>
+          <t>000001611</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>ulica Świętojańska 123, 81-372 Gdynia</t>
+          <t>ulica Mickiewicza 123, 39-300 Mielec</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>ulica Świętojańska 123, 81-372 Gdynia</t>
+          <t>ulica Mickiewicza 123, 39-300 Mielec</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>22-03-2021</t>
+          <t>05-05-2025</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -10449,7 +10449,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o. o.</t>
+          <t>Amber Produkcja sp. z o. o.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10479,12 +10479,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>10 Lutego 140, 81-364 Gdynia</t>
+          <t>Długa 140, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>10 Lutego 140, 81-364 Gdynia</t>
+          <t>Długa 140, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10499,19 +10499,19 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-11-05</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Silesia Invest Sp. z o.o.</t>
+          <t>Amber Przemysł Sp. z o.o.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10541,12 +10541,12 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>ul. Bolesława Prusa 157/25, 05-800 Pruszków</t>
+          <t>157/25, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>ul. Bolesława Prusa 157/25, 05-800 Pruszków</t>
+          <t>157/25, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>20160709</t>
+          <t>20150719</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -10573,7 +10573,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Vistula Fintech SP Z O O</t>
+          <t>Amber Ekologia SP Z O O</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>ul Kościuszki 174, 05-500 Piaseczno</t>
+          <t>ul Chrobrego 174, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>ul Kościuszki 174, 05-500 Piaseczno</t>
+          <t>ul Chrobrego 174, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>26/11/2023</t>
+          <t>26/08/2016</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -10635,7 +10635,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Astra Finance spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Energetyka spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10665,12 +10665,12 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 11, 32-020 Wieliczka</t>
+          <t>ulica Słowiańska 11, 64-100 Leszno</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 11, 32-020 Wieliczka</t>
+          <t>ulica Słowiańska 11, 64-100 Leszno</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2025/03/06</t>
+          <t>2017/05/09</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -10697,7 +10697,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Instalacje Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10727,12 +10727,12 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Dąbrowskiego 28, 32-600 Oświęcim</t>
+          <t>Gdańska 28, 83-110 Tczew</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Dąbrowskiego 28, 32-600 Oświęcim</t>
+          <t>Gdańska 28, 83-110 Tczew</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>03-06-2023</t>
+          <t>12-10-2018</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -10759,7 +10759,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Helios Markets S.A.</t>
+          <t>Amber Nieruchomości S.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10789,12 +10789,12 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>ul. Rynek 45/77, 38-400 Krosno</t>
+          <t>ul. Sobieskiego 45/77, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>ul. Rynek 45/77, 38-400 Krosno</t>
+          <t>ul. Sobieskiego 45/77, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10809,19 +10809,19 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2020-22-01</t>
+          <t>2019-19-11</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2019-12-04</t>
+          <t>2019-04-12</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Lumen Advisory SA</t>
+          <t>Amber Inwestycje SA</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 62, 39-300 Mielec</t>
+          <t>ul Głęboka 62, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 62, 39-300 Mielec</t>
+          <t>ul Głęboka 62, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>20190529</t>
+          <t>20201226</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -10883,7 +10883,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Nova Data S. A.</t>
+          <t>Amber Medycyna S. A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -10913,12 +10913,12 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>os. Długa 79, 58-100 Świdnica</t>
+          <t>os. Małachowskiego 79, 42-500 Będzin</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>os. Długa 79, 58-100 Świdnica</t>
+          <t>os. Małachowskiego 79, 42-500 Będzin</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>21/09/2016</t>
+          <t>05/01/2021</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -10945,7 +10945,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka Akcyjna</t>
+          <t>Amber Zdrowie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -10975,12 +10975,12 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>96, 57-300 Kłodzko</t>
+          <t>Królowej Jadwigi 96, 88-100 Inowrocław</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>96, 57-300 Kłodzko</t>
+          <t>Królowej Jadwigi 96, 88-100 Inowrocław</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2018/27/11</t>
+          <t>2022/12/02</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -11007,7 +11007,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o.o.</t>
+          <t>Amber Urody sp. z o.o.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>ul. Chrobrego 113/39, 62-200 Gniezno</t>
+          <t>ul. Wybickiego 113/39, 86-300 Grudziądz</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>ul. Chrobrego 113/39, 62-200 Gniezno</t>
+          <t>ul. Wybickiego 113/39, 86-300 Grudziądz</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>26-07-2023</t>
+          <t>19-03-2023</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11069,7 +11069,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Quantum Services sp z oo</t>
+          <t>Amber Turystyka sp z oo</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>ul Słowiańska 130, 64-100 Leszno</t>
+          <t>ul Czarnieckiego 130, 14-100 Ostróda</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>ul Słowiańska 130, 64-100 Leszno</t>
+          <t>ul Czarnieckiego 130, 14-100 Ostróda</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11119,19 +11119,19 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2018-26-10</t>
+          <t>2024-26-04</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2022-10-06</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o. o.</t>
+          <t>Amber Rozrywka sp. z o. o.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11161,12 +11161,12 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>ulica Gdańska 147, 83-110 Tczew</t>
+          <t>ulica Warszawska 147, 11-500 Giżycko</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>ulica Gdańska 147, 83-110 Tczew</t>
+          <t>ulica Warszawska 147, 11-500 Giżycko</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>20201023</t>
+          <t>20250505</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11193,7 +11193,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Vistula Fintech Sp. z o.o.</t>
+          <t>Amber Gastronomia Sp. z o.o.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>249218045</t>
+          <t>259138887</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11223,12 +11223,12 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Sobieskiego 164, 84-200 Wejherowo</t>
+          <t>Lubelska 164, 24-100 Puławy</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Sobieskiego 164, 84-200 Wejherowo</t>
+          <t>Lubelska 164, 24-100 Puławy</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>25/12/2016</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11255,7 +11255,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PPHU Astra Finance</t>
+          <t>PPHU Amber Moda</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>ul. Głęboka 1/1, 43-400 Cieszyn</t>
+          <t>ul. Staszica 1/1, 22-400 Zamość</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>ul. Głęboka 1/1, 43-400 Cieszyn</t>
+          <t>ul. Staszica 1/1, 22-400 Zamość</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2022/29/07</t>
+          <t>2015/19/07</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11317,7 +11317,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Baltic Med Supply spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Tekstylia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11347,12 +11347,12 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>ul Małachowskiego 18, 42-500 Będzin</t>
+          <t>ul 3 Maja 18, 16-300 Augustów</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>ul Małachowskiego 18, 42-500 Będzin</t>
+          <t>ul 3 Maja 18, 16-300 Augustów</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>08-05-2019</t>
+          <t>26-08-2016</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11379,7 +11379,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Motoryzacja Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11389,12 +11389,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>249455615</t>
+          <t>259376457</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11409,12 +11409,12 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>ulica Królowej Jadwigi 35, 88-100 Inowrocław</t>
+          <t>ulica Kościuszki 35, 16-400 Suwałki</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>ulica Królowej Jadwigi 35, 88-100 Inowrocław</t>
+          <t>ulica Kościuszki 35, 16-400 Suwałki</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2017-29-04</t>
+          <t>2017-05-09</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -11441,7 +11441,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Lumen Advisory S.A.</t>
+          <t>Amber Ubezpieczenia S.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11471,12 +11471,12 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>os. Kościuszki 172, 16-400</t>
+          <t>os. Kupiecka 172, 65-058</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>os. Kościuszki 172, 16-400</t>
+          <t>os. Kupiecka 172, 65-058</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11491,19 +11491,19 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>20161011</t>
+          <t>20181012</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>20180305</t>
+          <t>20180503</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Nova Data SA</t>
+          <t>Amber Spawalnictwo SA</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>ul. Czarnieckiego 69/53, 14-100 Ostróda</t>
+          <t>ul. Długa 69/53, 49-300 Brzeg</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>ul. Czarnieckiego 69/53, 14-100 Ostróda</t>
+          <t>ul. Długa 69/53, 49-300 Brzeg</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>28/08/2025</t>
+          <t>19/11/2019</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -11565,7 +11565,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Optima Trade S. A.</t>
+          <t>Amber Ślusarstwo S. A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>ul Warszawska 86, 11-500 Giżycko</t>
+          <t>ul Rynek 86, 68-200 Żary</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>ul Warszawska 86, 11-500 Giżycko</t>
+          <t>ul Rynek 86, 68-200 Żary</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>2025/12/09</t>
+          <t>2020/26/12</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -11627,7 +11627,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka Akcyjna</t>
+          <t>Amber Krawiectwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11657,12 +11657,12 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>ulica Lubelska 103, 24-100 Puławy</t>
+          <t>ulica Sikorskiego 103, 66-200 Świebodzin</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>ulica Lubelska 103, 24-100 Puławy</t>
+          <t>ulica Sikorskiego 103, 66-200 Świebodzin</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>26-08-2019</t>
+          <t>05-01-2021</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -11689,7 +11689,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o.o.</t>
+          <t>Amber Ochrona sp. z o.o.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Staszica 120, 22-400 Zamość</t>
+          <t>Armii Krajowej 120, 78-100 Kołobrzeg</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Staszica 120, 22-400 Zamość</t>
+          <t>Armii Krajowej 120, 78-100 Kołobrzeg</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -11739,19 +11739,19 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2022-03-08</t>
+          <t>2022-12-02</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
+          <t>2022-07-05</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Silesia Invest sp z oo</t>
+          <t>Amber Catering sp z oo</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 137/15, 16-300 Augustów</t>
+          <t>ul. Piłsudskiego 137/15, 73-110 Stargard</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 137/15, 16-300 Augustów</t>
+          <t>ul. Piłsudskiego 137/15, 73-110 Stargard</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>20170524</t>
+          <t>20230319</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -11813,7 +11813,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o. o.</t>
+          <t>Amber Księgowość sp. z o. o.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>350009941</t>
+          <t>259930787</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11843,12 +11843,12 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>ul Kościuszki 154, 16-400 Suwałki</t>
+          <t>154, 27-600 Sandomierz</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>ul Kościuszki 154, 16-400 Suwałki</t>
+          <t>154, 27-600 Sandomierz</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>02/10/2016</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -11875,7 +11875,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Astra Finance Sp. z o.o.</t>
+          <t>Bizon Budownictwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -11905,12 +11905,12 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>ulica Piastowska 171, 48-300 Nysa</t>
+          <t>ulica Sienkiewicza 171, 27-400 Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>ulica Piastowska 171, 48-300 Nysa</t>
+          <t>ulica Sienkiewicza 171, 27-400 Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2017/08/08</t>
+          <t>2025/05/05</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -11937,7 +11937,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SP Z O O</t>
+          <t>Bizon Transport SP Z O O</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Długa 8, 49-300 Brzeg</t>
+          <t>Chmielna 8, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Długa 8, 49-300 Brzeg</t>
+          <t>Chmielna 8, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>25-02-2017</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -11999,7 +11999,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Helios Markets spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Spedycja spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -12029,12 +12029,12 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>ul. Rynek 25/67, 68-200 Żary</t>
+          <t>ul. Nowy Świat 25/67, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>ul. Rynek 25/67, 68-200 Żary</t>
+          <t>ul. Nowy Świat 25/67, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2020-10-10</t>
+          <t>2015-19-07</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -12061,7 +12061,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Logistyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -12091,12 +12091,12 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>ul Sikorskiego 42, 66-200 Świebodzin</t>
+          <t>ul os. Przyjaźń 42, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>ul Sikorskiego 42, 66-200 Świebodzin</t>
+          <t>ul os. Przyjaźń 42, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>20200318</t>
+          <t>20160826</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -12123,7 +12123,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Nova Data S.A.</t>
+          <t>Bizon Handel S.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -12153,12 +12153,12 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>ulica Armii Krajowej 59, 78-100 Kołobrzeg</t>
+          <t>ulica Jagiellońska 59, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>ulica Armii Krajowej 59, 78-100 Kołobrzeg</t>
+          <t>ulica Jagiellońska 59, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>09/03/2017</t>
+          <t>05/09/2017</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -12185,7 +12185,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Optima Trade SA</t>
+          <t>Bizon Usługi SA</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>81050774016</t>
+          <t>71050774016</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -12215,12 +12215,12 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Piłsudskiego 76, 73-110 Stargard</t>
+          <t>Piłsudskiego 76, 05-270 Marki</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Piłsudskiego 76, 73-110 Stargard</t>
+          <t>Piłsudskiego 76, 05-270 Marki</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2025/17/11</t>
+          <t>2018/12/10</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -12247,7 +12247,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Polaris Capital S. A.</t>
+          <t>Bizon Finanse S. A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>250564275</t>
+          <t>260485119</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>93/29, 27-600 Sandomierz</t>
+          <t>ul. Andriollego 93/29, 05-400 Otwock</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>93/29, 27-600 Sandomierz</t>
+          <t>ul. Andriollego 93/29, 05-400 Otwock</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>30-07-2025</t>
+          <t>19-11-2019</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -12309,7 +12309,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka Akcyjna</t>
+          <t>Bizon Doradztwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Zwolniony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -12334,17 +12334,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>000001911</t>
+          <t>0000019117</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 110, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>ul Żeromskiego 110, 26-600 Radom</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 110, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>ul Żeromskiego 110, 26-600 Radom</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2021-20-07</t>
+          <t>2020-26-12</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -12371,7 +12371,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Bizon Szkolenia sp. z o.o.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Czynny</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 127, 00-590 Warszawa</t>
+          <t>ulica Tumska 127, 09-402 Płock</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 127, 00-590 Warszawa</t>
+          <t>ulica Tumska 127, 09-402 Płock</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>20231004</t>
+          <t>20210105</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -12433,7 +12433,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Bizon Media sp z oo</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12443,7 +12443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Wykreślony</t>
+          <t>AKTYWNY</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -12463,12 +12463,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 144, 00-071 Warszawa</t>
+          <t>Karmelicka 144, 31-128 Kraków</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 144, 00-071 Warszawa</t>
+          <t>Karmelicka 144, 31-128 Kraków</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>19/11/2020</t>
+          <t>12/02/2022</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">

--- a/data/xlsx/vat.xlsx
+++ b/data/xlsx/vat.xlsx
@@ -95,12 +95,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Facebook - Meta</t>
+          <t>X - Twitter</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1234805466</t>
+          <t>1282319462</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -110,7 +110,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>234963846</t>
+          <t>282477841</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -120,17 +120,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0000000008</t>
+          <t>0000058208</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>os. Marszałkowska 1/1, 00-590 Warszawa</t>
+          <t>ul. Zwycięstwa 121/61, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>os. Marszałkowska 1/1, 00-590 Warszawa</t>
+          <t>ul. Zwycięstwa 121/61, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -157,12 +157,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Polskie Przetwory sp z oo</t>
+          <t>Zielony Bieszczady S.A.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1234884655</t>
+          <t>1282398651</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -172,7 +172,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>235043036</t>
+          <t>282557037</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -182,17 +182,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0000000105</t>
+          <t>0000058305</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 18, 00-071 Warszawa</t>
+          <t>ul Bocheńskiego 138, 43-100 Tychy</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 18, 00-071 Warszawa</t>
+          <t>ul Bocheńskiego 138, 43-100 Tychy</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -219,12 +219,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hurtownia Nabiału Mleczko sp. z o. o.</t>
+          <t>Zielony Karpaty SA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1234963840</t>
+          <t>1282477847</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -234,7 +234,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>235122221</t>
+          <t>282636222</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -244,17 +244,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0000000202</t>
+          <t>0000058402</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ulica Floriańska 35, 31-019 Kraków</t>
+          <t>ulica Najświętszej Maryi Panny 155, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ulica Floriańska 35, 31-019 Kraków</t>
+          <t>ulica Najświętszej Maryi Panny 155, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -281,12 +281,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Agencja Reklamowa Kreatywni Sp. z o.o.</t>
+          <t>Zielony Bałtyk S. A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1235043030</t>
+          <t>1282557032</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -296,7 +296,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>235201417</t>
+          <t>282715418</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -306,17 +306,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0000000299</t>
+          <t>0000058499</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Długa 52, 31-147 Kraków</t>
+          <t>11 Listopada 172, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Długa 52, 31-147 Kraków</t>
+          <t>11 Listopada 172, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -343,12 +343,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kancelaria Prawna Sankcja SP Z O O</t>
+          <t>Zielony Sudety Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1235122226</t>
+          <t>1282636228</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -358,7 +358,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>235280606</t>
+          <t>282794607</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -368,17 +368,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0000000396</t>
+          <t>0000058596</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ul. Piotrkowska 69/53, 90-102 Łódź</t>
+          <t>9/23, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ul. Piotrkowska 69/53, 90-102 Łódź</t>
+          <t>9/23, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -405,12 +405,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Śląskie Zakłady Mechaniczne spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Amber sp. z o.o.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1235201411</t>
+          <t>1282715413</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>235359791</t>
+          <t>282873790</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -430,17 +430,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0000000493</t>
+          <t>0000058693</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ul Zachodnia 86, 90-402 Łódź</t>
+          <t>ul Franciszkańska 26, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ul Zachodnia 86, 90-402 Łódź</t>
+          <t>ul Franciszkańska 26, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -467,12 +467,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fabryka Okien i Drzwi Profil Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Bizon sp z oo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1235280600</t>
+          <t>1282794602</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>235438987</t>
+          <t>282952986</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -492,17 +492,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0000000590</t>
+          <t>0000058790</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ulica Świdnicka 103, 50-066 Wrocław</t>
+          <t>ulica Kościuszki 43, 38-500 Sanok</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ulica Świdnicka 103, 50-066 Wrocław</t>
+          <t>ulica Kościuszki 43, 38-500 Sanok</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -529,12 +529,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Przedsiębiorstwo Robót rDogowych S.A.</t>
+          <t>Niebieski Canyon s. z o. o.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1235359796</t>
+          <t>1282873796</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>235518172</t>
+          <t>283032176</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -554,17 +554,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0000000687</t>
+          <t>0000058887</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Legnicka 120, 54-203 Wrocław</t>
+          <t>Suraska 60, 15-422 Białystok</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Legnicka 120, 54-203 Wrocław</t>
+          <t>Suraska 60, 15-422 Białystok</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -584,19 +584,19 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2021-11-08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Krakowskie Biuro Nieruchomości SA</t>
+          <t>Niebieski Delfin Sp. z o.o.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1235438981</t>
+          <t>1282952981</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>235597361</t>
+          <t>283111361</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0000000784</t>
+          <t>0000058984</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ul. Święty Marcin 137/15, 61-806 Poznań</t>
+          <t>77/75, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ul. Święty Marcin 137/15, 61-806 Poznań</t>
+          <t>77/75, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -653,12 +653,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Salon Samochodowy Auto-Hit S. A.</t>
+          <t>Niebieski Echo SP Z O O</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1235518177</t>
+          <t>1283032171</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>235676557</t>
+          <t>283190550</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -678,17 +678,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0000000881</t>
+          <t>0000059081</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ul Głogowska 154, 60-734 Poznań</t>
+          <t>os. 3 Maja 94, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ul Głogowska 154, 60-734 Poznań</t>
+          <t>os. 3 Maja 94, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Klinika Stomatologiczna Dent-Med Spółka Akcyjna</t>
+          <t>Niebieski Falcon spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1235597366</t>
+          <t>1283111367</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>235755742</t>
+          <t>283269748</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -740,17 +740,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0000000978</t>
+          <t>0000059178</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ulica Długa 171, 80-831 Gdańsk</t>
+          <t>ulica os. LSM 111, 20-400 Lublin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ulica Długa 171, 80-831 Gdańsk</t>
+          <t>ulica os. LSM 111, 20-400 Lublin</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -777,12 +777,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Polski Tytoń sp. z o.o.</t>
+          <t>Niebieski Gryf Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1235676551</t>
+          <t>1283190556</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>235834938</t>
+          <t>283348933</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0000001075</t>
+          <t>0000059275</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Grunwaldzka 8, 80-236 Gdańsk</t>
+          <t>128, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Grunwaldzka 8, 80-236 Gdańsk</t>
+          <t>128, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -839,12 +839,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gdańska Stocznia Jachtowa sp z oo</t>
+          <t>Niebieski Horyzont S.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1235755747</t>
+          <t>1283269743</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>235914123</t>
+          <t>283428129</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -864,17 +864,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0000001172</t>
+          <t>0000059372</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ul. Jagiellońska 25/67, 70-435 Szczecin</t>
+          <t>ul. Brzeska 145/37, 21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ul. Jagiellońska 25/67, 70-435 Szczecin</t>
+          <t>ul. Brzeska 145/37, 21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -901,12 +901,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Wytwórnia Makaronu Jajecznego sp. z o. o.</t>
+          <t>Niebieski Ikar SA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1235834932</t>
+          <t>1283348939</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>235993312</t>
+          <t>283507314</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -926,17 +926,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0000001269</t>
+          <t>0000059469</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ul Wyszyńskiego 42, 70-200 Szczecin</t>
+          <t>ul Rynek Staromiejski 162, 87-100 Toruń</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ul Wyszyńskiego 42, 70-200 Szczecin</t>
+          <t>ul Rynek Staromiejski 162, 87-100 Toruń</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -963,12 +963,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Zakłady Mięsne Tradycja Sp. z o.o.</t>
+          <t>Niebieski Jantar S. A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1235914128</t>
+          <t>1283428124</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>236072502</t>
+          <t>283586503</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0000001366</t>
+          <t>0000059566</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ulica Mariacka 59, 40-014 Katowice</t>
+          <t>ulica Mostowa 179, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ulica Mariacka 59, 40-014 Katowice</t>
+          <t>ulica Mostowa 179, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1025,12 +1025,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spółdzielnia Mleczarska Radomsko SP Z O O</t>
+          <t>Niebieski Koral Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1235993317</t>
+          <t>1293507345</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>236151696</t>
+          <t>283665697</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1050,17 +1050,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0000001463</t>
+          <t>0000059663</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Warszawska 76, 40-009 Katowice</t>
+          <t>Stare Miasto 16, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Warszawska 76, 40-009 Katowice</t>
+          <t>Stare Miasto 16, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1087,12 +1087,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kancelaria Finansowo-Księgowa Bilans spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Lotos sp. z o.o.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1236072507</t>
+          <t>1283586509</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>236230881</t>
+          <t>283744882</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1112,17 +1112,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0000001560</t>
+          <t>0000059760</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ul. Krakowskie Przedmieście 93/29, 20-002 Lublin</t>
+          <t>ul. Warszawska 33/89, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ul. Krakowskie Przedmieście 93/29, 20-002 Lublin</t>
+          <t>ul. Warszawska 33/89, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1149,12 +1149,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Zarząd Nieruchomości Komercyjnych Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Magnolia sp z oo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1236151690</t>
+          <t>1283665692</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>236310077</t>
+          <t>283824078</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1174,17 +1174,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0000001657</t>
+          <t>0000059857</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ul Narutowicza 110, 20-004 Lublin</t>
+          <t>ul Wojska Polskiego 50, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ul Narutowicza 110, 20-004 Lublin</t>
+          <t>ul Wojska Polskiego 50, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1211,12 +1211,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Polskie Linie Oceaniczne S.A.</t>
+          <t>Niebieski Neon sp. z o. o.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1236230886</t>
+          <t>1283744888</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>236389268</t>
+          <t>283903263</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1236,17 +1236,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0000001754</t>
+          <t>0000059954</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ulica Lipowa 127, 15-424 Białystok</t>
+          <t>ulica Monte Cassino 67, 72-600 Świnoujście</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ulica Lipowa 127, 15-424 Białystok</t>
+          <t>ulica Monte Cassino 67, 72-600 Świnoujście</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1273,12 +1273,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Hurtownia Materiałów Budowlanych Cegiełka SA</t>
+          <t>Niebieski Oaza Sp. z o.o.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1236310071</t>
+          <t>1283824073</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>236468453</t>
+          <t>283982452</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0000001851</t>
+          <t>0000060051</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PPHU Studio Projektowe Architektura</t>
+          <t>P.P.H.U. Niebieski Pegaz</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1236389262</t>
+          <t>1283903269</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>236547649</t>
+          <t>284061642</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0000001948</t>
+          <t>0000060148</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ul. Gdańska 161/81, 85-005 Bydgoszcz</t>
+          <t>ul. Byczyńska 101/51, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ul. Gdańska 161/81, 85-005 Bydgoszcz</t>
+          <t>ul. Byczyńska 101/51, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1397,12 +1397,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Centrum Medycyny Pracy Spółka Akcyjna</t>
+          <t>Niebieski Rubin spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1236468458</t>
+          <t>1283982458</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>236626834</t>
+          <t>284140838</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1422,17 +1422,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0000002045</t>
+          <t>0000060245</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ul Dworcowa 178, 85-009 Bydgoszcz</t>
+          <t>ul Chrobrego 118, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>ul Dworcowa 178, 85-009 Bydgoszcz</t>
+          <t>ul Chrobrego 118, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Przedsiębiorstwo Energetyki Cieplnej sp. z o.o.</t>
+          <t>Niebieski Szafir Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1236547643</t>
+          <t>1284061648</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>246706057</t>
+          <t>284220023</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1484,17 +1484,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0000002142</t>
+          <t>0000060342</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ulica Szeroka 15, 87-100 Toruń</t>
+          <t>ulica 30 Stycznia 135, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>ulica Szeroka 15, 87-100 Toruń</t>
+          <t>ulica 30 Stycznia 135, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1521,12 +1521,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gospodarstwo Rolno-Ogrodnicze sp z oo</t>
+          <t>Niebieski Tytan S.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1236626839</t>
+          <t>1284140833</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>236785219</t>
+          <t>284299214</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0000002239</t>
+          <t>0000060439</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chełmińska 32, 87-100 Toruń</t>
+          <t>Paderewskiego 152, 25-004 Kielce</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Chełmińska 32, 87-100 Toruń</t>
+          <t>Paderewskiego 152, 25-004 Kielce</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1583,12 +1583,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Drukarnia Wielkoformatowa Impress sp. z o. o.</t>
+          <t>Niebieski Uran SA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1236706024</t>
+          <t>1284220029</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>236864404</t>
+          <t>294378437</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1608,17 +1608,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0000002336</t>
+          <t>0000060536</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 49/43, 35-030 Rzeszów</t>
+          <t>ul. 1 Maja 169/13, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 49/43, 35-030 Rzeszów</t>
+          <t>ul. 1 Maja 169/13, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1645,12 +1645,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Klub Fitness Sylwetka Sp. z o.o.</t>
+          <t>Niebieski Wektor S. A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1236785213</t>
+          <t>1294299245</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>236943598</t>
+          <t>284457593</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1670,17 +1670,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0000002433</t>
+          <t>0000060633</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 66, 35-074 Rzeszów</t>
+          <t>ul Marszałkowska 6, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 66, 35-074 Rzeszów</t>
+          <t>ul Marszałkowska 6, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1707,12 +1707,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Polska Grupa Energetyczna SP Z O O</t>
+          <t>Niebieski Zefir Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1236864409</t>
+          <t>1284378405</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>237022788</t>
+          <t>284536789</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1732,17 +1732,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0000002530</t>
+          <t>0000060730</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 83, 25-007 Kielce</t>
+          <t>ulica Krakowskie Przedmieście 23, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 83, 25-007 Kielce</t>
+          <t>ulica Krakowskie Przedmieście 23, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1769,12 +1769,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mazowieckie Zakłady Drobiarskie spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Żubr sp. z o.o.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1236943592</t>
+          <t>1284457599</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>237101973</t>
+          <t>284615974</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1794,17 +1794,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0000002627</t>
+          <t>0000060827</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Warszawska 100, 25-512 Kielce</t>
+          <t>Floriańska 40, 31-019 Kraków</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Warszawska 100, 25-512 Kielce</t>
+          <t>Floriańska 40, 31-019 Kraków</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1824,19 +1824,19 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2018-03-05</t>
+          <t>2018-05-03</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hurtownia Farmaceutyczna Aptekarz Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Sokół sp z oo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1237022782</t>
+          <t>1284536784</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>237181162</t>
+          <t>284695163</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1856,17 +1856,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0000002724</t>
+          <t>0000060924</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ul. Kościuszki 117/5, 10-504 Olsztyn</t>
+          <t>ul. Długa 57/65, 31-147 Kraków</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ul. Kościuszki 117/5, 10-504 Olsztyn</t>
+          <t>ul. Długa 57/65, 31-147 Kraków</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1893,12 +1893,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kancelaria Notarialna Lex S.A.</t>
+          <t>Niebieski Orzeł sp. z o. o.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1237101978</t>
+          <t>1294616007</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>237260358</t>
+          <t>284774359</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1918,17 +1918,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0000002821</t>
+          <t>0000061021</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>os. Dąbrowszczaków 134, 10-540 Olsztyn</t>
+          <t>ul Piotrkowska 74, 90-102 Łódź</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>os. Dąbrowszczaków 134, 10-540 Olsztyn</t>
+          <t>ul Piotrkowska 74, 90-102 Łódź</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1955,12 +1955,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Biuro Podróży Wojażer SA</t>
+          <t>Niebieski Kormoran Sp. z o.o.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1237181167</t>
+          <t>1284695169</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1970,27 +1970,27 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>237339545</t>
+          <t>284853544</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>90082847941</t>
+          <t>92082869943</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0000002918</t>
+          <t>0000061118</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ulica Krakowska 151, 45-018 Opole</t>
+          <t>ulica Zachodnia 91, 90-402 Łódź</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ulica Krakowska 151, 45-018 Opole</t>
+          <t>ulica Zachodnia 91, 90-402 Łódź</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2017,12 +2017,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Szkoła Języków Obcych Lingua S. A.</t>
+          <t>Niebieski Barycz SP Z O O</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1237260352</t>
+          <t>1284774354</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2032,27 +2032,27 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>237418730</t>
+          <t>294932767</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>91090749335</t>
+          <t>93090771330</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0000003015</t>
+          <t>0000061215</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ozimska 168, 45-057 Opole</t>
+          <t>Świdnicka 108, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Ozimska 168, 45-057 Opole</t>
+          <t>Świdnicka 108, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2079,12 +2079,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Centrum Logistyczne Podlasie Spółka Akcyjna</t>
+          <t>Niebieski Noteć spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1247339575</t>
+          <t>1294853575</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2094,27 +2094,27 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>247497957</t>
+          <t>295011957</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>92101450680</t>
+          <t>94101472682</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0000003112</t>
+          <t>0000061312</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ul. Bohaterów Westerplatte 5/57, 65-034 Zielona Góra</t>
+          <t>ul. Legnicka 125/27, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ul. Bohaterów Westerplatte 5/57, 65-034 Zielona Góra</t>
+          <t>ul. Legnicka 125/27, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-12-08</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Fabryka Mebli Drewnianych Dąb sp. z o.o.</t>
+          <t>Niebieski Pilica Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1237418735</t>
+          <t>1284932735</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2156,27 +2156,27 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>237577115</t>
+          <t>285091119</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>93112152077</t>
+          <t>95112174079</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0000003209</t>
+          <t>0000061409</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ul Kupiecka 22, 65-058 Zielona Góra</t>
+          <t>ul Święty Marcin 142, 61-806 Poznań</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ul Kupiecka 22, 65-058 Zielona Góra</t>
+          <t>ul Święty Marcin 142, 61-806 Poznań</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2203,12 +2203,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Polskie Sady sp z oo</t>
+          <t>Niebieski Narew S.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1237497924</t>
+          <t>1285011925</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2218,27 +2218,27 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>237656300</t>
+          <t>285170304</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>94122853426</t>
+          <t>96122875428</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0000003306</t>
+          <t>0000061506</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>ulica Świętojańska 39, 81-372 Gdynia</t>
+          <t>ulica Głogowska 159, 60-734 Poznań</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>ulica Świętojańska 39, 81-372 Gdynia</t>
+          <t>ulica Głogowska 159, 60-734 Poznań</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2265,12 +2265,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Wielkopolska Hurtownia Stali sp. z o. o.</t>
+          <t>Niebieski Jodełka SA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1247577145</t>
+          <t>1285091114</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2280,27 +2280,27 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>237735494</t>
+          <t>295249529</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>95010754814</t>
+          <t>97010776816</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0000003403</t>
+          <t>0000061603</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>10 Lutego 56, 81-364 Gdynia</t>
+          <t>Długa 176, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>10 Lutego 56, 81-364 Gdynia</t>
+          <t>Długa 176, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2327,12 +2327,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Zakład Oczyszczania Miasta Sp. z o.o.</t>
+          <t>Niebieski Kaktus S. A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1237656305</t>
+          <t>1295170335</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2342,27 +2342,27 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>247814719</t>
+          <t>285328685</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>96021456164</t>
+          <t>98021478166</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0000003500</t>
+          <t>0000061700</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ul. Bolesława Prusa 73/19, 05-800 Pruszków</t>
+          <t>ul. Grunwaldzka 13/79, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ul. Bolesława Prusa 73/19, 05-800 Pruszków</t>
+          <t>ul. Grunwaldzka 13/79, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2389,12 +2389,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Przedsiębiorstwo Wodociągów i Kanalizacji SP Z O O</t>
+          <t>Niebieski Szmaragd Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1237735499</t>
+          <t>1285249495</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2404,17 +2404,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>237893879</t>
+          <t>285407870</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>97032157550</t>
+          <t>99032179552</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0000003597</t>
+          <t>0000061797</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2451,12 +2451,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Instytut Badań Rynkowych spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Topaz sp. z o.o.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1237814684</t>
+          <t>1285328680</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2466,27 +2466,27 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>237973064</t>
+          <t>395487097</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>98042858909</t>
+          <t>00242880909</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0000003694</t>
+          <t>0000061894</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 107, 32-020 Wieliczka</t>
+          <t>os. Wyszyńskiego 47, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 107, 32-020 Wieliczka</t>
+          <t>os. Wyszyńskiego 47, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2513,12 +2513,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Agencja Ochrony Solidna Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Granit sp z oo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1237893873</t>
+          <t>1285407876</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2528,27 +2528,27 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>238052254</t>
+          <t>285566255</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>99050760297</t>
+          <t>01250782294</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0000003791</t>
+          <t>0000061991</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dąbrowskiego 124, 32-600 Oświęcim</t>
+          <t>Mariacka 64, 40-014 Katowice</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Dąbrowskiego 124, 32-600 Oświęcim</t>
+          <t>Mariacka 64, 40-014 Katowice</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2575,12 +2575,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Instagram - Meta</t>
+          <t>Facebook - Meta</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1237973069</t>
+          <t>1285487065</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2590,27 +2590,27 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>348131477</t>
+          <t>285645440</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>00261461640</t>
+          <t>02261483642</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0000003888</t>
+          <t>0000062088</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ul. Rynek 141/71, 38-400 Krosno</t>
+          <t>ul. Warszawska 81/41, 40-009 Katowice</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ul. Rynek 141/71, 38-400 Krosno</t>
+          <t>ul. Warszawska 81/41, 40-009 Katowice</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2637,12 +2637,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Krajowa Izba Gospodarcza SA</t>
+          <t>Niebieski Syrena Sp. z o.o.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1238052259</t>
+          <t>1285566250</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2652,27 +2652,27 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>238210635</t>
+          <t>285724636</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>01272163037</t>
+          <t>03272185039</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0000003985</t>
+          <t>0000062185</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 158, 39-300 Mielec</t>
+          <t>ul Krakowskie Przedmieście 98, 20-002 Lublin</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 158, 39-300 Mielec</t>
+          <t>ul Krakowskie Przedmieście 98, 20-002 Lublin</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2699,12 +2699,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Polskie Zakłady Lotnicze S. A.</t>
+          <t>Niebieski Zodiak SP Z O O</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1238131444</t>
+          <t>1285645446</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2714,27 +2714,27 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>238289826</t>
+          <t>285803821</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>02282864387</t>
+          <t>04282886389</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0000004082</t>
+          <t>0000062282</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>175, 58-100 Świdnica</t>
+          <t>ulica Narutowicza 115, 20-004 Lublin</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>175, 58-100 Świdnica</t>
+          <t>ulica Narutowicza 115, 20-004 Lublin</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2761,12 +2761,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hurtownia Elektryczna Wat Spółka Akcyjna</t>
+          <t>Niebieski Olimp spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1248210665</t>
+          <t>1285724631</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2776,27 +2776,27 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>238369011</t>
+          <t>285883010</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>03290765770</t>
+          <t>05290787772</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0000004179</t>
+          <t>0000062379</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Wojska Polskiego 12, 57-300 Kłodzko</t>
+          <t>Lipowa 132, 15-424 Białystok</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Wojska Polskiego 12, 57-300 Kłodzko</t>
+          <t>Lipowa 132, 15-424 Białystok</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2823,12 +2823,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Centrum Ogrodnicze Zielona Oaza sp. z o.o.</t>
+          <t>Niebieski Zorza Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1238289820</t>
+          <t>1285803827</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2838,27 +2838,27 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>238448207</t>
+          <t>285962206</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>04301467122</t>
+          <t>60101489120</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0000004276</t>
+          <t>0000062476</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ul. Chrobrego 29/33, 62-200 Gniezno</t>
+          <t>ul. Sienkiewicza 149/3, 15-092 Białystok</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>ul. Chrobrego 29/33, 62-200 Gniezno</t>
+          <t>ul. Sienkiewicza 149/3, 15-092 Białystok</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2885,12 +2885,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Piekarnia i Cukiernia Chrupiący Rogalik sp z oo</t>
+          <t>Niebieski Krokus S.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1238369016</t>
+          <t>1285883016</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2900,27 +2900,27 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>238527390</t>
+          <t>286041394</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>05312168518</t>
+          <t>61112190519</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0000004373</t>
+          <t>0000062573</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>ul Słowiańska 46, 64-100 Leszno</t>
+          <t>ul Gdańska 166, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>ul Słowiańska 46, 64-100 Leszno</t>
+          <t>ul Gdańska 166, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2947,12 +2947,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Zakład Usług Komunalnych sp. z o. o.</t>
+          <t>Niebieski Narcyz SA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1238448201</t>
+          <t>1285962201</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2962,27 +2962,27 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>238606586</t>
+          <t>296120619</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>60122869864</t>
+          <t>62122891869</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0000004470</t>
+          <t>0000062670</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>ulica Gdańska 63, 83-110 Tczew</t>
+          <t>ulica Dworcowa 3, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>ulica Gdańska 63, 83-110 Tczew</t>
+          <t>ulica Dworcowa 3, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3009,12 +3009,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Polski Komfort Sp. z o.o.</t>
+          <t>Niebieski Giewont S. A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1238527395</t>
+          <t>1296041427</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3024,27 +3024,27 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>238685775</t>
+          <t>286199770</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>61010771256</t>
+          <t>63010793258</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0000004567</t>
+          <t>0000062767</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sobieskiego 80, 84-200 Wejherowo</t>
+          <t>Szeroka 20, 87-100 Toruń</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sobieskiego 80, 84-200 Wejherowo</t>
+          <t>Szeroka 20, 87-100 Toruń</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3064,19 +3064,19 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kancelaria Radców Prawnych Partnerzy SP Z O O</t>
+          <t>Niebieski Rysy Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1238606580</t>
+          <t>1286120585</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3086,27 +3086,27 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>238764960</t>
+          <t>286278966</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>62021472604</t>
+          <t>64021494606</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0000004664</t>
+          <t>0000062864</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>ul. Głęboka 97/85, 43-400 Cieszyn</t>
+          <t>ul. Chełmińska 37/55, 87-100 Toruń</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>ul. Głęboka 97/85, 43-400 Cieszyn</t>
+          <t>ul. Chełmińska 37/55, 87-100 Toruń</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3133,12 +3133,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Centrum Dystrybucji Alkoholi spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Kasprowy sp. z o.o.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1248685807</t>
+          <t>1286199776</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3148,27 +3148,27 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>238844156</t>
+          <t>286358151</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>63032173991</t>
+          <t>65032195993</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0000004761</t>
+          <t>0000062961</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>114, 42-500 Będzin</t>
+          <t>ul 3 Maja 54, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>114, 42-500 Będzin</t>
+          <t>ul 3 Maja 54, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Przedsiębiorstwo Spedycyjne Ładunek Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Budownictwo sp z oo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1238764965</t>
+          <t>1286278961</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3210,27 +3210,27 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>238923341</t>
+          <t>286437347</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>64042875341</t>
+          <t>66042897343</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0000004858</t>
+          <t>0000063058</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ulica Królowej Jadwigi 131, 88-100 Inowrocław</t>
+          <t>ulica Piłsudskiego 71, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ulica Królowej Jadwigi 131, 88-100 Inowrocław</t>
+          <t>ulica Piłsudskiego 71, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3257,12 +3257,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Fabryka Tekstyliów Splot S.A.</t>
+          <t>Amber Transport sp. z o. o.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1238844150</t>
+          <t>1286358157</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3272,27 +3272,27 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>239002531</t>
+          <t>286516532</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>65050776734</t>
+          <t>67050798736</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0000004955</t>
+          <t>0000063155</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Wybickiego 148, 86-300 Grudziądz</t>
+          <t>Sienkiewicza 88, 25-007 Kielce</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Wybickiego 148, 86-300 Grudziądz</t>
+          <t>Sienkiewicza 88, 25-007 Kielce</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3319,12 +3319,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Górnośląskie Towarzystwo Finansowe SA</t>
+          <t>Amber Spedycja Sp. z o.o.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1238923346</t>
+          <t>1286437342</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3334,27 +3334,27 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>239081720</t>
+          <t>286595721</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>66061478084</t>
+          <t>68061400089</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0000005052</t>
+          <t>0000063252</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>ul. Czarnieckiego 165/47, 14-100 Ostróda</t>
+          <t>ul. Warszawska 105/17, 25-512 Kielce</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>ul. Czarnieckiego 165/47, 14-100 Ostróda</t>
+          <t>ul. Warszawska 105/17, 25-512 Kielce</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3374,19 +3374,19 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2019-04-12</t>
+          <t>2019-12-04</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Krajowa Agencja Informacyjna S. A.</t>
+          <t>Amber Logistyka SP Z O O</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1239002536</t>
+          <t>1286516538</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3396,27 +3396,27 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>239160916</t>
+          <t>286674917</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>67072179470</t>
+          <t>69072101475</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0000005149</t>
+          <t>0000063349</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>ul Warszawska 2, 11-500 Giżycko</t>
+          <t>ul Kościuszki 122, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>ul Warszawska 2, 11-500 Giżycko</t>
+          <t>ul Kościuszki 122, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3443,12 +3443,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Polskie Jagody Spółka Akcyjna</t>
+          <t>Amber Handel spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1239081725</t>
+          <t>1286595727</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3458,27 +3458,27 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>239240101</t>
+          <t>286754102</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>68082880822</t>
+          <t>70082802823</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0000005246</t>
+          <t>0000063446</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ulica Lubelska 19, 24-100 Puławy</t>
+          <t>ulica Dąbrowszczaków 139, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>ulica Lubelska 19, 24-100 Puławy</t>
+          <t>ulica Dąbrowszczaków 139, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3505,12 +3505,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Zielony Amber sp. z o.o.</t>
+          <t>Amber Usługi Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1239160910</t>
+          <t>1286674912</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3520,27 +3520,27 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>239319297</t>
+          <t>286833296</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>69090782216</t>
+          <t>71090704217</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0000005343</t>
+          <t>0000063543</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Staszica 36, 22-400 Zamość</t>
+          <t>Krakowska 156, 45-018 Opole</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Staszica 36, 22-400 Zamość</t>
+          <t>Krakowska 156, 45-018 Opole</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3567,12 +3567,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Zielony Bizon sp z oo</t>
+          <t>Amber Finanse S.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1239240106</t>
+          <t>1286754108</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3582,27 +3582,27 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>239398486</t>
+          <t>286912481</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>70101483567</t>
+          <t>72101405569</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0000005440</t>
+          <t>0000063640</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>53/9, 16-300 Augustów</t>
+          <t>ul. Ozimska 173/69, 45-057 Opole</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>53/9, 16-300 Augustów</t>
+          <t>ul. Ozimska 173/69, 45-057 Opole</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3629,12 +3629,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Zielony Canyon sp. z o. .</t>
+          <t>Amber Doradztwo SA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1239319291</t>
+          <t>1286833291</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3644,27 +3644,27 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>239477671</t>
+          <t>286991670</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>71112184953</t>
+          <t>73112106955</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0000005537</t>
+          <t>0000063737</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ul Kościuszki 70, 16-400 Suwałki</t>
+          <t>ul Bohaterów Westerplatte 10, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>ul Kościuszki 70, 16-400 Suwałki</t>
+          <t>ul Bohaterów Westerplatte 10, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3691,12 +3691,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Zielony Delfin Sp. z o.o.</t>
+          <t>Amber Szkolenia S. A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1239398480</t>
+          <t>1286912487</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3706,27 +3706,27 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>239556867</t>
+          <t>287070860</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>72122886303</t>
+          <t>74122808305</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0000005634</t>
+          <t>0000063834</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>os. Piastowska 87, 48-300 Nysa</t>
+          <t>ulica Kupiecka 27, 65-058 Zielona Góra</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>os. Piastowska 87, 48-300 Nysa</t>
+          <t>ulica Kupiecka 27, 65-058 Zielona Góra</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3753,12 +3753,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Zielony Echo SP Z O O</t>
+          <t>Amber Media Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1239477676</t>
+          <t>1286991676</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3768,27 +3768,27 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>239636052</t>
+          <t>287150056</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>73010787692</t>
+          <t>75010709694</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0000005731</t>
+          <t>0000063931</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Długa 104, 49-300 Brzeg</t>
+          <t>Świętojańska 44, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Długa 104, 49-300 Brzeg</t>
+          <t>Świętojańska 44, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3815,12 +3815,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>P.P.H.U. Zielony Falcon</t>
+          <t>PPHU Amber Reklama</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1239556861</t>
+          <t>1287070866</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3830,27 +3830,27 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>239715248</t>
+          <t>287229243</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>74021489041</t>
+          <t>76021411046</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0000005828</t>
+          <t>0000064028</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ul. Rynek 121/61, 68-200 Żary</t>
+          <t>ul. 10 Lutego 61/31, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>ul. Rynek 121/61, 68-200 Żary</t>
+          <t>ul. 10 Lutego 61/31, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3877,12 +3877,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Zielony Gryf Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Marketing sp z oo</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1239636057</t>
+          <t>1287150051</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3892,27 +3892,27 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>239794437</t>
+          <t>287308439</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>75032190430</t>
+          <t>77032112432</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0000005925</t>
+          <t>0000064125</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>ul Sikorskiego 138, 66-200 Świebodzin</t>
+          <t>ul Bolesława Prusa 78, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>ul Sikorskiego 138, 66-200 Świebodzin</t>
+          <t>ul Bolesława Prusa 78, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3939,12 +3939,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Zielony Horyzont S.A.</t>
+          <t>Amber Druk sp. z o. o.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1239715242</t>
+          <t>1287229249</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3954,27 +3954,27 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>239873622</t>
+          <t>287387628</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>76042891780</t>
+          <t>78042813782</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0000006022</t>
+          <t>0000064222</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>ulica Armii Krajowej 155, 78-100 Kołobrzeg</t>
+          <t>ulica Kościuszki 95, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ulica Armii Krajowej 155, 78-100 Kołobrzeg</t>
+          <t>ulica Kościuszki 95, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4001,12 +4001,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Zielony Ikar SA</t>
+          <t>Amber Informatyka Sp. z o.o.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1239794431</t>
+          <t>1287308434</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4016,27 +4016,27 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>239952818</t>
+          <t>287466813</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>77050793174</t>
+          <t>79050715176</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0000006119</t>
+          <t>0000064319</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Piłsudskiego 172, 73-110 Stargard</t>
+          <t>Sienkiewicza 112, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Piłsudskiego 172, 73-110 Stargard</t>
+          <t>Sienkiewicza 112, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Zielony Jantar S. A.</t>
+          <t>Amber Oprogramowanie SP Z O O</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1239873627</t>
+          <t>1287387623</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4078,27 +4078,27 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>240032008</t>
+          <t>287546009</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>78061494522</t>
+          <t>80061416523</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0000006216</t>
+          <t>0000064416</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>ul. Mickiewicza 9/23, 27-600 Sandomierz</t>
+          <t>ul. Dąbrowskiego 129/83, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>ul. Mickiewicza 9/23, 27-600 Sandomierz</t>
+          <t>ul. Dąbrowskiego 129/83, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4125,12 +4125,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Zielony Koral Spółka Akcyjna</t>
+          <t>Amber Rolnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1239952812</t>
+          <t>1287466819</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4140,27 +4140,27 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>240111191</t>
+          <t>287625192</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>79072195918</t>
+          <t>81072117919</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0000006313</t>
+          <t>0000064513</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 26, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>146, 38-400 Krosno</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 26, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>146, 38-400 Krosno</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4187,12 +4187,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Zielony Lotos sp. z o.o.</t>
+          <t>Amber Ogrodnictwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1240032000</t>
+          <t>1287546004</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4202,27 +4202,27 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>240190380</t>
+          <t>287704388</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>80082897268</t>
+          <t>82082819260</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0000006410</t>
+          <t>0000064610</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ulica Chmielna 43, 00-020 Warszawa</t>
+          <t>ulica Mickiewicza 163, 39-300 Mielec</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>ulica Chmielna 43, 00-020 Warszawa</t>
+          <t>ulica Mickiewicza 163, 39-300 Mielec</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4249,12 +4249,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Zielony Magnolia sp z oo</t>
+          <t>Amber Produkcja S.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1240111194</t>
+          <t>1287625198</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4264,27 +4264,27 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>240269578</t>
+          <t>287783577</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>81090798651</t>
+          <t>83090720656</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0000006507</t>
+          <t>0000064707</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nowy Świat 60, 00-029 Warszawa</t>
+          <t>os. Długa 180, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Nowy Świat 60, 00-029 Warszawa</t>
+          <t>os. Długa 180, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4304,19 +4304,19 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2022-07-05</t>
+          <t>2022-05-07</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Zielony Neon sp. z o. o.</t>
+          <t>Amber Przemysł SA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1240190383</t>
+          <t>1287704383</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4326,27 +4326,27 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>240348763</t>
+          <t>287862762</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>82101400006</t>
+          <t>84101422008</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0000006604</t>
+          <t>0000064804</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ul. os. Przyjaźń 77/75, 01-355 Warszawa</t>
+          <t>ul. Wojska Polskiego 17/45, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>ul. os. Przyjaźń 77/75, 01-355 Warszawa</t>
+          <t>ul. Wojska Polskiego 17/45, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4373,12 +4373,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Zielony Oaza Sp. z o.o.</t>
+          <t>Amber Ekologia S. A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1240269570</t>
+          <t>1287783572</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4388,27 +4388,27 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>240427959</t>
+          <t>287941958</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>83112101393</t>
+          <t>85112123395</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0000006701</t>
+          <t>0000064901</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ul Jagiellońska 94, 05-120 Legionowo</t>
+          <t>ul Chrobrego 34, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ul Jagiellońska 94, 05-120 Legionowo</t>
+          <t>ul Chrobrego 34, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4435,12 +4435,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Zielony Pegaz SP Z O O</t>
+          <t>Amber Energetyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1240348766</t>
+          <t>1287862768</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4450,27 +4450,27 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>240507144</t>
+          <t>288021148</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>84122802742</t>
+          <t>86122824744</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0000006798</t>
+          <t>0000064998</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ulica Piłsudskiego 111, 05-270 Marki</t>
+          <t>ulica Słowiańska 51, 64-100 Leszno</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ulica Piłsudskiego 111, 05-270 Marki</t>
+          <t>ulica Słowiańska 51, 64-100 Leszno</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4497,12 +4497,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Zielony Rubin spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Instalacje sp. z o.o.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1240427951</t>
+          <t>1287941953</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4512,27 +4512,27 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>240586333</t>
+          <t>288100333</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>85010704131</t>
+          <t>87010726133</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0000006895</t>
+          <t>0000065095</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Andriollego 128, 05-400 Otwock</t>
+          <t>Gdańska 68, 83-110 Tczew</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Andriollego 128, 05-400 Otwock</t>
+          <t>Gdańska 68, 83-110 Tczew</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4559,12 +4559,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Zielony Szafir Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Nieruchomości sp z oo</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1240507147</t>
+          <t>1288021143</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4574,27 +4574,27 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>240665529</t>
+          <t>288179524</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>86021405480</t>
+          <t>88021427482</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0000006992</t>
+          <t>0000065192</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ul. Żeromskiego 145/37, 26-600 Radom</t>
+          <t>85/7, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>ul. Żeromskiego 145/37, 26-600 Radom</t>
+          <t>85/7, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4621,12 +4621,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Zielony Tytan S.A.</t>
+          <t>Amber Inwestycje sp. z o. o.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1240586336</t>
+          <t>1288100339</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4636,27 +4636,27 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>240744714</t>
+          <t>298258747</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>87032106876</t>
+          <t>89032128878</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0000007089</t>
+          <t>0000065289</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ul Tumska 162, 09-402 Płock</t>
+          <t>ul Głęboka 102, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>ul Tumska 162, 09-402 Płock</t>
+          <t>ul Głęboka 102, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4683,12 +4683,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Zielony Uran SA</t>
+          <t>Amber Medycyna Sp. z o.o.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1240665521</t>
+          <t>1298179555</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4698,27 +4698,27 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>250823937</t>
+          <t>288337905</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>88042808226</t>
+          <t>90042830220</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0000007186</t>
+          <t>0000065386</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ulica Karmelicka 179, 31-128 Kraków</t>
+          <t>ulica Małachowskiego 119, 42-500 Będzin</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>ulica Karmelicka 179, 31-128 Kraków</t>
+          <t>ulica Małachowskiego 119, 42-500 Będzin</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4745,12 +4745,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Zielony Wektor S. A.</t>
+          <t>Amber Zdrowie SP Z O O</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1240744717</t>
+          <t>1288258715</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4760,27 +4760,27 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>240903093</t>
+          <t>288417099</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>89050709619</t>
+          <t>91050731613</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0000007283</t>
+          <t>0000065483</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>os. Na Stoku 16, 31-704 Kraków</t>
+          <t>Królowej Jadwigi 136, 88-100 Inowrocław</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>os. Na Stoku 16, 31-704 Kraków</t>
+          <t>Królowej Jadwigi 136, 88-100 Inowrocław</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4807,12 +4807,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Zielony Zefir Spółka Akcyjna</t>
+          <t>Amber Urody spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1240823902</t>
+          <t>1288337900</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4822,27 +4822,27 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>240982282</t>
+          <t>288496288</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>90061410960</t>
+          <t>92061432962</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>0000007380</t>
+          <t>0000065580</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ul. Krupówki 33/89, 34-500 Zakopane</t>
+          <t>ul. Wybickiego 153/59, 86-300 Grudziądz</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ul. Krupówki 33/89, 34-500 Zakopane</t>
+          <t>ul. Wybickiego 153/59, 86-300 Grudziądz</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4869,12 +4869,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Zielony Żubr sp. z o.o.</t>
+          <t>Amber Turystyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1240903096</t>
+          <t>1288417094</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4884,27 +4884,27 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>241061472</t>
+          <t>288575473</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>91072112357</t>
+          <t>93072134359</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0000007477</t>
+          <t>0000065677</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>50, 34-600 Mordarka</t>
+          <t>ul Czarnieckiego 170, 14-100 Ostróda</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>50, 34-600 Mordarka</t>
+          <t>ul Czarnieckiego 170, 14-100 Ostróda</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4931,12 +4931,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Zielony Sokół sp z oo</t>
+          <t>Amber Rozrywka S.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1240982285</t>
+          <t>1288496283</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4946,27 +4946,27 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>241140668</t>
+          <t>288654669</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>92082813706</t>
+          <t>94082835708</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>0000007574</t>
+          <t>0000065774</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>ulica Galicyjska 67, 32-087 Zielonki</t>
+          <t>ulica Warszawska 7, 11-500 Giżycko</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>ulica Galicyjska 67, 32-087 Zielonki</t>
+          <t>ulica Warszawska 7, 11-500 Giżycko</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4993,12 +4993,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Zielony Orzeł sp. z o. o.</t>
+          <t>Amber Gastronomia SA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1241061475</t>
+          <t>1288575479</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5008,27 +5008,27 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>241219855</t>
+          <t>288733854</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>93090715091</t>
+          <t>95090737093</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0000007671</t>
+          <t>0000065871</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>84, 32-003 Podłęże</t>
+          <t>24, 24-100 Puławy</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>84, 32-003 Podłęże</t>
+          <t>24, 24-100 Puławy</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5055,12 +5055,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>mBank</t>
+          <t>Instagram - Meta</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1241140660</t>
+          <t>1288654664</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5070,27 +5070,27 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>241299044</t>
+          <t>298813077</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>94101416442</t>
+          <t>96101438444</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>0000007768</t>
+          <t>0000065968</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ul. Wałowa 101/51, 33-100 Tarnów</t>
+          <t>ul. Staszica 41/21, 22-400 Zamość</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>ul. Wałowa 101/51, 33-100 Tarnów</t>
+          <t>ul. Staszica 41/21, 22-400 Zamość</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5117,12 +5117,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Zielony Barycz SP Z O O</t>
+          <t>Amber Tekstylia Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1241219858</t>
+          <t>1298733885</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5132,27 +5132,27 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>251378267</t>
+          <t>288892239</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>95112117838</t>
+          <t>97112139830</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>0000007865</t>
+          <t>0000066065</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ul Narutowicza 118, 90-135 Łódź</t>
+          <t>ul 3 Maja 58, 16-300 Augustów</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>ul Narutowicza 118, 90-135 Łódź</t>
+          <t>ul 3 Maja 58, 16-300 Augustów</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5179,12 +5179,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Zielony Noteć spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Motoryzacja sp. z o.o.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1241299047</t>
+          <t>1288813045</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5194,27 +5194,27 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>241457425</t>
+          <t>288971424</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>96122819189</t>
+          <t/>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0000007962</t>
+          <t>0000066162</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ulica os. Retkinia 135, 94-004 Łódź</t>
+          <t>ulica Kościuszki 75, 16-400 Suwałki</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>ulica os. Retkinia 135, 94-004 Łódź</t>
+          <t>ulica Kościuszki 75, 16-400 Suwałki</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5234,19 +5234,19 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-26-10</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Zielony Pilica Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Ubezpieczenia sp z oo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1241378232</t>
+          <t>1288892234</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5256,17 +5256,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>241536610</t>
+          <t>289050614</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>97010720570</t>
+          <t>99010742572</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0000008059</t>
+          <t>0000066259</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5303,12 +5303,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Zielony Narew S.A.</t>
+          <t>Amber Spawalnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1241457428</t>
+          <t>1298971455</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5318,27 +5318,27 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>241615806</t>
+          <t>289129801</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>98021421928</t>
+          <t>00221443925</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0000008156</t>
+          <t>0000066356</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ul. Długa 169/13, 95-100 Zgierz</t>
+          <t>ul. Długa 109/73, 49-300 Brzeg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>ul. Długa 169/13, 95-100 Zgierz</t>
+          <t>ul. Długa 109/73, 49-300 Brzeg</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5365,12 +5365,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Zielony Jodełka SA</t>
+          <t>Amber Ślusarstwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1241536613</t>
+          <t>1299050645</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5380,27 +5380,27 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>241694993</t>
+          <t>289208995</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>99032123315</t>
+          <t>01232145312</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0000008253</t>
+          <t>0000066453</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ul Rynek 6, 50-101 Wrocław</t>
+          <t>ul Rynek 126, 68-200 Żary</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>ul Rynek 6, 50-101 Wrocław</t>
+          <t>ul Rynek 126, 68-200 Żary</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5427,7 +5427,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Zielony Kaktus S. A.</t>
+          <t>Amber Krawiectwo SP Z O O</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5442,27 +5442,27 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>241774189</t>
+          <t>289288184</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>00242824660</t>
+          <t>02242846662</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>0000008350</t>
+          <t>0000066550</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ulica Jedności Narodowej 23, 50-260 Wrocław</t>
+          <t>143, 66-200 Świebodzin</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>ulica Jedności Narodowej 23, 50-260 Wrocław</t>
+          <t>143, 66-200 Świebodzin</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5489,12 +5489,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Zielony Szmaragd Spółka Akcyjna</t>
+          <t>Amber Ochrona spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1241694996</t>
+          <t>1289208990</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5504,27 +5504,27 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>241853374</t>
+          <t>299367409</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>01250726054</t>
+          <t>03250748056</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>0000008447</t>
+          <t>0000066647</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>os. Konstytucji 3 Maja 40, 58-540 Karpacz</t>
+          <t>Armii Krajowej 160, 78-100 Kołobrzeg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>os. Konstytucji 3 Maja 40, 58-540 Karpacz</t>
+          <t>Armii Krajowej 160, 78-100 Kołobrzeg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5544,19 +5544,19 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2018-03-05</t>
+          <t>2018-05-03</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Zielony Topaz sp. z o.o.</t>
+          <t>Amber Catering Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1241774181</t>
+          <t>1299288217</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5566,27 +5566,27 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>251932597</t>
+          <t>289446565</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>02261427402</t>
+          <t>04261449404</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>0000008544</t>
+          <t>0000066744</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>ul. Odrodzenia 57/65, 59-300 Lubin</t>
+          <t>ul. Piłsudskiego 177/35, 73-110 Stargard</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>ul. Odrodzenia 57/65, 59-300 Lubin</t>
+          <t>ul. Piłsudskiego 177/35, 73-110 Stargard</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5613,12 +5613,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Zielony Granit sp z oo</t>
+          <t>Amber Księgowość S.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1241853377</t>
+          <t>1289367375</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5628,27 +5628,27 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>252011787</t>
+          <t>289525750</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>03272128799</t>
+          <t>05272150794</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>0000008641</t>
+          <t>0000066841</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ul Słowackiego 74, 58-300 Wałbrzych</t>
+          <t>ul Mickiewicza 14, 27-600 Sandomierz</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>ul Słowackiego 74, 58-300 Wałbrzych</t>
+          <t>ul Mickiewicza 14, 27-600 Sandomierz</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5675,12 +5675,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Zielony Marmur sp. z o. o.</t>
+          <t>Bizon Budownictwo SA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1241932562</t>
+          <t>1289446560</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5690,27 +5690,27 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>242090949</t>
+          <t>289604946</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>04282830142</t>
+          <t>60082852140</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>0000008738</t>
+          <t>0000066938</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ulica Półwiejska 91, 61-888 Poznań</t>
+          <t>ulica Sienkiewicza 31, 27-400 Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>ulica Półwiejska 91, 61-888 Poznań</t>
+          <t>ulica Sienkiewicza 31, 27-400 Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5737,12 +5737,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Zielony Syrena Sp. z o.o.</t>
+          <t>Bizon Transport S. A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1242011752</t>
+          <t>1289525756</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5752,27 +5752,27 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>242170134</t>
+          <t>289684135</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>05290731535</t>
+          <t>61090753533</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>0000008835</t>
+          <t>0000067035</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>os. Bolesława Chrobrego 108, 60-681 Poznań</t>
+          <t>Chmielna 48, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>os. Bolesława Chrobrego 108, 60-681 Poznań</t>
+          <t>Chmielna 48, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5799,12 +5799,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Zielony Zodiak SP Z O O</t>
+          <t>Bizon Spedycja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1242090941</t>
+          <t>1289604941</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5814,27 +5814,27 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>242249321</t>
+          <t>289763320</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>60101432883</t>
+          <t>62101454885</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>0000008932</t>
+          <t>0000067132</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ul. Główny Rynek 125/27, 62-800 Kalisz</t>
+          <t>ul. Nowy Świat 65/87, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>ul. Główny Rynek 125/27, 62-800 Kalisz</t>
+          <t>ul. Nowy Świat 65/87, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5854,19 +5854,19 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-12-08</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Zielony Olimp spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Logistyka sp. z o.o.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1242170137</t>
+          <t>1289684130</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5876,27 +5876,27 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>242328517</t>
+          <t>289842516</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>61112134270</t>
+          <t>63112156272</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>0000009029</t>
+          <t>0000067229</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>ul Kaliska 142, 63-400 Ostrów Wielkopolski</t>
+          <t>ul os. Przyjaźń 82, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>ul Kaliska 142, 63-400 Ostrów Wielkopolski</t>
+          <t>ul os. Przyjaźń 82, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5923,12 +5923,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Zielony Zorza Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Handel sp z oo</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1242249324</t>
+          <t>1289763326</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5938,27 +5938,27 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>242407702</t>
+          <t>289921701</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>62122835629</t>
+          <t>64122857621</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>0000009126</t>
+          <t>0000067326</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>ulica Ogarna 159, 80-826 Gdańsk</t>
+          <t>ulica Jagiellońska 99, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>ulica Ogarna 159, 80-826 Gdańsk</t>
+          <t>ulica Jagiellońska 99, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5985,12 +5985,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Zielony Krokus S.A.</t>
+          <t>Bizon Usługi sp. z o. o.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1252328545</t>
+          <t>1289842511</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6000,27 +6000,27 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>252486929</t>
+          <t>300000924</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>63010737018</t>
+          <t>65010759010</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0000009223</t>
+          <t>0000067423</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>os. Jasień 176, 80-180 Gdańsk</t>
+          <t>Piłsudskiego 116, 05-270 Marki</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>os. Jasień 176, 80-180 Gdańsk</t>
+          <t>Piłsudskiego 116, 05-270 Marki</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6047,12 +6047,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Zielony Narcyz SA</t>
+          <t>Bizon Finanse Sp. z o.o.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1242407705</t>
+          <t>1289921707</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6062,27 +6062,27 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>242566085</t>
+          <t>290080089</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>64021438367</t>
+          <t>66021460362</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>0000009320</t>
+          <t>0000067520</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>ul. Bohaterów Monte Cassino 13/79, 81-759 Sopot</t>
+          <t>os. Andriollego 133/49, 05-400 Otwock</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>ul. Bohaterów Monte Cassino 13/79, 81-759 Sopot</t>
+          <t>os. Andriollego 133/49, 05-400 Otwock</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6109,12 +6109,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Zielony Giewont S. A.</t>
+          <t>Bizon Doradztwo SP Z O O</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1242486892</t>
+          <t>1290000893</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6124,27 +6124,27 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>242645270</t>
+          <t>290159276</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>65032139753</t>
+          <t>67032161758</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>0000009417</t>
+          <t>0000067617</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>30, 80-209 Chwaszczyno</t>
+          <t>ul Żeromskiego 150, 26-600 Radom</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>30, 80-209 Chwaszczyno</t>
+          <t>ul Żeromskiego 150, 26-600 Radom</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6171,12 +6171,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Zielony Rysy Spółka Akcyjna</t>
+          <t>Bizon Szkolenia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1242566088</t>
+          <t>1290080082</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6186,27 +6186,27 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>242724466</t>
+          <t>290238461</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>66042841106</t>
+          <t>68042863108</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>0000009514</t>
+          <t>0000067714</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 47, 40-096 Katowice</t>
+          <t>ulica Tumska 167, 09-402 Płock</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 47, 40-096 Katowice</t>
+          <t>ulica Tumska 167, 09-402 Płock</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6233,12 +6233,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Zielony Kasprowy sp. z o.o.</t>
+          <t>Bizon Media Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1242645273</t>
+          <t>1300159308</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6248,27 +6248,27 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>242803651</t>
+          <t>290317657</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>67050742490</t>
+          <t>69050764492</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>0000009611</t>
+          <t>0000067811</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>os. Paderewskiego 64, 40-282 Katowice</t>
+          <t>Karmelicka 4, 31-128 Kraków</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>os. Paderewskiego 64, 40-282 Katowice</t>
+          <t>Karmelicka 4, 31-128 Kraków</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6295,12 +6295,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PPHU Zielony Beskid</t>
+          <t>P.P.H.U. Bizon Reklama</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1242724469</t>
+          <t>1290238465</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6310,27 +6310,27 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>242882840</t>
+          <t>290396846</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>68061443848</t>
+          <t>70061465849</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>0000009708</t>
+          <t>0000067908</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>ul. Zwycięstwa 81/41, 44-100 Gliwice</t>
+          <t>ul. os. Na Stoku 21/11, 31-704 Kraków</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>ul. Zwycięstwa 81/41, 44-100 Gliwice</t>
+          <t>ul. os. Na Stoku 21/11, 31-704 Kraków</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6357,12 +6357,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Zielony Bieszczady sp. z o. o.</t>
+          <t>Bizon Marketing SA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1242803654</t>
+          <t>1290317650</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6372,17 +6372,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>242962036</t>
+          <t>290476031</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>69072145235</t>
+          <t>71072167236</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>0000009805</t>
+          <t>0000068005</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6419,12 +6419,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Zielony Karpaty Sp. z o.o.</t>
+          <t>Bizon Druk S. A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1242882843</t>
+          <t>1300396876</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6434,27 +6434,27 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>243041226</t>
+          <t>290555227</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>70082846584</t>
+          <t>72082868586</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>0000009902</t>
+          <t>0000068102</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>ulica Najświętszej Maryi Panny 115, 42-200 Częstochowa</t>
+          <t>55, 34-600 Mordarka</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>ulica Najświętszej Maryi Panny 115, 42-200 Częstochowa</t>
+          <t>55, 34-600 Mordarka</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6474,19 +6474,19 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-12-05</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Zielony Bałtyk SP Z O O</t>
+          <t>Bizon Informatyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1242962039</t>
+          <t>1290476035</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6496,27 +6496,27 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>243120411</t>
+          <t>290634412</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>71090747977</t>
+          <t>73090769979</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>0000009999</t>
+          <t>0000068199</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>11 Listopada 132, 43-300 Bielsko-Biała</t>
+          <t>Galicyjska 72, 32-087 Zielonki</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>11 Listopada 132, 43-300 Bielsko-Biała</t>
+          <t>Galicyjska 72, 32-087 Zielonki</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6543,12 +6543,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Zielony Sudety spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Oprogramowanie sp. z o.o.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1243041229</t>
+          <t>1290555220</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6558,27 +6558,27 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>243199602</t>
+          <t>290713608</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>72101449329</t>
+          <t>74101471324</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>0000010096</t>
+          <t>0000068296</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>149/3, 36-047 Niechobrz</t>
+          <t>89/63, 32-003 Podłęże</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>149/3, 36-047 Niechobrz</t>
+          <t>89/63, 32-003 Podłęże</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6605,12 +6605,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Niebieski Amber Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Rolnictwo sp z oo</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1243120414</t>
+          <t>1290634416</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6620,27 +6620,27 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>243278796</t>
+          <t>290792795</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>73112150718</t>
+          <t>75112172710</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>0000010193</t>
+          <t>0000068393</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>ul Franciszkańska 166, 37-700 Przemyśl</t>
+          <t>ul Wałowa 106, 33-100 Tarnów</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>ul Franciszkańska 166, 37-700 Przemyśl</t>
+          <t>ul Wałowa 106, 33-100 Tarnów</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6667,12 +6667,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Niebieski Bizon S.A.</t>
+          <t>Bizon Ogrodnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1243199605</t>
+          <t>1290713601</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6682,27 +6682,27 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>243357981</t>
+          <t>290871980</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>74122852069</t>
+          <t>76122874061</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>0000010290</t>
+          <t>0000068490</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 3, 38-500 Sanok</t>
+          <t>ulica Narutowicza 123, 90-135 Łódź</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 3, 38-500 Sanok</t>
+          <t>ulica Narutowicza 123, 90-135 Łódź</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6729,12 +6729,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Niebieski Canoyn SA</t>
+          <t>Bizon Produkcaj Sp. z o.o.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1243278799</t>
+          <t>1290792799</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6744,27 +6744,27 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>243437177</t>
+          <t>290951176</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>75010753457</t>
+          <t>77010775459</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>0000010387</t>
+          <t>0000068587</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Suraska 20, 15-422 Białystok</t>
+          <t>os. Retkinia 140, 94-004 Łódź</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Suraska 20, 15-422 Białystok</t>
+          <t>os. Retkinia 140, 94-004 Łódź</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6784,19 +6784,19 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Niebieski Delfin S. A.</t>
+          <t>Bizon Przemysł SP Z O O</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1243357984</t>
+          <t>1290871984</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6806,27 +6806,27 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>243516362</t>
+          <t>291030366</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>76021454805</t>
+          <t>78021476807</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>0000010484</t>
+          <t>0000068684</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>37/55, 16-030 Ogrodniczki</t>
+          <t>ul. Zamkowa 157/25, 95-200 Pabianice</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>37/55, 16-030 Ogrodniczki</t>
+          <t>ul. Zamkowa 157/25, 95-200 Pabianice</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6853,12 +6853,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Niebieski Echo Spółka Akcyjna</t>
+          <t>Bizon Ekologia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1253437207</t>
+          <t>1300951208</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6868,27 +6868,27 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>243595551</t>
+          <t>291109553</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>77032156193</t>
+          <t>79032178195</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>0000010581</t>
+          <t>0000068781</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>ul 3 Maja 54, 17-200 Hajnówka</t>
+          <t>ul Długa 174, 95-100 Zgierz</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>ul 3 Maja 54, 17-200 Hajnówka</t>
+          <t>ul Długa 174, 95-100 Zgierz</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6915,12 +6915,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Niebieski Falcon sp. z o.o.</t>
+          <t>Bizon Energetyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1243516365</t>
+          <t>1301030396</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6930,27 +6930,27 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>243674747</t>
+          <t>291188742</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>78042857542</t>
+          <t>80042879543</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>0000010678</t>
+          <t>0000068878</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>ulica os. LSM 71, 20-400 Lublin</t>
+          <t>ulica Rynek 11, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>ulica os. LSM 71, 20-400 Lublin</t>
+          <t>ulica Rynek 11, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6977,12 +6977,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Niebieski Gryf sp z oo</t>
+          <t>Bizon Instalacje S.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1243595554</t>
+          <t>1291109557</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6992,27 +6992,27 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>243753932</t>
+          <t>291267938</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>79050758935</t>
+          <t>81050780939</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>0000010775</t>
+          <t>0000068975</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>88, 24-120 Mięćmierz</t>
+          <t>Jedności Narodowej 28, 50-260 Wrocław</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>88, 24-120 Mięćmierz</t>
+          <t>Jedności Narodowej 28, 50-260 Wrocław</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7039,12 +7039,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Niebieski Horyzont sp. z o. o.</t>
+          <t>Bizon Nieruchomości SA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1253674775</t>
+          <t>1291188746</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7054,27 +7054,27 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>243833128</t>
+          <t>291347123</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>80061460287</t>
+          <t>82061482289</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>0000010872</t>
+          <t>0000069072</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>ul. Brzeska 105/17, 21-500 Biała Podlaska</t>
+          <t>ul. Konstytucji 3 Maja 45/77, 58-540 Karpacz</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>ul. Brzeska 105/17, 21-500 Biała Podlaska</t>
+          <t>ul. Konstytucji 3 Maja 45/77, 58-540 Karpacz</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7094,19 +7094,19 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2019-04-12</t>
+          <t>2019-12-04</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Niebieski Ikar Sp. z o.o.</t>
+          <t>Bizon Inwestycje S. A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1243753935</t>
+          <t>1291267931</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7116,27 +7116,27 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>243912313</t>
+          <t>291426319</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>81072161673</t>
+          <t>83072183675</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>0000010969</t>
+          <t>0000069169</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>ul Rynek Staromiejski 122, 87-100 Toruń</t>
+          <t>ul Odrodzenia 62, 59-300 Lubin</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>ul Rynek Staromiejski 122, 87-100 Toruń</t>
+          <t>ul Odrodzenia 62, 59-300 Lubin</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7163,12 +7163,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Niebieski Jantar SP Z O O</t>
+          <t>Bizon Medycyna Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1243833120</t>
+          <t>1291347127</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>243991502</t>
+          <t>291505504</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>82082863023</t>
+          <t>84082885025</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>ulica Mostowa 139, 85-110 Bydgoszcz</t>
+          <t>ulica Słowackiego 79, 58-300 Wałbrzych</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>ulica Mostowa 139, 85-110 Bydgoszcz</t>
+          <t>ulica Słowackiego 79, 58-300 Wałbrzych</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7225,12 +7225,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Niebieski Koral spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Zdrowie sp. z o.o.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1243912316</t>
+          <t>1291426312</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7240,27 +7240,27 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>244070690</t>
+          <t>291584691</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>83090764416</t>
+          <t>85090786418</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>0000011163</t>
+          <t>0000069363</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Stare Miasto 156, 10-026 Olsztyn</t>
+          <t>Półwiejska 96, 61-888 Poznań</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Stare Miasto 156, 10-026 Olsztyn</t>
+          <t>Półwiejska 96, 61-888 Poznań</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7287,12 +7287,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Niebieski Lotos Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Urody sp z oo</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1243991505</t>
+          <t>1291505508</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7302,27 +7302,27 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>244149888</t>
+          <t>291663887</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>84101465768</t>
+          <t>86101487760</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>0000011260</t>
+          <t>0000069460</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>os. Warszawska 173/69, 11-700 Mrągowo</t>
+          <t>ul. os. Bolesława Chrobrego 113/39, 60-681 Poznań</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>os. Warszawska 173/69, 11-700 Mrągowo</t>
+          <t>ul. os. Bolesława Chrobrego 113/39, 60-681 Poznań</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7349,12 +7349,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Niebieski Magnolia S.A.</t>
+          <t>Bizon Turystyka sp. z o. o.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1244070693</t>
+          <t>1291584695</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7364,27 +7364,27 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>244229073</t>
+          <t>291743072</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>85112167155</t>
+          <t>87112189157</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>0000011357</t>
+          <t>0000069557</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>ul Wojska Polskiego 10, 70-470 Szczecin</t>
+          <t>ul Główny Rynek 130, 62-800 Kalisz</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>ul Wojska Polskiego 10, 70-470 Szczecin</t>
+          <t>ul Główny Rynek 130, 62-800 Kalisz</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7411,12 +7411,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Niebieski Neon SA</t>
+          <t>Bizon Rozrywka Sp. z o.o.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1244149880</t>
+          <t>1291663880</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7426,17 +7426,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>244308269</t>
+          <t/>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>86122868504</t>
+          <t>88122890509</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>0000011454</t>
+          <t>0000069654</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -7473,12 +7473,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Niebieski Oaza S. A.</t>
+          <t>Bizon Gastronomia SP Z O O</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1244229076</t>
+          <t>1291743076</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7488,17 +7488,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t/>
+          <t>291901453</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>87010769893</t>
+          <t>89010791898</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>0000011551</t>
+          <t>0000069751</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7535,12 +7535,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>X - Twitter</t>
+          <t>mBank</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1244308261</t>
+          <t>1291822261</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7550,27 +7550,27 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>244466643</t>
+          <t>291980642</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>88021471245</t>
+          <t>90021493246</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>0000011648</t>
+          <t>0000069848</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>ul. Byczyńska 61/31, 46-200 Kluczbork</t>
+          <t>ul. os. Jasień 1/1, 80-180 Gdańsk</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>ul. Byczyńska 61/31, 46-200 Kluczbork</t>
+          <t>ul. os. Jasień 1/1, 80-180 Gdańsk</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7597,12 +7597,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Niebieski Rubin sp. z o.o.</t>
+          <t>Bizon Tekstylia Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1244387450</t>
+          <t>1291901457</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7612,27 +7612,27 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>244545839</t>
+          <t>292059834</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>89032172631</t>
+          <t>91032194632</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>0000011745</t>
+          <t>0000069945</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>ul Chrobrego 78, 66-400 Gorzów Wielkopolski</t>
+          <t>ul Bohaterów Monte Cassino 18, 81-759 Sopot</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>ul Chrobrego 78, 66-400 Gorzów Wielkopolski</t>
+          <t>ul Bohaterów Monte Cassino 18, 81-759 Sopot</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7659,12 +7659,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Niebieski Szafir sp z oo</t>
+          <t>Bizon Motoryzacja S.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1244466646</t>
+          <t>1291980646</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7674,27 +7674,27 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>244625024</t>
+          <t>302139052</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>90042873980</t>
+          <t>92042895982</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>0000011842</t>
+          <t>0000070042</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>ulica 30 Stycznia 95, 66-300 Międzyrzecz</t>
+          <t>35, 80-209 Chwaszczyno</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>ulica 30 Stycznia 95, 66-300 Międzyrzecz</t>
+          <t>35, 80-209 Chwaszczyno</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7721,12 +7721,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Niebieski Tytan sp. z o. o.</t>
+          <t>Bizon Ubezpieczenia SA</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1244545831</t>
+          <t>1292059838</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7736,27 +7736,27 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>254704247</t>
+          <t>292218215</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>91050775374</t>
+          <t>93050797376</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>0000011939</t>
+          <t>0000070139</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Paderewskiego 112, 25-004 Kielce</t>
+          <t>3 Maja 52, 40-096 Katowice</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Paderewskiego 112, 25-004 Kielce</t>
+          <t>3 Maja 52, 40-096 Katowice</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -7783,12 +7783,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Niebieski Uran Sp. z o.o.</t>
+          <t>Bizon Spawalnictwo S. A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1244625027</t>
+          <t>1292139023</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7798,27 +7798,27 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>244783409</t>
+          <t>292297404</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>92061476722</t>
+          <t>94061498724</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>0000012036</t>
+          <t>0000070236</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>ul. 1 Maja 129/83, 28-100 Busko-Zdrój</t>
+          <t>ul. os. Paderewskiego 69/53, 40-282 Katowice</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>ul. 1 Maja 129/83, 28-100 Busko-Zdrój</t>
+          <t>ul. os. Paderewskiego 69/53, 40-282 Katowice</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7845,12 +7845,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Niebieski Wektor SP Z O O</t>
+          <t>Bizon Ślusarstwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1244704212</t>
+          <t>1292218219</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7860,27 +7860,27 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>244862592</t>
+          <t>292376598</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>93072178119</t>
+          <t>95072100114</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>0000012133</t>
+          <t>0000070333</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>ul Marszałkowska 146, 00-590 Warszawa</t>
+          <t>os. Zwycięstwa 86, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>ul Marszałkowska 146, 00-590 Warszawa</t>
+          <t>os. Zwycięstwa 86, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7907,12 +7907,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Niebieski Zefir spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Krawiectwo sp. z o.o.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1244783401</t>
+          <t>1292297408</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7922,27 +7922,27 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>244941788</t>
+          <t>292455783</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>94082879469</t>
+          <t>96082801464</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>0000012230</t>
+          <t>0000070430</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>ulica Krakowskie Przedmieście 163, 00-071 Warszawa</t>
+          <t>ulica Bocheńskiego 103, 43-100 Tychy</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>ulica Krakowskie Przedmieście 163, 00-071 Warszawa</t>
+          <t>ulica Bocheńskiego 103, 43-100 Tychy</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7969,12 +7969,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Niebieski Żubr Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Ochrona sp z oo</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1244862595</t>
+          <t>1292376591</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7984,27 +7984,27 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>245020978</t>
+          <t>292534979</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>95090780855</t>
+          <t>97090702857</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>0000012327</t>
+          <t>0000070527</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Floriańska 180, 31-019 Kraków</t>
+          <t>Najświętszej Maryi Panny 120, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Floriańska 180, 31-019 Kraków</t>
+          <t>Najświętszej Maryi Panny 120, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8024,19 +8024,19 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2022-07-05</t>
+          <t>2022-05-07</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Niebieski Sokół S.A.</t>
+          <t>Bizon Catering sp. z o. o.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1244941780</t>
+          <t>1292455787</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8046,27 +8046,27 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>245100163</t>
+          <t>292614164</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>06101482207</t>
+          <t>98101404209</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>0000012424</t>
+          <t>0000070624</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>ul. Długa 17/45, 31-147 Kraków</t>
+          <t>ul. 11 Listopada 137/15, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>ul. Długa 17/45, 31-147 Kraków</t>
+          <t>ul. 11 Listopada 137/15, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8093,12 +8093,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Niebieski Orzeł SA</t>
+          <t>Bizon Księgowość Sp. z o.o.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1245020970</t>
+          <t>1292534972</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8108,27 +8108,27 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>245179354</t>
+          <t>292693353</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>97112183594</t>
+          <t>09112105596</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>0000012521</t>
+          <t>0000070721</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>ul Piotrkowska 34, 90-102 Łódź</t>
+          <t>154, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>ul Piotrkowska 34, 90-102 Łódź</t>
+          <t>154, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8155,12 +8155,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Niebieski Kormoran S. A.</t>
+          <t>Canyon Budownictwo SP Z O O</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1245100166</t>
+          <t>1292614168</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8170,27 +8170,27 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>255258577</t>
+          <t>292772549</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>98122884943</t>
+          <t>00322806940</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>0000012618</t>
+          <t>0000070818</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>ulica Zachodnia 51, 90-402 Łódź</t>
+          <t>ulica Franciszkańska 171, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>ulica Zachodnia 51, 90-402 Łódź</t>
+          <t>ulica Franciszkańska 171, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8217,12 +8217,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Niebieski Barycz Spółka Akcyjna</t>
+          <t>Canyon Transport spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1245179357</t>
+          <t>1292693357</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8232,27 +8232,27 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>245337735</t>
+          <t>292851734</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>99010786332</t>
+          <t>01210708339</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0000012715</t>
+          <t>0000070915</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Świdnicka 68, 50-066 Wrocław</t>
+          <t>Kościuszki 8, 38-500 Sanok</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Świdnicka 68, 50-066 Wrocław</t>
+          <t>Kościuszki 8, 38-500 Sanok</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8279,12 +8279,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Niebieski Noteć sp. z o.o.</t>
+          <t>Canyon Spedycja Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1245258542</t>
+          <t>1292772542</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8294,27 +8294,27 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>245416920</t>
+          <t>302930952</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>00221487686</t>
+          <t>02221409688</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>0000012812</t>
+          <t>0000071012</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>ul. Legnicka 85/7, 54-203 Wrocław</t>
+          <t>ul. Suraska 25/67, 15-422 Białystok</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>ul. Legnicka 85/7, 54-203 Wrocław</t>
+          <t>ul. Suraska 25/67, 15-422 Białystok</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8341,12 +8341,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Niebieski Pilica sp z oo</t>
+          <t>Canyon Logistyka S.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1245337738</t>
+          <t>1292851738</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8356,27 +8356,27 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>255496147</t>
+          <t>303010142</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>01232189073</t>
+          <t>03232111078</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>0000012909</t>
+          <t>0000071109</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>ul Święty Marcin 102, 61-806 Poznań</t>
+          <t>42, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>ul Święty Marcin 102, 61-806 Poznań</t>
+          <t>42, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8403,12 +8403,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Niebieski Narew sp. z o. o.</t>
+          <t>Canyon Handel SA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1245416923</t>
+          <t>1292930923</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8418,27 +8418,27 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>245575305</t>
+          <t>293089300</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>02242890425</t>
+          <t>04242812427</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>0000013006</t>
+          <t>0000071206</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>ulica Głogowska 119, 60-734 Poznań</t>
+          <t>ulica 3 Maja 59, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>ulica Głogowska 119, 60-734 Poznań</t>
+          <t>ulica 3 Maja 59, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8465,12 +8465,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Niebieski Jodełka Sp. z o.o.</t>
+          <t>Canyon Usługi S. A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1245496112</t>
+          <t>1293010113</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8480,27 +8480,27 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>245654499</t>
+          <t>293168494</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>03250791818</t>
+          <t>05250713810</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>0000013103</t>
+          <t>0000071303</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Długa 136, 80-831 Gdańsk</t>
+          <t>os. LSM 76, 20-400 Lublin</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Długa 136, 80-831 Gdańsk</t>
+          <t>os. LSM 76, 20-400 Lublin</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8527,12 +8527,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Niebieski Kaktus SP Z O O</t>
+          <t>Canyon Finanse Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1245575308</t>
+          <t>1293089304</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8542,27 +8542,27 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>245733684</t>
+          <t>303247714</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>04261493168</t>
+          <t>60061415166</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>0000013200</t>
+          <t>0000071400</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>ul. Grunwaldzka 153/59, 80-236 Gdańsk</t>
+          <t>93/29, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>ul. Grunwaldzka 153/59, 80-236 Gdańsk</t>
+          <t>93/29, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8589,12 +8589,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Niebieski Szmaragd spółka z ograniczoną odpowiedzialnością</t>
+          <t>Canyon Doradztwo sp. z o.o.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1245654491</t>
+          <t>1293168498</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8604,17 +8604,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>255812909</t>
+          <t>293326875</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>05272194554</t>
+          <t>61072116552</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>0000013297</t>
+          <t>0000071497</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -8651,12 +8651,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Niebieski Topaz Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Canyon Szkolenia sp z oo</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1245733687</t>
+          <t>1293247683</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8666,27 +8666,27 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>245892069</t>
+          <t>293406060</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>60082895909</t>
+          <t>62082817901</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>0000013394</t>
+          <t>0000071594</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>ulica Wyszyńskiego 7, 70-200 Szczecin</t>
+          <t>ulica Rynek Staromiejski 127, 87-100 Toruń</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>ulica Wyszyńskiego 7, 70-200 Szczecin</t>
+          <t>ulica Rynek Staromiejski 127, 87-100 Toruń</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8713,12 +8713,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Niebieski Granit S.A.</t>
+          <t>Canyon Media sp. z o. o.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2245812872</t>
+          <t>2293326879</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8728,27 +8728,27 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>245971254</t>
+          <t>303485282</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>61090797294</t>
+          <t>63090719296</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>0000013491</t>
+          <t>0000071691</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Mariacka 24, 40-014 Katowice</t>
+          <t>Mostowa 144, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Mariacka 24, 40-014 Katowice</t>
+          <t>Mostowa 144, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8775,12 +8775,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>P.P.H.U. Niebieski Marmur</t>
+          <t>PPHU Canyon Reklama</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1245892061</t>
+          <t>1293406064</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8790,27 +8790,27 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>246050444</t>
+          <t>293564445</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>62101498645</t>
+          <t>64101420640</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>0000013588</t>
+          <t>0000071788</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>ul. Warszawska 41/21, 40-009 Katowice</t>
+          <t>ul. Stare Miasto 161/81, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>ul. Warszawska 41/21, 40-009 Katowice</t>
+          <t>ul. Stare Miasto 161/81, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8837,12 +8837,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Niebieski Syrena S. A.</t>
+          <t>Canyon Marketing SP Z O O</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1245971257</t>
+          <t>1293485253</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8852,27 +8852,27 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>246129631</t>
+          <t>293643630</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>63112100035</t>
+          <t>65112122037</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>0000013685</t>
+          <t>0000071885</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 58, 20-002 Lublin</t>
+          <t>ul Warszawska 178, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 58, 20-002 Lublin</t>
+          <t>ul Warszawska 178, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8899,12 +8899,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Niebieski Zodiak Spółka Akcyjna</t>
+          <t>Canyon Druk spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1246050447</t>
+          <t>1293564449</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8914,27 +8914,27 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>246208827</t>
+          <t>293722826</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>64122801385</t>
+          <t>66122823387</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>0000013782</t>
+          <t>0000071982</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>ulica Narutowicza 75, 20-004 Lublin</t>
+          <t>ulica Wojska Polskiego 15, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>ulica Narutowicza 75, 20-004 Lublin</t>
+          <t>ulica Wojska Polskiego 15, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8961,12 +8961,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Niebieski Olimp sp. z o.o.</t>
+          <t>Canyon Informatyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1246129634</t>
+          <t>1293643634</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8976,27 +8976,27 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>246288016</t>
+          <t>293802011</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>65010702773</t>
+          <t>67010724775</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>0000013879</t>
+          <t>0000072079</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lipowa 92, 15-424 Białystok</t>
+          <t>Monte Cassino 32, 72-600 Świnoujście</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Lipowa 92, 15-424 Białystok</t>
+          <t>Monte Cassino 32, 72-600 Świnoujście</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9023,12 +9023,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Niebieski Zorza sp z oo</t>
+          <t>Canyon Oprogramowanie S.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1256208855</t>
+          <t>1303722856</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9038,27 +9038,27 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>246367201</t>
+          <t>293881200</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>66021404122</t>
+          <t>68021426124</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>0000013976</t>
+          <t>0000072176</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 109/73, 15-092 Białystok</t>
+          <t>ul. Rynek 49/43, 45-015 Opole</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 109/73, 15-092 Białystok</t>
+          <t>ul. Rynek 49/43, 45-015 Opole</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9085,12 +9085,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Niebieski Krokus sp. z o. o.</t>
+          <t>Canyon Rolnictwo SA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1246288019</t>
+          <t>1293802015</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9100,27 +9100,27 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>246446395</t>
+          <t>293960394</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>67032105518</t>
+          <t>69032127510</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>0000014073</t>
+          <t>0000072273</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>os. Gdańska 126, 85-005 Bydgoszcz</t>
+          <t>ul Byczyńska 66, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>os. Gdańska 126, 85-005 Bydgoszcz</t>
+          <t>ul Byczyńska 66, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9147,12 +9147,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Niebieski Narcyz Sp. z o.o.</t>
+          <t>Canyon Ogrodnictwo S. A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1246367204</t>
+          <t>1293881204</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9162,27 +9162,27 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>246525580</t>
+          <t>294039586</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>68042806868</t>
+          <t>70042828869</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>0000014170</t>
+          <t>0000072370</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>ulica Dworcowa 143, 85-009 Bydgoszcz</t>
+          <t>ulica Chrobrego 83, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>ulica Dworcowa 143, 85-009 Bydgoszcz</t>
+          <t>ulica Chrobrego 83, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9209,12 +9209,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Niebieski Giewont SP Z O O</t>
+          <t>Canyon Produkcja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1246446398</t>
+          <t>1293960398</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9224,27 +9224,27 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>246604776</t>
+          <t>294118771</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>69050708252</t>
+          <t>71050730256</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>0000014267</t>
+          <t>0000072467</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Szeroka 160, 87-100 Toruń</t>
+          <t>30 Stycznia 100, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Szeroka 160, 87-100 Toruń</t>
+          <t>30 Stycznia 100, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9264,19 +9264,19 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2018-03-05</t>
+          <t>2018-05-03</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Niebieski Rysy spółka z ograniczoną odpowiedzialnością</t>
+          <t>Canyon Przemysł sp. z o.o.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1246525583</t>
+          <t>1304039618</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9286,27 +9286,27 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>246683965</t>
+          <t>294197960</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>70061409609</t>
+          <t>72061431604</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>0000014364</t>
+          <t>0000072564</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>ul. Chełmińska 177/35, 87-100 Toruń</t>
+          <t>ul. Paderewskiego 117/5, 25-004 Kielce</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>ul. Chełmińska 177/35, 87-100 Toruń</t>
+          <t>ul. Paderewskiego 117/5, 25-004 Kielce</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9333,12 +9333,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Niebieski Kasprowy Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Canyon Ekologia sp z oo</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1246604779</t>
+          <t>1294118775</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9348,27 +9348,27 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>246763150</t>
+          <t>294277156</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>71072110999</t>
+          <t>73072132991</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>0000014461</t>
+          <t>0000072661</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>ul 3 Maja 14, 35-030 Rzeszów</t>
+          <t>ul 1 Maja 134, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>ul 3 Maja 14, 35-030 Rzeszów</t>
+          <t>ul 1 Maja 134, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9395,12 +9395,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Amber Budownictwo S.A.</t>
+          <t>Canyon Energetyka sp. z o. o.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1246683968</t>
+          <t>1294197964</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9410,27 +9410,27 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>246842346</t>
+          <t>294356341</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>72082812349</t>
+          <t>74082834341</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>0000014558</t>
+          <t>0000072758</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>ulica Piłsudskiego 31, 35-074 Rzeszów</t>
+          <t>ulica Marszałkowska 151, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>ulica Piłsudskiego 31, 35-074 Rzeszów</t>
+          <t>ulica Marszałkowska 151, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9457,12 +9457,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Amber Transport SA</t>
+          <t>Canyon Instalacje Sp. z o.o.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1246763153</t>
+          <t>1304277186</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9472,27 +9472,27 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>246921531</t>
+          <t>294435537</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>73090713732</t>
+          <t>75090735734</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>0000014655</t>
+          <t>0000072855</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Sienkiewicza 48, 25-007 Kielce</t>
+          <t>Krakowskie Przedmieście 168, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Sienkiewicza 48, 25-007 Kielce</t>
+          <t>Krakowskie Przedmieście 168, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9519,12 +9519,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Amber Spedycja S. A.</t>
+          <t>Canyon Nieruchomości SP Z O O</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1246842349</t>
+          <t>1294356345</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9534,27 +9534,27 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>247000721</t>
+          <t>294514722</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>74101415085</t>
+          <t>76101437087</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>0000014752</t>
+          <t>0000072952</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>ul. Warszawska 65/87, 25-512 Kielce</t>
+          <t>ul. Floriańska 5/57, 31-019 Kraków</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>ul. Warszawska 65/87, 25-512 Kielce</t>
+          <t>ul. Floriańska 5/57, 31-019 Kraków</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9574,19 +9574,19 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-04-10</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Amber Logistyka Spółka Akcyjna</t>
+          <t>Canyon Inwestycje spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1246921534</t>
+          <t>1294435530</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9596,27 +9596,27 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>247079912</t>
+          <t>294593911</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>75112116471</t>
+          <t>77112138473</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>0000014849</t>
+          <t>0000073049</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>ul Kościuszki 82, 10-504 Olsztyn</t>
+          <t>ul Długa 22, 31-147 Kraków</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>ul Kościuszki 82, 10-504 Olsztyn</t>
+          <t>ul Długa 22, 31-147 Kraków</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9643,12 +9643,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Amber Handel sp. z o.o.</t>
+          <t>Canyon Medycyna Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>1247000724</t>
+          <t>1294514726</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9658,27 +9658,27 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>247159108</t>
+          <t>294673107</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>76122817820</t>
+          <t>78122839822</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>0000014946</t>
+          <t>0000073146</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>ulica Dąbrowszczaków 99, 10-540 Olsztyn</t>
+          <t>os. Piotrkowska 39, 90-102 Łódź</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>ulica Dąbrowszczaków 99, 10-540 Olsztyn</t>
+          <t>os. Piotrkowska 39, 90-102 Łódź</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9705,12 +9705,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Amber Usługi sp z oo</t>
+          <t>Canyon Zdrowie S.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1247079915</t>
+          <t>1294593915</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9720,27 +9720,27 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>247238291</t>
+          <t>294752290</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>77010719219</t>
+          <t>79010741214</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>0000015043</t>
+          <t>0000073243</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Krakowska 116, 45-018 Opole</t>
+          <t>Zachodnia 56, 90-402 Łódź</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Krakowska 116, 45-018 Opole</t>
+          <t>Zachodnia 56, 90-402 Łódź</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9767,12 +9767,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Amber Finanse sp. z o. o.</t>
+          <t>Canyon Urody SA</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1247159100</t>
+          <t>1294673100</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9782,27 +9782,27 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>247317487</t>
+          <t>294831486</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>78021420561</t>
+          <t>80021442562</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>0000015140</t>
+          <t>0000073340</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>ul. Ozimska 133/49, 45-057 Opole</t>
+          <t>ul. Świdnicka 73/19, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>ul. Ozimska 133/49, 45-057 Opole</t>
+          <t>ul. Świdnicka 73/19, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9829,12 +9829,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Amber Doradztwo pS. z o.o.</t>
+          <t>Canyon Turystyka S. .</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1247238294</t>
+          <t>1294752294</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9844,27 +9844,27 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>247396676</t>
+          <t>294910671</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>79032121957</t>
+          <t>81032143958</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>0000015237</t>
+          <t>0000073437</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>ul Bohaterów Westerplatte 150, 65-034 Zielona Góra</t>
+          <t>ul Legnicka 90, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>ul Bohaterów Westerplatte 150, 65-034 Zielona Góra</t>
+          <t>ul Legnicka 90, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9891,12 +9891,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Amber Szkolenia SP Z O O</t>
+          <t>Canyon Rozrywka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1257317517</t>
+          <t>1304831518</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9906,27 +9906,27 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>247475861</t>
+          <t>294989862</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>80042823306</t>
+          <t>82042845308</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>0000015334</t>
+          <t>0000073534</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>ulica Kupiecka 167, 65-058 Zielona Góra</t>
+          <t>ulica Święty Marcin 107, 61-806 Poznań</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>ulica Kupiecka 167, 65-058 Zielona Góra</t>
+          <t>ulica Święty Marcin 107, 61-806 Poznań</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9953,12 +9953,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Amber Media spółka z ograniczoną odpowiedzialnością</t>
+          <t>Canyon Gastronomia sp. z o.o.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>1247396679</t>
+          <t>1294910675</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9968,27 +9968,27 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>247555057</t>
+          <t>295069052</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>81050724690</t>
+          <t>83050746692</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>0000015431</t>
+          <t>0000073631</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Świętojańska 4, 81-372 Gdynia</t>
+          <t>Głogowska 124, 60-734 Poznań</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Świętojańska 4, 81-372 Gdynia</t>
+          <t>Głogowska 124, 60-734 Poznań</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10015,12 +10015,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Facebook - Meta</t>
+          <t>X - Twitter</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1247475864</t>
+          <t>1294989866</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10030,27 +10030,27 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>247634242</t>
+          <t>295148248</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>82061426049</t>
+          <t>84061448041</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>0000015528</t>
+          <t>0000073728</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>ul. 10 Lutego 21/11, 81-364 Gdynia</t>
+          <t>ul. Długa 141/71, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>ul. 10 Lutego 21/11, 81-364 Gdynia</t>
+          <t>ul. Długa 141/71, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10077,12 +10077,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Amber Marketing S.A.</t>
+          <t>Canyon Tekstylia sp. z o. o.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>1257555085</t>
+          <t>1295069056</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10092,27 +10092,27 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>247713438</t>
+          <t>295227433</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>83072127435</t>
+          <t>85072149437</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>0000015625</t>
+          <t>0000073825</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>ul Bolesława Prusa 38, 05-800 Pruszków</t>
+          <t>ul Grunwaldzka 158, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>ul Bolesława Prusa 38, 05-800 Pruszków</t>
+          <t>ul Grunwaldzka 158, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10139,12 +10139,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Amber Druk SA</t>
+          <t>Canyon Motoryzacja Sp. z o.o.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>1247634245</t>
+          <t>1295148241</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10154,27 +10154,27 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>247792627</t>
+          <t>295306629</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>84082828785</t>
+          <t>86082850780</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>0000015722</t>
+          <t>0000073922</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 55, 05-500 Piaseczno</t>
+          <t>ulica Jagiellońska 175, 70-435 Szczecin</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 55, 05-500 Piaseczno</t>
+          <t>ulica Jagiellońska 175, 70-435 Szczecin</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10201,12 +10201,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Amber Informatyka S. A.</t>
+          <t>Canyon Ubezpieczenia SP Z O O</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1247713430</t>
+          <t>1295227437</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10216,27 +10216,27 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>247871812</t>
+          <t>295385818</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>85090730172</t>
+          <t>87090752174</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>0000015819</t>
+          <t>0000074019</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Sienkiewicza 72, 32-020 Wieliczka</t>
+          <t>Wyszyńskiego 12, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Sienkiewicza 72, 32-020 Wieliczka</t>
+          <t>Wyszyńskiego 12, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10263,12 +10263,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Amber Oprogramowanie Spółka Akcyjna</t>
+          <t>Canyon Spawalnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1257792655</t>
+          <t>1295306622</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10278,27 +10278,27 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>247951008</t>
+          <t>295465003</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>86101431523</t>
+          <t>88101453525</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>0000015916</t>
+          <t>0000074116</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>ul. Dąbrowskiego 89/63, 32-600 Oświęcim</t>
+          <t>ul. Mariacka 29/33, 40-014 Katowice</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>ul. Dąbrowskiego 89/63, 32-600 Oświęcim</t>
+          <t>ul. Mariacka 29/33, 40-014 Katowice</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10325,12 +10325,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Amber Rolnictwo sp. z o.o.</t>
+          <t>Canyon Ślusarstwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>1247871815</t>
+          <t>1295385811</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10340,27 +10340,27 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>248030196</t>
+          <t>295544197</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>87112132919</t>
+          <t>89112154911</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>0000016013</t>
+          <t>0000074213</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>ul Rynek 106, 38-400 Krosno</t>
+          <t>ul Warszawska 46, 40-009 Katowice</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>ul Rynek 106, 38-400 Krosno</t>
+          <t>ul Warszawska 46, 40-009 Katowice</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10387,12 +10387,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Amber Ogrodnictwo sp z oo</t>
+          <t>Canyon Krawiectwo S.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>1247951000</t>
+          <t>1295465007</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10402,27 +10402,27 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>248109383</t>
+          <t>295623382</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>88122834260</t>
+          <t>90122856261</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>000001611</t>
+          <t>000007431</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>ulica Mickiewicza 123, 39-300 Mielec</t>
+          <t>ulica Krakowskie Przedmieście 63, 20-002 Lublin</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>ulica Mickiewicza 123, 39-300 Mielec</t>
+          <t>ulica Krakowskie Przedmieście 63, 20-002 Lublin</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10449,12 +10449,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Amber Produkcja sp. z o. o.</t>
+          <t>Canyon Ochrona SA</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>1248030199</t>
+          <t>1295544190</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10464,27 +10464,27 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>248188572</t>
+          <t>295702578</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>89010735658</t>
+          <t>91010757659</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>0000016207</t>
+          <t>0000074407</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Długa 140, 58-100 Świdnica</t>
+          <t>Narutowicza 80, 20-004 Lublin</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Długa 140, 58-100 Świdnica</t>
+          <t>Narutowicza 80, 20-004 Lublin</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10504,19 +10504,19 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Amber Przemysł Sp. z o.o.</t>
+          <t>Canyon Catering S. A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>1248109386</t>
+          <t>1295623386</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10526,27 +10526,27 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>248267768</t>
+          <t>295781767</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>90021437006</t>
+          <t>92021459008</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>0000016304</t>
+          <t>0000074504</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>157/25, 57-300 Kłodzko</t>
+          <t>ul. Lipowa 97/85, 15-424 Białystok</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>157/25, 57-300 Kłodzko</t>
+          <t>ul. Lipowa 97/85, 15-424 Białystok</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10573,12 +10573,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Amber Ekologia SP Z O O</t>
+          <t>Canyon Księgowość Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>1248188575</t>
+          <t>1295702571</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10588,27 +10588,27 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>248346953</t>
+          <t>295860952</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>91032138393</t>
+          <t>93032160398</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>0000016401</t>
+          <t>0000074601</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>ul Chrobrego 174, 62-200 Gniezno</t>
+          <t>ul Sienkiewicza 114, 15-092 Białystok</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>ul Chrobrego 174, 62-200 Gniezno</t>
+          <t>ul Sienkiewicza 114, 15-092 Białystok</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10635,12 +10635,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Amber Energetyka spółka z ograniczoną odpowiedzialnością</t>
+          <t>Astra Group sp. z o.o.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>1248267760</t>
+          <t>1295781760</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10650,27 +10650,27 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>248426149</t>
+          <t>295940148</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>92042839742</t>
+          <t>94042861747</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>0000016498</t>
+          <t>0000074698</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>ulica Słowiańska 11, 64-100 Leszno</t>
+          <t>ulica Gdańska 131, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>ulica Słowiańska 11, 64-100 Leszno</t>
+          <t>ulica Gdańska 131, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10697,12 +10697,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Amber Instalacje Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Astra Systems sp z oo</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>1248346956</t>
+          <t>1295860956</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10712,27 +10712,27 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>248505334</t>
+          <t>306019362</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>93050741139</t>
+          <t>95050763131</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>0000016595</t>
+          <t>0000074795</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Gdańska 28, 83-110 Tczew</t>
+          <t>Dworcowa 148, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Gdańska 28, 83-110 Tczew</t>
+          <t>Dworcowa 148, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -10759,12 +10759,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Amber Nieruchomości S.A.</t>
+          <t>Astra Holding sp. z o. o.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>1248426141</t>
+          <t>1295940141</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10774,27 +10774,27 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>248584523</t>
+          <t>296098529</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>94061442488</t>
+          <t>96061464480</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>0000016692</t>
+          <t>0000074892</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>ul. Sobieskiego 45/77, 84-200 Wejherowo</t>
+          <t>ul. Szeroka 165/47, 87-100 Toruń</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>ul. Sobieskiego 45/77, 84-200 Wejherowo</t>
+          <t>ul. Szeroka 165/47, 87-100 Toruń</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10814,19 +10814,19 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2019-04-12</t>
+          <t>2019-12-04</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Amber Inwestycje SA</t>
+          <t>Astra Partners Sp. z o.o.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>1248505337</t>
+          <t>1296019333</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10836,27 +10836,27 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>248663719</t>
+          <t>296177714</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>95072143874</t>
+          <t>97072165876</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>0000016789</t>
+          <t>0000074989</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>ul Głęboka 62, 43-400 Cieszyn</t>
+          <t>ul Chełmińska 2, 87-100 Toruń</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>ul Głęboka 62, 43-400 Cieszyn</t>
+          <t>ul Chełmińska 2, 87-100 Toruń</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10883,12 +10883,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Amber Medycyna S. A.</t>
+          <t>Astra Polska SP Z O O</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>1248584526</t>
+          <t>1296098522</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10898,27 +10898,27 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>248742904</t>
+          <t>306256932</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>96082845224</t>
+          <t>98082867226</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>0000016886</t>
+          <t>0000075086</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>os. Małachowskiego 79, 42-500 Będzin</t>
+          <t>ulica 3 Maja 19, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>os. Małachowskiego 79, 42-500 Będzin</t>
+          <t>ulica 3 Maja 19, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10945,12 +10945,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Amber Zdrowie Spółka Akcyjna</t>
+          <t>Astra Enterprise spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>1248663711</t>
+          <t>1296177718</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10960,27 +10960,27 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>248822098</t>
+          <t>296336093</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>97090746617</t>
+          <t>99090768619</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>0000016983</t>
+          <t>0000075183</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Królowej Jadwigi 96, 88-100 Inowrocław</t>
+          <t>Piłsudskiego 36, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Królowej Jadwigi 96, 88-100 Inowrocław</t>
+          <t>Piłsudskiego 36, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11007,12 +11007,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Amber Urody sp. z o.o.</t>
+          <t>Astra Network Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>1248742907</t>
+          <t>1296256903</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11022,27 +11022,27 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>248901283</t>
+          <t>296415289</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>98101447969</t>
+          <t>00301469966</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>0000017080</t>
+          <t>0000075280</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>ul. Wybickiego 113/39, 86-300 Grudziądz</t>
+          <t>ul. Sienkiewicza 53/9, 25-007 Kielce</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>ul. Wybickiego 113/39, 86-300 Grudziądz</t>
+          <t>ul. Sienkiewicza 53/9, 25-007 Kielce</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11069,12 +11069,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Amber Turystyka sp z oo</t>
+          <t>Apex Group S.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>1248822090</t>
+          <t>1296336097</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11084,27 +11084,27 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>248980472</t>
+          <t>296494478</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>99112149356</t>
+          <t>01312171356</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>0000017177</t>
+          <t>0000075377</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>ul Czarnieckiego 130, 14-100 Ostróda</t>
+          <t>ul Warszawska 70, 25-512 Kielce</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>ul Czarnieckiego 130, 14-100 Ostróda</t>
+          <t>ul Warszawska 70, 25-512 Kielce</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11124,19 +11124,19 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
+          <t>2022-06-10</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Amber Rozrywka sp. z o. o.</t>
+          <t>Apex Systems SA</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>1248901286</t>
+          <t>1296415282</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11146,27 +11146,27 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>249059664</t>
+          <t>296573663</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>00322850703</t>
+          <t>02322872705</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>0000017274</t>
+          <t>0000075474</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>ulica Warszawska 147, 11-500 Giżycko</t>
+          <t>ulica Kościuszki 87, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>ulica Warszawska 147, 11-500 Giżycko</t>
+          <t>ulica Kościuszki 87, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11193,12 +11193,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Amber Gastronomia Sp. z o.o.</t>
+          <t>Apex Holding S. A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>1248980475</t>
+          <t>1296494471</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11208,27 +11208,27 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>259138887</t>
+          <t>296652859</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>01210752093</t>
+          <t>03210774095</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>0000017371</t>
+          <t>0000075571</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Lubelska 164, 24-100 Puławy</t>
+          <t>Dąbrowszczaków 104, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Lubelska 164, 24-100 Puławy</t>
+          <t>Dąbrowszczaków 104, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11255,12 +11255,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PPHU Amber Moda</t>
+          <t>P.P.H.U. Apex Partners</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>1249059667</t>
+          <t>1296573667</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11270,27 +11270,27 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>249218045</t>
+          <t>296732044</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>02221453441</t>
+          <t>04221475443</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>0000017468</t>
+          <t>0000075668</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>ul. Staszica 1/1, 22-400 Zamość</t>
+          <t>ul. Krakowska 121/61, 45-018 Opole</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>ul. Staszica 1/1, 22-400 Zamość</t>
+          <t>ul. Krakowska 121/61, 45-018 Opole</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11317,12 +11317,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Amber Tekstylia spółka z ograniczoną odpowiedzialnością</t>
+          <t>Apex Polska sp. z o.o.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>1249138852</t>
+          <t>1296652852</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11332,27 +11332,27 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>249297234</t>
+          <t>306811262</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>03232154837</t>
+          <t>05232176839</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>0000017565</t>
+          <t>0000075765</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>ul 3 Maja 18, 16-300 Augustów</t>
+          <t>ul Ozimska 138, 45-057 Opole</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>ul 3 Maja 18, 16-300 Augustów</t>
+          <t>ul Ozimska 138, 45-057 Opole</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11379,12 +11379,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Amber Motoryzacja Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Apex Enterprise sp z oo</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>1249218048</t>
+          <t>1296732048</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11394,27 +11394,27 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>259376457</t>
+          <t>296890429</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>04242856188</t>
+          <t>60042878186</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>0000017662</t>
+          <t>0000075862</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 35, 16-400 Suwałki</t>
+          <t>ulica Bohaterów Westerplatte 155, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 35, 16-400 Suwałki</t>
+          <t>ulica Bohaterów Westerplatte 155, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11441,12 +11441,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Amber Ubezpieczenia S.A.</t>
+          <t>Apex Network sp. z o. o.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>1249297237</t>
+          <t>1296811233</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11456,17 +11456,17 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>249455615</t>
+          <t>296969616</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>05250757571</t>
+          <t>61050779579</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>0000017759</t>
+          <t>0000075959</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -11496,19 +11496,19 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>20180503</t>
+          <t>20180305</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Amber Spawalnictwo SA</t>
+          <t>Clarity Group Sp. z o.o.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>1249376422</t>
+          <t>1296890422</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11518,27 +11518,27 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>249534800</t>
+          <t>297048806</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>60061458925</t>
+          <t>62061480920</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>0000017856</t>
+          <t>0000076056</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>ul. Długa 69/53, 49-300 Brzeg</t>
+          <t>ul. Świętojańska 9/23, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>ul. Długa 69/53, 49-300 Brzeg</t>
+          <t>ul. Świętojańska 9/23, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11565,12 +11565,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Amber Ślusarstwo S. A.</t>
+          <t>Clarity Systems SP Z O O</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>1249455618</t>
+          <t>1306969646</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11580,27 +11580,27 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>249613994</t>
+          <t>307128024</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>61072160315</t>
+          <t>63072182317</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>0000017953</t>
+          <t>0000076153</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>ul Rynek 86, 68-200 Żary</t>
+          <t>ul 10 Lutego 26, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>ul Rynek 86, 68-200 Żary</t>
+          <t>ul 10 Lutego 26, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11627,12 +11627,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Amber Krawiectwo Spółka Akcyjna</t>
+          <t>Clarity Holding spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>1249534803</t>
+          <t>1307048836</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11642,27 +11642,27 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>249693183</t>
+          <t>297207185</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>62082861665</t>
+          <t>64082883667</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>0000018050</t>
+          <t>0000076250</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>ulica Sikorskiego 103, 66-200 Świebodzin</t>
+          <t>ulica Bolesława Prusa 43, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>ulica Sikorskiego 103, 66-200 Świebodzin</t>
+          <t>ulica Bolesława Prusa 43, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11689,12 +11689,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Amber Ochrona sp. z o.o.</t>
+          <t>Clarity Partners Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>1249613997</t>
+          <t>1297127993</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11704,27 +11704,27 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>249772379</t>
+          <t>297286374</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>63090763059</t>
+          <t>65090785051</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>0000018147</t>
+          <t>0000076347</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Armii Krajowej 120, 78-100 Kołobrzeg</t>
+          <t>Kościuszki 60, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Armii Krajowej 120, 78-100 Kołobrzeg</t>
+          <t>Kościuszki 60, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -11744,19 +11744,19 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2022-07-05</t>
+          <t>2022-05-07</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Amber Catering sp z oo</t>
+          <t>Clarity Polska S.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>1249693186</t>
+          <t>1297207189</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11766,27 +11766,27 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>249851564</t>
+          <t>307365592</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>64101464400</t>
+          <t>66101486402</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>0000018244</t>
+          <t>0000076444</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>ul. Piłsudskiego 137/15, 73-110 Stargard</t>
+          <t>ul. Sienkiewicza 77/75, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>ul. Piłsudskiego 137/15, 73-110 Stargard</t>
+          <t>ul. Sienkiewicza 77/75, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -11813,12 +11813,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Amber Księgowość sp. z o. o.</t>
+          <t>Clarity Enterprise SA</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>1249772371</t>
+          <t>1297286378</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11828,27 +11828,27 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>259930787</t>
+          <t>297444755</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>65112165797</t>
+          <t>67112187799</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>0000018341</t>
+          <t>0000076541</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>154, 27-600 Sandomierz</t>
+          <t>ul Dąbrowskiego 94, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>154, 27-600 Sandomierz</t>
+          <t>ul Dąbrowskiego 94, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -11875,12 +11875,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Bizon Budownictwo Sp. z o.o.</t>
+          <t>Clarity Network S. A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>1249851567</t>
+          <t>1297365563</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11890,27 +11890,27 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>250009941</t>
+          <t>297523940</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>66122867147</t>
+          <t>68122889149</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>0000018438</t>
+          <t>0000076638</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 171, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>ulica Rynek 111, 38-400 Krosno</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 171, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>ulica Rynek 111, 38-400 Krosno</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -11937,12 +11937,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Bizon Transport SP Z O O</t>
+          <t>Core Group Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>1249930752</t>
+          <t>1297444759</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11952,27 +11952,27 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>250089130</t>
+          <t>297603136</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>67010768535</t>
+          <t>69010790530</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>0000018535</t>
+          <t>0000076735</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Chmielna 8, 00-020 Warszawa</t>
+          <t>128, 39-300 Mielec</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Chmielna 8, 00-020 Warszawa</t>
+          <t>128, 39-300 Mielec</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -11999,12 +11999,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Bizon Spedycja spółka z ograniczoną odpowiedzialnością</t>
+          <t>Core Systems sp. z o.o.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>1250009942</t>
+          <t>1297523944</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12014,27 +12014,27 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>250168326</t>
+          <t>297682325</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>68021469884</t>
+          <t>70021491888</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>0000018632</t>
+          <t>0000076832</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>ul. Nowy Świat 25/67, 00-029 Warszawa</t>
+          <t>ul. Długa 145/37, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>ul. Nowy Świat 25/67, 00-029 Warszawa</t>
+          <t>ul. Długa 145/37, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12061,12 +12061,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Bizon Logistyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Core Holding sp z oo</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>1250089131</t>
+          <t>1307603166</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12076,27 +12076,27 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>250247511</t>
+          <t>297761510</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>69032171274</t>
+          <t>71032193275</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>0000018729</t>
+          <t>0000076929</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>ul os. Przyjaźń 42, 01-355 Warszawa</t>
+          <t>ul Wojska Polskiego 162, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>ul os. Przyjaźń 42, 01-355 Warszawa</t>
+          <t>ul Wojska Polskiego 162, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12123,12 +12123,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Bizon Handel S.A.</t>
+          <t>Core Partners sp. z o. o.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>1250168327</t>
+          <t>1297682329</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12138,27 +12138,27 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>250326707</t>
+          <t>297840706</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>70042872622</t>
+          <t>72042894624</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>0000018826</t>
+          <t>0000077026</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>ulica Jagiellońska 59, 05-120 Legionowo</t>
+          <t>ulica Chrobrego 179, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>ulica Jagiellońska 59, 05-120 Legionowo</t>
+          <t>ulica Chrobrego 179, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12185,12 +12185,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Bizon Usługi SA</t>
+          <t>Core Polska Sp. z o.o.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>1250247512</t>
+          <t>1297761514</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12200,27 +12200,27 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>250405890</t>
+          <t>297919891</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>71050774016</t>
+          <t>73050796018</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>0000018923</t>
+          <t>0000077123</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Piłsudskiego 76, 05-270 Marki</t>
+          <t>Słowiańska 16, 64-100 Leszno</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Piłsudskiego 76, 05-270 Marki</t>
+          <t>Słowiańska 16, 64-100 Leszno</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12247,12 +12247,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Bizon Finanse S. A.</t>
+          <t>Core Enterprise SP Z O O</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>1250326708</t>
+          <t>1307840736</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12262,27 +12262,27 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>260485119</t>
+          <t>297999080</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>72061475365</t>
+          <t>74061497367</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>0000019020</t>
+          <t>0000077220</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>ul. Andriollego 93/29, 05-400 Otwock</t>
+          <t>ul. Gdańska 33/89, 83-110 Tczew</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>ul. Andriollego 93/29, 05-400 Otwock</t>
+          <t>ul. Gdańska 33/89, 83-110 Tczew</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12309,12 +12309,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Bizon Doradztwo Spółka Akcyjna</t>
+          <t>Core Network spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>1250405891</t>
+          <t>1297919895</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12324,27 +12324,27 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>250564275</t>
+          <t>298078270</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>73072176751</t>
+          <t>75072198753</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>0000019117</t>
+          <t>0000077317</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>ul Żeromskiego 110, 26-600 Radom</t>
+          <t>ul Sobieskiego 50, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>ul Żeromskiego 110, 26-600 Radom</t>
+          <t>ul Sobieskiego 50, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12371,12 +12371,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Bizon Szkolenia sp. z o.o.</t>
+          <t>Direct Group Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>1250485080</t>
+          <t>1297999084</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12386,27 +12386,27 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>250643460</t>
+          <t>298157466</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>74082878101</t>
+          <t>76082800106</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>0000019214</t>
+          <t>0000077414</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>ulica Tumska 127, 09-402 Płock</t>
+          <t>67, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>ulica Tumska 127, 09-402 Płock</t>
+          <t>67, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12433,12 +12433,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Bizon Media sp z oo</t>
+          <t>Direct Systems S.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>1250564276</t>
+          <t>1298078274</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12448,27 +12448,27 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>250722656</t>
+          <t>298236651</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>75090779495</t>
+          <t>77090701490</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>0000019311</t>
+          <t>0000077511</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Karmelicka 144, 31-128 Kraków</t>
+          <t>Małachowskiego 84, 42-500 Będzin</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Karmelicka 144, 31-128 Kraków</t>
+          <t>Małachowskiego 84, 42-500 Będzin</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">

--- a/data/xlsx/vat.xlsx
+++ b/data/xlsx/vat.xlsx
@@ -115,7 +115,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>60021406849</t>
+          <t>62021428841</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -157,7 +157,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Zielony Bieszczady S.A.</t>
+          <t>Pewny Delfin S.A.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -177,7 +177,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>61032108236</t>
+          <t>63032130231</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -219,7 +219,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Zielony Karpaty SA</t>
+          <t>Dobry Koral SA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>62042809586</t>
+          <t>64042831581</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -281,7 +281,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Zielony Bałtyk S. A.</t>
+          <t>Polski Szafir S. A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -301,7 +301,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>63050710972</t>
+          <t>65050732974</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -343,7 +343,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Zielony Sudety Spółka Akcyjna</t>
+          <t>Europejski Orzeł Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -363,7 +363,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>64061412321</t>
+          <t>66061434323</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -405,7 +405,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Niebieski Amber sp. z o.o.</t>
+          <t>Globalny Kaktus sp. z o.o.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -425,7 +425,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>65072113717</t>
+          <t>67072135719</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -467,7 +467,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Niebieski Bizon sp z oo</t>
+          <t>Lokalny Olimp sp z oo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>66082815068</t>
+          <t>68082837060</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -529,7 +529,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Niebieski Canyon s. z o. o.</t>
+          <t>Nowoczesny Beskid sp. z . o.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>67090716451</t>
+          <t>69090738453</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Niebieski Delfin Sp. z o.o.</t>
+          <t>Tradycyjny Canyon Sp. z o.o.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>68101417802</t>
+          <t>70101439803</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Niebieski Echo SP Z O O</t>
+          <t>Dynamiczny Jantar SP Z O O</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>69112119190</t>
+          <t>71112141194</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Niebieski Falcon spółka z ograniczoną odpowiedzialnością</t>
+          <t>Stabilny Rubin spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>70122820541</t>
+          <t>72122842543</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -777,7 +777,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Niebieski Gryf Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Innowacyjny Sokół Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>71010721939</t>
+          <t>73010743931</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Niebieski Horyzont S.A.</t>
+          <t>Kreatywny Jodełka S.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>72021423289</t>
+          <t>74021445281</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Niebieski Ikar SA</t>
+          <t>Aktywny Zodiak SA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>73032124675</t>
+          <t>75032146677</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Niebieski Jantar S. A.</t>
+          <t>Jasny Kasprowy S. A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>74042826025</t>
+          <t>76042848027</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Niebieski Koral Spółka Akcyjna</t>
+          <t>Green Bizon Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>75050727418</t>
+          <t>77050749410</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1087,7 +1087,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Niebieski Lotos sp. z o.o.</t>
+          <t>Blue Ikar sp. z o.o.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>76061428767</t>
+          <t>78061450762</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1149,7 +1149,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Niebieski Magnolia sp z oo</t>
+          <t>Gold Pegaz sp z oo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>77072130157</t>
+          <t>79072152159</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Niebieski Neon sp. z o. o.</t>
+          <t>Silver Żubr sp. z o. o.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>78082831506</t>
+          <t>80082853507</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1273,7 +1273,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Niebieski Oaza Sp. z o.o.</t>
+          <t>Smart Narew Sp. z o.o.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>79090732890</t>
+          <t>81090754891</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P.P.H.U. Niebieski Pegaz</t>
+          <t>P.P.H.U. Fast Syrena</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80101434241</t>
+          <t>82101456243</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1397,7 +1397,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Niebieski Rubin spółka z ograniczoną odpowiedzialnością</t>
+          <t>Safe Rysy spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>81112135637</t>
+          <t>83112157639</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1459,7 +1459,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Niebieski Szafir Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Best Amber Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82122836987</t>
+          <t>84122858989</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Niebieski Tytan S.A.</t>
+          <t>Global Horyzont S.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>83010738376</t>
+          <t>85010760371</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1583,7 +1583,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Niebieski Uran SA</t>
+          <t>Future Oaza SA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>84021439724</t>
+          <t>86021461729</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1645,7 +1645,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Niebieski Wektor S. A.</t>
+          <t>Wielkopolski Zefir S. A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>85032141114</t>
+          <t>87032163116</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Niebieski Zefir Spółka Akcyjna</t>
+          <t>Śląski Pilica Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>86042842464</t>
+          <t>88042864466</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1769,7 +1769,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Niebieski Żubr sp. z o.o.</t>
+          <t>Mazowiecki Marmur sp. z o.o.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>87050743857</t>
+          <t>89050765859</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Niebieski Sokół sp z oo</t>
+          <t>Pomorski Giewont sp z oo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>88061445206</t>
+          <t>90061467207</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1893,7 +1893,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Niebieski Orzeł sp. z o. o.</t>
+          <t>Dolnośląski Sudety sp. z o. o.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>89072146593</t>
+          <t>91072168594</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1955,7 +1955,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Niebieski Kormoran Sp. z o.o.</t>
+          <t>Karpacki Gryf Sp. z o.o.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2017,7 +2017,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Niebieski Barycz SP Z O O</t>
+          <t>Bałtycki Neon SP Z O O</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2079,7 +2079,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Niebieski Noteć spółka z ograniczoną odpowiedzialnością</t>
+          <t>Młody Wektor spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2141,7 +2141,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Niebieski Pilica Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Wspólny Noteć Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2203,7 +2203,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Niebieski Narew S.A.</t>
+          <t>Pierwszy Granit S.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2265,7 +2265,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Niebieski Jodełka SA</t>
+          <t>Zielony Żubr SA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2327,7 +2327,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Niebieski Kaktus S. A.</t>
+          <t>Niebieski Narew S. A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2389,7 +2389,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Niebieski Szmaragd Spółka Akcyjna</t>
+          <t>Złoty Syrena Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Niebieski Topaz sp. z o.o.</t>
+          <t>Srebrny Rysy sp. z o.o.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>395487097</t>
+          <t>295487097</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Niebieski Granit sp z oo</t>
+          <t>Czysty Amber sp z oo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2637,7 +2637,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Niebieski Syrena Sp. z o.o.</t>
+          <t>Pewny Oaza Sp. z o.o.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2699,7 +2699,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Niebieski Zodiak SP Z O O</t>
+          <t>Dobry Zefir SP Z O O</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>285803821</t>
+          <t>385803821</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2761,7 +2761,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Niebieski Olimp spółka z ograniczoną odpowiedzialnością</t>
+          <t>Polski Pilica spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2823,7 +2823,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Niebieski Zorza Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Europejski Marmur Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2885,7 +2885,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Niebieski Krokus S.A.</t>
+          <t>Globalny Giewont S.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2947,7 +2947,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Niebieski Narcyz SA</t>
+          <t>Lokalny Sudety SA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3009,7 +3009,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Niebieski Giewont S. A.</t>
+          <t>Nowoczesny Gryf S. A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3071,7 +3071,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Niebieski Rysy Spółka Akcyjna</t>
+          <t>Tradycyjny Neon Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3133,7 +3133,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Niebieski Kasprowy sp. z o.o.</t>
+          <t>Dynamiczny Wektor sp. z o.o.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3257,7 +3257,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Amber Transport sp. z o. o.</t>
+          <t>Falcon Transport sp. z o. o.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3319,7 +3319,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Amber Spedycja Sp. z o.o.</t>
+          <t>Koral Spedycja Sp. z o.o.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3381,7 +3381,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Amber Logistyka SP Z O O</t>
+          <t>Pegaz Logistyka SP Z O O</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3443,7 +3443,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Amber Handel spółka z ograniczoną odpowiedzialnością</t>
+          <t>Wektor Handel spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3505,7 +3505,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Amber Usługi Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kormoran Usługi Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3567,7 +3567,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Amber Finanse S.A.</t>
+          <t>Jodełka Finanse S.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Amber Doradztwo SA</t>
+          <t>Marmur Doradztwo SA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3691,7 +3691,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Amber Szkolenia S. A.</t>
+          <t>Krokus Szkolenia S. A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3753,7 +3753,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Amber Media Spółka Akcyjna</t>
+          <t>Beskid Media Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3877,7 +3877,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Amber Marketing sp z oo</t>
+          <t>Falcon Marketing sp z oo</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3939,7 +3939,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Amber Druk sp. z o. o.</t>
+          <t>Koral Druk sp. z o. o.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4001,7 +4001,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Amber Informatyka Sp. z o.o.</t>
+          <t>Pegaz Informatyka Sp. z o.o.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4063,7 +4063,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Amber Oprogramowanie SP Z O O</t>
+          <t>Wektor Oprogramowanie SP Z O O</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4125,7 +4125,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Amber Rolnictwo spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kormoran Rolnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4187,7 +4187,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Amber Ogrodnictwo Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jodełka Ogrodnictwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Amber Produkcja S.A.</t>
+          <t>Marmur Produkcja S.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4311,7 +4311,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Amber Przemysł SA</t>
+          <t>Krokus Przemysł SA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4373,7 +4373,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Amber Ekologia S. A.</t>
+          <t>Beskid Ekologia S. A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Amber Instalacje sp. z o.o.</t>
+          <t>Falcon Instalacje sp. z o.o.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4559,7 +4559,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Amber Nieruchomości sp z oo</t>
+          <t>Koral Nieruchomości sp z oo</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4621,7 +4621,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Amber Inwestycje sp. z o. o.</t>
+          <t>Pegaz Inwestycje sp. z o. o.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4683,7 +4683,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Amber Medycyna Sp. z o.o.</t>
+          <t>Wektor Medycyna Sp. z o.o.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4745,7 +4745,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Amber Zdrowie SP Z O O</t>
+          <t>Kormoran Zdrowie SP Z O O</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4807,7 +4807,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Amber Urody spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jodełka Urody spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4869,7 +4869,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Amber Turystyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Marmur Turystyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4931,7 +4931,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Amber Rozrywka S.A.</t>
+          <t>Krokus Rozrywka S.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4993,7 +4993,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Amber Gastronomia SA</t>
+          <t>Beskid Gastronomia SA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5117,7 +5117,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Amber Tekstylia Spółka Akcyjna</t>
+          <t>Falcon Tekstylia Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5179,7 +5179,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Amber Motoryzacja sp. z o.o.</t>
+          <t>Koral Motoryzacja sp. z o.o.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5199,32 +5199,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>98122841184</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0000066162</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ulica Kościuszki 75, 16-400 Suwałki</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ulica Kościuszki 75, 16-400 Suwałki</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>26 2399 6551 2838 7620 3194 9893</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
           <t/>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>0000066162</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>ulica Kościuszki 75, 16-400 Suwałki</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>ulica Kościuszki 75, 16-400 Suwałki</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>26 2399 6551 2838 7620 3194 9893</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>False</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5241,7 +5241,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Amber Ubezpieczenia sp z oo</t>
+          <t>Pegaz Ubezpieczenia sp z oo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5303,7 +5303,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Amber Spawalnictwo sp. z o. o.</t>
+          <t>Wektor Spawalnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5365,7 +5365,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Amber Ślusarstwo Sp. z o.o.</t>
+          <t>Kormoran Ślusarstwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5427,12 +5427,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Amber Krawiectwo SP Z O O</t>
+          <t>Jodełka Krawiectwo SP Z O O</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t/>
+          <t>1289129807</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5489,7 +5489,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Amber Ochrona spółka z ograniczoną odpowiedzialnością</t>
+          <t>Marmur Ochrona spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5551,12 +5551,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Amber Catering Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Krokus Catering Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1299288217</t>
+          <t/>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5613,7 +5613,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Amber Księgowość S.A.</t>
+          <t>Beskid Księgowość S.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5675,7 +5675,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Bizon Budownictwo SA</t>
+          <t>Jantar Budownictwo SA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5737,7 +5737,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Bizon Transport S. A.</t>
+          <t>Oaza Transport S. A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5799,7 +5799,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Bizon Spedycja Spółka Akcyjna</t>
+          <t>Uran Spedycja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5861,7 +5861,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Bizon Logistyka sp. z o.o.</t>
+          <t>Orzeł Logistyka sp. z o.o.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5923,7 +5923,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Bizon Handel sp z oo</t>
+          <t>Narew Handel sp z oo</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5985,7 +5985,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Bizon Usługi sp. z o. o.</t>
+          <t>Granit Usługi sp. z o. o.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6047,7 +6047,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Bizon Finanse Sp. z o.o.</t>
+          <t>Zorza Finanse Sp. z o.o.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6109,7 +6109,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Bizon Doradztwo SP Z O O</t>
+          <t>Kasprowy Doradztwo SP Z O O</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6171,7 +6171,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Bizon Szkolenia spółka z ograniczoną odpowiedzialnością</t>
+          <t>Sudety Szkolenia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6233,7 +6233,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Bizon Media Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Echo Media Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6295,7 +6295,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>P.P.H.U. Bizon Reklama</t>
+          <t>P.P.H.U. Jantar Reklama</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6357,7 +6357,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Bizon Marketing SA</t>
+          <t>Oaza Marketing SA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6419,7 +6419,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Bizon Druk S. A.</t>
+          <t>Uran Druk S. A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6481,7 +6481,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Bizon Informatyka Spółka Akcyjna</t>
+          <t>Orzeł Informatyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6543,7 +6543,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Bizon Oprogramowanie sp. z o.o.</t>
+          <t>Narew Oprogramowanie sp. z o.o.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6605,7 +6605,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Bizon Rolnictwo sp z oo</t>
+          <t>Granit Rolnictwo sp z oo</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6667,7 +6667,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Bizon Ogrodnictwo sp. z o. o.</t>
+          <t>Zorza Ogrodnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6729,7 +6729,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Bizon Produkcaj Sp. z o.o.</t>
+          <t>Kasprowy Produkcja Sp. z o.o.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6791,7 +6791,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Bizon Przemysł SP Z O O</t>
+          <t>Sudety Przemysł SP Z O O</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6853,7 +6853,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Bizon Ekologia spółka z ograniczoną odpowiedzialnością</t>
+          <t>Echo Ekologia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6915,7 +6915,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Bizon Energetyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jantar Energetyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6977,7 +6977,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Bizon Instalacje S.A.</t>
+          <t>Oaza Instalacje S.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7039,7 +7039,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Bizon Nieruchomości SA</t>
+          <t>Uran Nieruchomości SA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7101,7 +7101,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Bizon Inwestycje S. A.</t>
+          <t>Orzeł Inwestycje S. A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7163,7 +7163,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Bizon Medycyna Spółka Akcyjna</t>
+          <t>Narew Medycyna Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7225,7 +7225,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Bizon Zdrowie sp. z o.o.</t>
+          <t>Granit Zdrowie sp. z o.o.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7287,7 +7287,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Bizon Urody sp z oo</t>
+          <t>Zorza Urody sp z oo</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7349,7 +7349,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Bizon Turystyka sp. z o. o.</t>
+          <t>Kasprowy Turystyka sp. z o. o.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7411,7 +7411,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Bizon Rozrywka Sp. z o.o.</t>
+          <t>Sudety Rozrywka Sp. z o.o.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t/>
+          <t>291822268</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7473,7 +7473,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Bizon Gastronomia SP Z O O</t>
+          <t>Echo Gastronomia SP Z O O</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>291980642</t>
+          <t/>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7597,7 +7597,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Bizon Tekstylia Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Oaza Tekstylia Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7659,7 +7659,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Bizon Motoryzacja S.A.</t>
+          <t>Uran Motoryzacja S.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7721,7 +7721,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Bizon Ubezpieczenia SA</t>
+          <t>Orzeł Ubezpieczenia SA</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7783,7 +7783,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Bizon Spawalnictwo S. A.</t>
+          <t>Narew Spawalnictwo S. A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7845,7 +7845,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Bizon Ślusarstwo Spółka Akcyjna</t>
+          <t>Granit Ślusarstwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7907,7 +7907,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Bizon Krawiectwo sp. z o.o.</t>
+          <t>Zorza Krawiectwo sp. z o.o.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7969,7 +7969,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Bizon Ochrona sp z oo</t>
+          <t>Kasprowy Ochrona sp z oo</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8031,7 +8031,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Bizon Catering sp. z o. o.</t>
+          <t>Sudety Catering sp. z o. o.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>98101404209</t>
+          <t>08101404209</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -8093,7 +8093,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Bizon Księgowość Sp. z o.o.</t>
+          <t>Echo Księgowość Sp. z o.o.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>09112105596</t>
+          <t>99112105596</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8155,7 +8155,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Canyon Budownictwo SP Z O O</t>
+          <t>Tytan Budownictwo SP Z O O</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8217,7 +8217,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Canyon Transport spółka z ograniczoną odpowiedzialnością</t>
+          <t>Sokół Transport spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8279,7 +8279,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Canyon Spedycja Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Pilica Spedycja Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8341,7 +8341,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Canyon Logistyka S.A.</t>
+          <t>Topaz Logistyka S.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8403,7 +8403,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Canyon Handel SA</t>
+          <t>Olimp Handel SA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8465,7 +8465,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Canyon Usługi S. A.</t>
+          <t>Rysy Usługi S. A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8527,7 +8527,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Canyon Finanse Spółka Akcyjna</t>
+          <t>Bałtyk Finanse Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8589,7 +8589,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Canyon Doradztwo sp. z o.o.</t>
+          <t>Delfin Doradztwo sp. z o.o.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8651,7 +8651,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Canyon Szkolenia sp z oo</t>
+          <t>Ikar Szkolenia sp z oo</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8713,12 +8713,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Canyon Media sp. z o. o.</t>
+          <t>Neon Media sp. z o. o.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2293326879</t>
+          <t>1293326879</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8775,12 +8775,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PPHU Canyon Reklama</t>
+          <t>PPHU Tytan Reklama</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1293406064</t>
+          <t>2293406064</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8837,7 +8837,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Canyon Marketing SP Z O O</t>
+          <t>Sokół Marketing SP Z O O</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8899,7 +8899,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Canyon Druk spółka z ograniczoną odpowiedzialnością</t>
+          <t>Pilica Druk spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8961,7 +8961,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Canyon Informatyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Topaz Informatyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9023,7 +9023,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Canyon Oprogramowanie S.A.</t>
+          <t>Olimp Oprogramowanie S.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9085,7 +9085,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Canyon Rolnictwo SA</t>
+          <t>Rysy Rolnictwo SA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9147,7 +9147,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Canyon Ogrodnictwo S. A.</t>
+          <t>Bałtyk Ogrodnictwo S. A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9209,7 +9209,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Canyon Produkcja Spółka Akcyjna</t>
+          <t>Delfin Produkcja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9271,7 +9271,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Canyon Przemysł sp. z o.o.</t>
+          <t>Ikar Przemysł sp. z o.o.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9333,7 +9333,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Canyon Ekologia sp z oo</t>
+          <t>Neon Ekologia sp z oo</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9395,7 +9395,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Canyon Energetyka sp. z o. o.</t>
+          <t>Tytan Energetyka sp. z o. o.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9450,14 +9450,14 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2021/26/06</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Canyon Instalacje Sp. z o.o.</t>
+          <t>Sokół Instalacje Sp. z o.o.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9519,7 +9519,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Canyon Nieruchomości SP Z O O</t>
+          <t>Pilica Nieruchomości SP Z O O</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9581,7 +9581,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Canyon Inwestycje spółka z ograniczoną odpowiedzialnością</t>
+          <t>Topaz Inwestycje spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9643,7 +9643,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Canyon Medycyna Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Olimp Medycyna Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9705,7 +9705,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Canyon Zdrowie S.A.</t>
+          <t>Rysy Zdrowie S.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9767,7 +9767,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Canyon Urody SA</t>
+          <t>Bałtyk Urody SA</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -9829,7 +9829,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Canyon Turystyka S. .</t>
+          <t>Delfin Turystyka S. A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -9891,7 +9891,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Canyon Rozrywka Spółka Akcyjna</t>
+          <t>Ikar Rozrywka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -9953,7 +9953,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Canyon Gastronomia sp. z o.o.</t>
+          <t>Neon Gastronomia sp. z o.o.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10077,7 +10077,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Canyon Tekstylia sp. z o. o.</t>
+          <t>Sokół Tekstylia sp. z o. o.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10139,7 +10139,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Canyon Motoryzacja Sp. z o.o.</t>
+          <t>Pilica Motoryzacja Sp. z o.o.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10201,7 +10201,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Canyon Ubezpieczenia SP Z O O</t>
+          <t>Topaz Ubezpieczenia SP Z O O</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10263,7 +10263,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Canyon Spawalnictwo spółka z ograniczoną odpowiedzialnością</t>
+          <t>Olimp Spawalnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10325,7 +10325,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Canyon Ślusarstwo Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Rysy Ślusarstwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10387,7 +10387,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Canyon Krawiectwo S.A.</t>
+          <t>Bałtyk Krawiectwo S.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10449,7 +10449,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Canyon Ochrona SA</t>
+          <t>Delfin Ochrona SA</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10511,7 +10511,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Canyon Catering S. A.</t>
+          <t>Ikar Catering S. A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10573,7 +10573,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Canyon Księgowość Spółka Akcyjna</t>
+          <t>Neon Księgowość Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
